--- a/Laboratorio_de_mecanica_y_ondas_para_biociencias_2026-2/Notas/Notas_Laboratorio_Biociencias_G4_2026-2.xlsx
+++ b/Laboratorio_de_mecanica_y_ondas_para_biociencias_2026-2/Notas/Notas_Laboratorio_Biociencias_G4_2026-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\miguel_perdomo\Auxiliar_docente_UNAL\Laboratorio_de_mecanica_y_ondas_para_biociencias_2026-2\Notas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172A5A04-52D5-44D5-95CC-940520FB8E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FA444A-6378-4554-99F2-29B4B463AC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Configuración" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Notas!$A$3:$AG$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Notas!$A$3:$AG$36</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -425,7 +425,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="200">
   <si>
     <t>CÓMO USAR ESTE LIBRO</t>
   </si>
@@ -1019,6 +1019,12 @@
   </si>
   <si>
     <t xml:space="preserve">Registro de calificaciones · Semestre 2026-2 · </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Karen Hasbleidy Chacon Castro</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1035,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1141,8 +1147,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1191,6 +1203,12 @@
         <bgColor rgb="FFF0FAF3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFF0FAF3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1234,23 +1252,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1362,6 +1365,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1694,264 +1718,264 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
     </row>
     <row r="4" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
     </row>
     <row r="5" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
     </row>
     <row r="10" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
     </row>
     <row r="11" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
     </row>
     <row r="12" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
     </row>
     <row r="13" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
     </row>
     <row r="14" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
     </row>
     <row r="15" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
     </row>
     <row r="18" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
     </row>
     <row r="19" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
     </row>
     <row r="20" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
     </row>
     <row r="21" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
     </row>
     <row r="22" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
     </row>
     <row r="23" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
     </row>
     <row r="24" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
     </row>
     <row r="27" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
     </row>
     <row r="28" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
     </row>
     <row r="29" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
     </row>
     <row r="30" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
     </row>
     <row r="31" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -1990,7 +2014,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AG35"/>
+  <dimension ref="A1:AG36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.42578125" customWidth="1"/>
@@ -2011,2251 +2035,2317 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
+      <c r="AB1" s="46"/>
+      <c r="AC1" s="46"/>
+      <c r="AD1" s="46"/>
+      <c r="AE1" s="46"/>
+      <c r="AF1" s="46"/>
+      <c r="AG1" s="46"/>
     </row>
     <row r="2" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="47" t="s">
         <v>197</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
-      <c r="AC2" s="1"/>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="1"/>
-      <c r="AG2" s="1"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47"/>
+      <c r="W2" s="47"/>
+      <c r="X2" s="47"/>
+      <c r="Y2" s="47"/>
+      <c r="Z2" s="47"/>
+      <c r="AA2" s="47"/>
+      <c r="AB2" s="47"/>
+      <c r="AC2" s="47"/>
+      <c r="AD2" s="47"/>
+      <c r="AE2" s="47"/>
+      <c r="AF2" s="47"/>
+      <c r="AG2" s="47"/>
     </row>
     <row r="3" spans="1:33" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="P3" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="Q3" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="R3" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="S3" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="T3" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="U3" s="11" t="s">
+      <c r="U3" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="V3" s="11" t="s">
+      <c r="V3" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="W3" s="11" t="s">
+      <c r="W3" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="X3" s="11" t="s">
+      <c r="X3" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="Y3" s="11" t="s">
+      <c r="Y3" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="Z3" s="11" t="s">
+      <c r="Z3" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AA3" s="11" t="s">
+      <c r="AA3" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="AB3" s="11" t="s">
+      <c r="AB3" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="AC3" s="11" t="s">
+      <c r="AC3" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="AD3" s="11" t="s">
+      <c r="AD3" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="AE3" s="11" t="s">
+      <c r="AE3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AF3" s="12" t="s">
+      <c r="AF3" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="AG3" s="11" t="s">
+      <c r="AG3" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="8">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="10">
         <v>7</v>
       </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="17" t="str">
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="12" t="str">
         <f t="shared" ref="O4:O33" si="0">IFERROR(AVERAGE(E4:N4),"")</f>
         <v/>
       </c>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="17" t="str">
+      <c r="P4" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="12">
         <f t="shared" ref="R4:R33" si="1">IFERROR(AVERAGE(P4:Q4),"")</f>
-        <v/>
-      </c>
-      <c r="S4" s="16"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="16"/>
-      <c r="W4" s="16"/>
-      <c r="X4" s="16"/>
-      <c r="Y4" s="16"/>
-      <c r="Z4" s="16"/>
-      <c r="AA4" s="17" t="str">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="11"/>
+      <c r="W4" s="11"/>
+      <c r="X4" s="11"/>
+      <c r="Y4" s="11"/>
+      <c r="Z4" s="11"/>
+      <c r="AA4" s="12" t="str">
         <f t="shared" ref="AA4:AA33" si="2">IFERROR(AVERAGE(S4:Z4),"")</f>
         <v/>
       </c>
-      <c r="AB4" s="16"/>
-      <c r="AC4" s="16"/>
-      <c r="AD4" s="17" t="str">
+      <c r="AB4" s="11"/>
+      <c r="AC4" s="11"/>
+      <c r="AD4" s="12" t="str">
         <f t="shared" ref="AD4:AD33" si="3">IFERROR(AVERAGE(AB4:AC4),"")</f>
         <v/>
       </c>
-      <c r="AE4" s="18">
+      <c r="AE4" s="13">
         <v>1</v>
       </c>
-      <c r="AF4" s="19" t="str">
+      <c r="AF4" s="14">
         <f>IFERROR((IF(O4="",0,O4*Configuración!$B$4)+IF(R4="",0,R4*Configuración!$B$5)+IF(AA4="",0,AA4*Configuración!$B$6)+IF(AD4="",0,AD4*Configuración!$B$7))/(IF(O4="",0,Configuración!$B$4)+IF(R4="",0,Configuración!$B$5)+IF(AA4="",0,Configuración!$B$6)+IF(AD4="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG4" s="20" t="str">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AG4" s="15" t="str">
         <f>IF(AF4="","",IF(AE4&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF4&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="5" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21">
+      <c r="A5" s="16">
         <v>2</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="10">
         <v>2</v>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="17" t="str">
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="17" t="str">
+      <c r="P5" s="11">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S5" s="16"/>
-      <c r="T5" s="16"/>
-      <c r="U5" s="16"/>
-      <c r="V5" s="16"/>
-      <c r="W5" s="16"/>
-      <c r="X5" s="16"/>
-      <c r="Y5" s="16"/>
-      <c r="Z5" s="16"/>
-      <c r="AA5" s="17" t="str">
+        <v>5</v>
+      </c>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="11"/>
+      <c r="Z5" s="11"/>
+      <c r="AA5" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB5" s="16"/>
-      <c r="AC5" s="16"/>
-      <c r="AD5" s="17" t="str">
+      <c r="AB5" s="11"/>
+      <c r="AC5" s="11"/>
+      <c r="AD5" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE5" s="18">
+      <c r="AE5" s="13">
         <v>1</v>
       </c>
-      <c r="AF5" s="19" t="str">
+      <c r="AF5" s="14">
         <f>IFERROR((IF(O5="",0,O5*Configuración!$B$4)+IF(R5="",0,R5*Configuración!$B$5)+IF(AA5="",0,AA5*Configuración!$B$6)+IF(AD5="",0,AD5*Configuración!$B$7))/(IF(O5="",0,Configuración!$B$4)+IF(R5="",0,Configuración!$B$5)+IF(AA5="",0,Configuración!$B$6)+IF(AD5="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG5" s="20" t="str">
+        <v>5</v>
+      </c>
+      <c r="AG5" s="15" t="str">
         <f>IF(AF5="","",IF(AE5&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF5&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13">
+      <c r="A6" s="8">
         <v>3</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="10">
         <v>7</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="17" t="str">
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="17" t="str">
+      <c r="P6" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="16"/>
-      <c r="Z6" s="16"/>
-      <c r="AA6" s="17" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="S6" s="11"/>
+      <c r="T6" s="11"/>
+      <c r="U6" s="11"/>
+      <c r="V6" s="11"/>
+      <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11"/>
+      <c r="AA6" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB6" s="16"/>
-      <c r="AC6" s="16"/>
-      <c r="AD6" s="17" t="str">
+      <c r="AB6" s="11"/>
+      <c r="AC6" s="11"/>
+      <c r="AD6" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE6" s="18">
+      <c r="AE6" s="13">
         <v>1</v>
       </c>
-      <c r="AF6" s="19" t="str">
+      <c r="AF6" s="14">
         <f>IFERROR((IF(O6="",0,O6*Configuración!$B$4)+IF(R6="",0,R6*Configuración!$B$5)+IF(AA6="",0,AA6*Configuración!$B$6)+IF(AD6="",0,AD6*Configuración!$B$7))/(IF(O6="",0,Configuración!$B$4)+IF(R6="",0,Configuración!$B$5)+IF(AA6="",0,Configuración!$B$6)+IF(AD6="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG6" s="20" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="AG6" s="15" t="str">
         <f>IF(AF6="","",IF(AE6&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF6&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="7" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21">
+      <c r="A7" s="16">
         <v>4</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="10">
         <v>4</v>
       </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="17" t="str">
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="17" t="str">
+      <c r="P7" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="16"/>
-      <c r="Z7" s="16"/>
-      <c r="AA7" s="17" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="S7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+      <c r="W7" s="11"/>
+      <c r="X7" s="11"/>
+      <c r="Y7" s="11"/>
+      <c r="Z7" s="11"/>
+      <c r="AA7" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB7" s="16"/>
-      <c r="AC7" s="16"/>
-      <c r="AD7" s="17" t="str">
+      <c r="AB7" s="11"/>
+      <c r="AC7" s="11"/>
+      <c r="AD7" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE7" s="18">
+      <c r="AE7" s="13">
         <v>1</v>
       </c>
-      <c r="AF7" s="19" t="str">
+      <c r="AF7" s="14">
         <f>IFERROR((IF(O7="",0,O7*Configuración!$B$4)+IF(R7="",0,R7*Configuración!$B$5)+IF(AA7="",0,AA7*Configuración!$B$6)+IF(AD7="",0,AD7*Configuración!$B$7))/(IF(O7="",0,Configuración!$B$4)+IF(R7="",0,Configuración!$B$5)+IF(AA7="",0,Configuración!$B$6)+IF(AD7="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG7" s="20" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="AG7" s="15" t="str">
         <f>IF(AF7="","",IF(AE7&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF7&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="8" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
+      <c r="A8" s="8">
         <v>5</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="10">
         <v>4</v>
       </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="17" t="str">
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="17" t="str">
+      <c r="P8" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="16"/>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="16"/>
-      <c r="AA8" s="17" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
+      <c r="Y8" s="11"/>
+      <c r="Z8" s="11"/>
+      <c r="AA8" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB8" s="16"/>
-      <c r="AC8" s="16"/>
-      <c r="AD8" s="17" t="str">
+      <c r="AB8" s="11"/>
+      <c r="AC8" s="11"/>
+      <c r="AD8" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE8" s="18">
+      <c r="AE8" s="13">
         <v>1</v>
       </c>
-      <c r="AF8" s="19" t="str">
+      <c r="AF8" s="14">
         <f>IFERROR((IF(O8="",0,O8*Configuración!$B$4)+IF(R8="",0,R8*Configuración!$B$5)+IF(AA8="",0,AA8*Configuración!$B$6)+IF(AD8="",0,AD8*Configuración!$B$7))/(IF(O8="",0,Configuración!$B$4)+IF(R8="",0,Configuración!$B$5)+IF(AA8="",0,Configuración!$B$6)+IF(AD8="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG8" s="20" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="AG8" s="15" t="str">
         <f>IF(AF8="","",IF(AE8&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF8&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21">
+      <c r="A9" s="16">
         <v>6</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="10">
         <v>5</v>
       </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="17" t="str">
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="17" t="str">
+      <c r="P9" s="11">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="17" t="str">
+        <v>5</v>
+      </c>
+      <c r="S9" s="11"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="11"/>
+      <c r="V9" s="11"/>
+      <c r="W9" s="11"/>
+      <c r="X9" s="11"/>
+      <c r="Y9" s="11"/>
+      <c r="Z9" s="11"/>
+      <c r="AA9" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB9" s="16"/>
-      <c r="AC9" s="16"/>
-      <c r="AD9" s="17" t="str">
+      <c r="AB9" s="11"/>
+      <c r="AC9" s="11"/>
+      <c r="AD9" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE9" s="18">
+      <c r="AE9" s="13">
         <v>1</v>
       </c>
-      <c r="AF9" s="19" t="str">
+      <c r="AF9" s="14">
         <f>IFERROR((IF(O9="",0,O9*Configuración!$B$4)+IF(R9="",0,R9*Configuración!$B$5)+IF(AA9="",0,AA9*Configuración!$B$6)+IF(AD9="",0,AD9*Configuración!$B$7))/(IF(O9="",0,Configuración!$B$4)+IF(R9="",0,Configuración!$B$5)+IF(AA9="",0,Configuración!$B$6)+IF(AD9="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG9" s="20" t="str">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="15" t="str">
         <f>IF(AF9="","",IF(AE9&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF9&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13">
+      <c r="A10" s="8">
         <v>7</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="10">
         <v>4</v>
       </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="46"/>
-      <c r="O10" s="17" t="str">
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="17" t="str">
+      <c r="P10" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
-      <c r="Y10" s="16"/>
-      <c r="Z10" s="16"/>
-      <c r="AA10" s="17" t="str">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="11"/>
+      <c r="W10" s="11"/>
+      <c r="X10" s="11"/>
+      <c r="Y10" s="11"/>
+      <c r="Z10" s="11"/>
+      <c r="AA10" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB10" s="16"/>
-      <c r="AC10" s="16"/>
-      <c r="AD10" s="17" t="str">
+      <c r="AB10" s="11"/>
+      <c r="AC10" s="11"/>
+      <c r="AD10" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE10" s="18">
+      <c r="AE10" s="13">
         <v>1</v>
       </c>
-      <c r="AF10" s="19" t="str">
+      <c r="AF10" s="14">
         <f>IFERROR((IF(O10="",0,O10*Configuración!$B$4)+IF(R10="",0,R10*Configuración!$B$5)+IF(AA10="",0,AA10*Configuración!$B$6)+IF(AD10="",0,AD10*Configuración!$B$7))/(IF(O10="",0,Configuración!$B$4)+IF(R10="",0,Configuración!$B$5)+IF(AA10="",0,Configuración!$B$6)+IF(AD10="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG10" s="20" t="str">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AG10" s="15" t="str">
         <f>IF(AF10="","",IF(AE10&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF10&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="11" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21">
+      <c r="A11" s="16">
         <v>8</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="10">
         <v>6</v>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="17" t="str">
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="17" t="str">
+      <c r="P11" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S11" s="16"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="16"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="17" t="str">
+        <v>4.2</v>
+      </c>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="11"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="11"/>
+      <c r="AA11" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB11" s="16"/>
-      <c r="AC11" s="16"/>
-      <c r="AD11" s="17" t="str">
+      <c r="AB11" s="11"/>
+      <c r="AC11" s="11"/>
+      <c r="AD11" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE11" s="18">
+      <c r="AE11" s="13">
         <v>1</v>
       </c>
-      <c r="AF11" s="19" t="str">
+      <c r="AF11" s="14">
         <f>IFERROR((IF(O11="",0,O11*Configuración!$B$4)+IF(R11="",0,R11*Configuración!$B$5)+IF(AA11="",0,AA11*Configuración!$B$6)+IF(AD11="",0,AD11*Configuración!$B$7))/(IF(O11="",0,Configuración!$B$4)+IF(R11="",0,Configuración!$B$5)+IF(AA11="",0,Configuración!$B$6)+IF(AD11="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG11" s="20" t="str">
+        <v>4.2</v>
+      </c>
+      <c r="AG11" s="15" t="str">
         <f>IF(AF11="","",IF(AE11&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF11&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="12" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13">
+      <c r="A12" s="8">
         <v>9</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="10">
         <v>7</v>
       </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="17" t="str">
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="17" t="str">
+      <c r="P12" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="16"/>
-      <c r="Y12" s="16"/>
-      <c r="Z12" s="16"/>
-      <c r="AA12" s="17" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="11"/>
+      <c r="W12" s="11"/>
+      <c r="X12" s="11"/>
+      <c r="Y12" s="11"/>
+      <c r="Z12" s="11"/>
+      <c r="AA12" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB12" s="16"/>
-      <c r="AC12" s="16"/>
-      <c r="AD12" s="17" t="str">
+      <c r="AB12" s="11"/>
+      <c r="AC12" s="11"/>
+      <c r="AD12" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE12" s="18">
+      <c r="AE12" s="13">
         <v>1</v>
       </c>
-      <c r="AF12" s="19" t="str">
+      <c r="AF12" s="14">
         <f>IFERROR((IF(O12="",0,O12*Configuración!$B$4)+IF(R12="",0,R12*Configuración!$B$5)+IF(AA12="",0,AA12*Configuración!$B$6)+IF(AD12="",0,AD12*Configuración!$B$7))/(IF(O12="",0,Configuración!$B$4)+IF(R12="",0,Configuración!$B$5)+IF(AA12="",0,Configuración!$B$6)+IF(AD12="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG12" s="20" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="AG12" s="15" t="str">
         <f>IF(AF12="","",IF(AE12&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF12&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="13" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21">
+      <c r="A13" s="16">
         <v>10</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="10">
         <v>5</v>
       </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="17" t="str">
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="17" t="str">
+      <c r="P13" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="16"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
-      <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
-      <c r="AA13" s="17" t="str">
+        <v>4.3</v>
+      </c>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="11"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="11"/>
+      <c r="AA13" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB13" s="16"/>
-      <c r="AC13" s="16"/>
-      <c r="AD13" s="17" t="str">
+      <c r="AB13" s="11"/>
+      <c r="AC13" s="11"/>
+      <c r="AD13" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE13" s="18">
+      <c r="AE13" s="13">
         <v>1</v>
       </c>
-      <c r="AF13" s="19" t="str">
+      <c r="AF13" s="14">
         <f>IFERROR((IF(O13="",0,O13*Configuración!$B$4)+IF(R13="",0,R13*Configuración!$B$5)+IF(AA13="",0,AA13*Configuración!$B$6)+IF(AD13="",0,AD13*Configuración!$B$7))/(IF(O13="",0,Configuración!$B$4)+IF(R13="",0,Configuración!$B$5)+IF(AA13="",0,Configuración!$B$6)+IF(AD13="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG13" s="20" t="str">
+        <v>4.3</v>
+      </c>
+      <c r="AG13" s="15" t="str">
         <f>IF(AF13="","",IF(AE13&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF13&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="14" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13">
+      <c r="A14" s="8">
         <v>11</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="10">
         <v>4</v>
       </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="17" t="str">
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="17" t="str">
+      <c r="P14" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="16"/>
-      <c r="Y14" s="16"/>
-      <c r="Z14" s="16"/>
-      <c r="AA14" s="17" t="str">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="11"/>
+      <c r="X14" s="11"/>
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="11"/>
+      <c r="AA14" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB14" s="16"/>
-      <c r="AC14" s="16"/>
-      <c r="AD14" s="17" t="str">
+      <c r="AB14" s="11"/>
+      <c r="AC14" s="11"/>
+      <c r="AD14" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE14" s="18">
+      <c r="AE14" s="13">
         <v>1</v>
       </c>
-      <c r="AF14" s="19" t="str">
+      <c r="AF14" s="14">
         <f>IFERROR((IF(O14="",0,O14*Configuración!$B$4)+IF(R14="",0,R14*Configuración!$B$5)+IF(AA14="",0,AA14*Configuración!$B$6)+IF(AD14="",0,AD14*Configuración!$B$7))/(IF(O14="",0,Configuración!$B$4)+IF(R14="",0,Configuración!$B$5)+IF(AA14="",0,Configuración!$B$6)+IF(AD14="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG14" s="20" t="str">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AG14" s="15" t="str">
         <f>IF(AF14="","",IF(AE14&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF14&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="15" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21">
+      <c r="A15" s="16">
         <v>12</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="10">
         <v>1</v>
       </c>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="17" t="str">
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="17" t="str">
+      <c r="P15" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="16"/>
-      <c r="Z15" s="16"/>
-      <c r="AA15" s="17" t="str">
+        <v>4.7</v>
+      </c>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
+      <c r="Y15" s="11"/>
+      <c r="Z15" s="11"/>
+      <c r="AA15" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB15" s="16"/>
-      <c r="AC15" s="16"/>
-      <c r="AD15" s="17" t="str">
+      <c r="AB15" s="11"/>
+      <c r="AC15" s="11"/>
+      <c r="AD15" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE15" s="18">
+      <c r="AE15" s="13">
         <v>1</v>
       </c>
-      <c r="AF15" s="19" t="str">
+      <c r="AF15" s="14">
         <f>IFERROR((IF(O15="",0,O15*Configuración!$B$4)+IF(R15="",0,R15*Configuración!$B$5)+IF(AA15="",0,AA15*Configuración!$B$6)+IF(AD15="",0,AD15*Configuración!$B$7))/(IF(O15="",0,Configuración!$B$4)+IF(R15="",0,Configuración!$B$5)+IF(AA15="",0,Configuración!$B$6)+IF(AD15="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG15" s="20" t="str">
+        <v>4.7</v>
+      </c>
+      <c r="AG15" s="15" t="str">
         <f>IF(AF15="","",IF(AE15&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF15&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="16" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13">
+      <c r="A16" s="8">
         <v>13</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="15">
-        <v>4</v>
-      </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="17" t="str">
+      <c r="D16" s="10">
+        <v>9</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="17" t="str">
+      <c r="P16" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
-      <c r="Y16" s="16"/>
-      <c r="Z16" s="16"/>
-      <c r="AA16" s="17" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="11"/>
+      <c r="AA16" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB16" s="16"/>
-      <c r="AC16" s="16"/>
-      <c r="AD16" s="17" t="str">
+      <c r="AB16" s="11"/>
+      <c r="AC16" s="11"/>
+      <c r="AD16" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE16" s="18">
+      <c r="AE16" s="13">
         <v>1</v>
       </c>
-      <c r="AF16" s="19" t="str">
+      <c r="AF16" s="14">
         <f>IFERROR((IF(O16="",0,O16*Configuración!$B$4)+IF(R16="",0,R16*Configuración!$B$5)+IF(AA16="",0,AA16*Configuración!$B$6)+IF(AD16="",0,AD16*Configuración!$B$7))/(IF(O16="",0,Configuración!$B$4)+IF(R16="",0,Configuración!$B$5)+IF(AA16="",0,Configuración!$B$6)+IF(AD16="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG16" s="20" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="AG16" s="15" t="str">
         <f>IF(AF16="","",IF(AE16&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF16&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="17" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21">
+      <c r="A17" s="16">
         <v>14</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="10">
         <v>1</v>
       </c>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="17" t="str">
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="17" t="str">
+      <c r="P17" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="16"/>
-      <c r="Z17" s="16"/>
-      <c r="AA17" s="17" t="str">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="11"/>
+      <c r="W17" s="11"/>
+      <c r="X17" s="11"/>
+      <c r="Y17" s="11"/>
+      <c r="Z17" s="11"/>
+      <c r="AA17" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB17" s="16"/>
-      <c r="AC17" s="16"/>
-      <c r="AD17" s="17" t="str">
+      <c r="AB17" s="11"/>
+      <c r="AC17" s="11"/>
+      <c r="AD17" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE17" s="18">
+      <c r="AE17" s="13">
         <v>1</v>
       </c>
-      <c r="AF17" s="19" t="str">
+      <c r="AF17" s="14">
         <f>IFERROR((IF(O17="",0,O17*Configuración!$B$4)+IF(R17="",0,R17*Configuración!$B$5)+IF(AA17="",0,AA17*Configuración!$B$6)+IF(AD17="",0,AD17*Configuración!$B$7))/(IF(O17="",0,Configuración!$B$4)+IF(R17="",0,Configuración!$B$5)+IF(AA17="",0,Configuración!$B$6)+IF(AD17="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG17" s="20" t="str">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AG17" s="15" t="str">
         <f>IF(AF17="","",IF(AE17&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF17&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="18" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13">
+      <c r="A18" s="8">
         <v>15</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="10">
         <v>8</v>
       </c>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="17" t="str">
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="17" t="str">
+      <c r="P18" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="16"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
-      <c r="Y18" s="16"/>
-      <c r="Z18" s="16"/>
-      <c r="AA18" s="17" t="str">
+        <v>4.7</v>
+      </c>
+      <c r="S18" s="11"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
+      <c r="V18" s="11"/>
+      <c r="W18" s="11"/>
+      <c r="X18" s="11"/>
+      <c r="Y18" s="11"/>
+      <c r="Z18" s="11"/>
+      <c r="AA18" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB18" s="16"/>
-      <c r="AC18" s="16"/>
-      <c r="AD18" s="17" t="str">
+      <c r="AB18" s="11"/>
+      <c r="AC18" s="11"/>
+      <c r="AD18" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE18" s="18">
+      <c r="AE18" s="13">
         <v>1</v>
       </c>
-      <c r="AF18" s="19" t="str">
+      <c r="AF18" s="14">
         <f>IFERROR((IF(O18="",0,O18*Configuración!$B$4)+IF(R18="",0,R18*Configuración!$B$5)+IF(AA18="",0,AA18*Configuración!$B$6)+IF(AD18="",0,AD18*Configuración!$B$7))/(IF(O18="",0,Configuración!$B$4)+IF(R18="",0,Configuración!$B$5)+IF(AA18="",0,Configuración!$B$6)+IF(AD18="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG18" s="20" t="str">
+        <v>4.7</v>
+      </c>
+      <c r="AG18" s="15" t="str">
         <f>IF(AF18="","",IF(AE18&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF18&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="19" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="21">
+      <c r="A19" s="16">
         <v>16</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="10">
         <v>3</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="17" t="str">
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="17" t="str">
+      <c r="P19" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="16"/>
-      <c r="Y19" s="16"/>
-      <c r="Z19" s="16"/>
-      <c r="AA19" s="17" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="S19" s="11"/>
+      <c r="T19" s="11"/>
+      <c r="U19" s="11"/>
+      <c r="V19" s="11"/>
+      <c r="W19" s="11"/>
+      <c r="X19" s="11"/>
+      <c r="Y19" s="11"/>
+      <c r="Z19" s="11"/>
+      <c r="AA19" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB19" s="16"/>
-      <c r="AC19" s="16"/>
-      <c r="AD19" s="17" t="str">
+      <c r="AB19" s="11"/>
+      <c r="AC19" s="11"/>
+      <c r="AD19" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE19" s="18">
+      <c r="AE19" s="13">
         <v>1</v>
       </c>
-      <c r="AF19" s="19" t="str">
+      <c r="AF19" s="14">
         <f>IFERROR((IF(O19="",0,O19*Configuración!$B$4)+IF(R19="",0,R19*Configuración!$B$5)+IF(AA19="",0,AA19*Configuración!$B$6)+IF(AD19="",0,AD19*Configuración!$B$7))/(IF(O19="",0,Configuración!$B$4)+IF(R19="",0,Configuración!$B$5)+IF(AA19="",0,Configuración!$B$6)+IF(AD19="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG19" s="20" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="AG19" s="15" t="str">
         <f>IF(AF19="","",IF(AE19&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF19&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="20" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13">
+      <c r="A20" s="8">
         <v>17</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="10">
         <v>3</v>
       </c>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="17" t="str">
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="17" t="str">
+      <c r="P20" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S20" s="16"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="16"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="16"/>
-      <c r="Y20" s="16"/>
-      <c r="Z20" s="16"/>
-      <c r="AA20" s="17" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="S20" s="11"/>
+      <c r="T20" s="11"/>
+      <c r="U20" s="11"/>
+      <c r="V20" s="11"/>
+      <c r="W20" s="11"/>
+      <c r="X20" s="11"/>
+      <c r="Y20" s="11"/>
+      <c r="Z20" s="11"/>
+      <c r="AA20" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB20" s="16"/>
-      <c r="AC20" s="16"/>
-      <c r="AD20" s="17" t="str">
+      <c r="AB20" s="11"/>
+      <c r="AC20" s="11"/>
+      <c r="AD20" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE20" s="18">
+      <c r="AE20" s="13">
         <v>1</v>
       </c>
-      <c r="AF20" s="19" t="str">
+      <c r="AF20" s="14">
         <f>IFERROR((IF(O20="",0,O20*Configuración!$B$4)+IF(R20="",0,R20*Configuración!$B$5)+IF(AA20="",0,AA20*Configuración!$B$6)+IF(AD20="",0,AD20*Configuración!$B$7))/(IF(O20="",0,Configuración!$B$4)+IF(R20="",0,Configuración!$B$5)+IF(AA20="",0,Configuración!$B$6)+IF(AD20="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG20" s="20" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="AG20" s="15" t="str">
         <f>IF(AF20="","",IF(AE20&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF20&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="21" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="21">
+      <c r="A21" s="16">
         <v>18</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="10">
         <v>8</v>
       </c>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="17" t="str">
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="17" t="str">
+      <c r="P21" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S21" s="16"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="16"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
-      <c r="X21" s="16"/>
-      <c r="Y21" s="16"/>
-      <c r="Z21" s="16"/>
-      <c r="AA21" s="17" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="S21" s="11"/>
+      <c r="T21" s="11"/>
+      <c r="U21" s="11"/>
+      <c r="V21" s="11"/>
+      <c r="W21" s="11"/>
+      <c r="X21" s="11"/>
+      <c r="Y21" s="11"/>
+      <c r="Z21" s="11"/>
+      <c r="AA21" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB21" s="16"/>
-      <c r="AC21" s="16"/>
-      <c r="AD21" s="17" t="str">
+      <c r="AB21" s="11"/>
+      <c r="AC21" s="11"/>
+      <c r="AD21" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE21" s="18">
+      <c r="AE21" s="13">
         <v>1</v>
       </c>
-      <c r="AF21" s="19" t="str">
+      <c r="AF21" s="14">
         <f>IFERROR((IF(O21="",0,O21*Configuración!$B$4)+IF(R21="",0,R21*Configuración!$B$5)+IF(AA21="",0,AA21*Configuración!$B$6)+IF(AD21="",0,AD21*Configuración!$B$7))/(IF(O21="",0,Configuración!$B$4)+IF(R21="",0,Configuración!$B$5)+IF(AA21="",0,Configuración!$B$6)+IF(AD21="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG21" s="20" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="AG21" s="15" t="str">
         <f>IF(AF21="","",IF(AE21&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF21&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="22" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13">
+      <c r="A22" s="8">
         <v>19</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="10">
         <v>6</v>
       </c>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="17" t="str">
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="17" t="str">
+      <c r="P22" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S22" s="16"/>
-      <c r="T22" s="16"/>
-      <c r="U22" s="16"/>
-      <c r="V22" s="16"/>
-      <c r="W22" s="16"/>
-      <c r="X22" s="16"/>
-      <c r="Y22" s="16"/>
-      <c r="Z22" s="16"/>
-      <c r="AA22" s="17" t="str">
+        <v>4.2</v>
+      </c>
+      <c r="S22" s="11"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="11"/>
+      <c r="Y22" s="11"/>
+      <c r="Z22" s="11"/>
+      <c r="AA22" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB22" s="16"/>
-      <c r="AC22" s="16"/>
-      <c r="AD22" s="17" t="str">
+      <c r="AB22" s="11"/>
+      <c r="AC22" s="11"/>
+      <c r="AD22" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE22" s="18">
+      <c r="AE22" s="13">
         <v>1</v>
       </c>
-      <c r="AF22" s="19" t="str">
+      <c r="AF22" s="14">
         <f>IFERROR((IF(O22="",0,O22*Configuración!$B$4)+IF(R22="",0,R22*Configuración!$B$5)+IF(AA22="",0,AA22*Configuración!$B$6)+IF(AD22="",0,AD22*Configuración!$B$7))/(IF(O22="",0,Configuración!$B$4)+IF(R22="",0,Configuración!$B$5)+IF(AA22="",0,Configuración!$B$6)+IF(AD22="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG22" s="20" t="str">
+        <v>4.2</v>
+      </c>
+      <c r="AG22" s="15" t="str">
         <f>IF(AF22="","",IF(AE22&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF22&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="23" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="21">
+      <c r="A23" s="16">
         <v>20</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="10">
         <v>7</v>
       </c>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="17" t="str">
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="17" t="str">
+      <c r="P23" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S23" s="16"/>
-      <c r="T23" s="16"/>
-      <c r="U23" s="16"/>
-      <c r="V23" s="16"/>
-      <c r="W23" s="16"/>
-      <c r="X23" s="16"/>
-      <c r="Y23" s="16"/>
-      <c r="Z23" s="16"/>
-      <c r="AA23" s="17" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="S23" s="11"/>
+      <c r="T23" s="11"/>
+      <c r="U23" s="11"/>
+      <c r="V23" s="11"/>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+      <c r="Z23" s="11"/>
+      <c r="AA23" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB23" s="16"/>
-      <c r="AC23" s="16"/>
-      <c r="AD23" s="17" t="str">
+      <c r="AB23" s="11"/>
+      <c r="AC23" s="11"/>
+      <c r="AD23" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE23" s="18">
+      <c r="AE23" s="13">
         <v>1</v>
       </c>
-      <c r="AF23" s="19" t="str">
+      <c r="AF23" s="14">
         <f>IFERROR((IF(O23="",0,O23*Configuración!$B$4)+IF(R23="",0,R23*Configuración!$B$5)+IF(AA23="",0,AA23*Configuración!$B$6)+IF(AD23="",0,AD23*Configuración!$B$7))/(IF(O23="",0,Configuración!$B$4)+IF(R23="",0,Configuración!$B$5)+IF(AA23="",0,Configuración!$B$6)+IF(AD23="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG23" s="20" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="AG23" s="15" t="str">
         <f>IF(AF23="","",IF(AE23&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF23&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="24" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="13">
+      <c r="A24" s="8">
         <v>21</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="10">
         <v>2</v>
       </c>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="17" t="str">
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="17" t="str">
+      <c r="P24" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S24" s="16"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="16"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
-      <c r="X24" s="16"/>
-      <c r="Y24" s="16"/>
-      <c r="Z24" s="16"/>
-      <c r="AA24" s="17" t="str">
+        <v>4.2</v>
+      </c>
+      <c r="S24" s="11"/>
+      <c r="T24" s="11"/>
+      <c r="U24" s="11"/>
+      <c r="V24" s="11"/>
+      <c r="W24" s="11"/>
+      <c r="X24" s="11"/>
+      <c r="Y24" s="11"/>
+      <c r="Z24" s="11"/>
+      <c r="AA24" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB24" s="16"/>
-      <c r="AC24" s="16"/>
-      <c r="AD24" s="17" t="str">
+      <c r="AB24" s="11"/>
+      <c r="AC24" s="11"/>
+      <c r="AD24" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE24" s="18">
+      <c r="AE24" s="13">
         <v>1</v>
       </c>
-      <c r="AF24" s="19" t="str">
+      <c r="AF24" s="14">
         <f>IFERROR((IF(O24="",0,O24*Configuración!$B$4)+IF(R24="",0,R24*Configuración!$B$5)+IF(AA24="",0,AA24*Configuración!$B$6)+IF(AD24="",0,AD24*Configuración!$B$7))/(IF(O24="",0,Configuración!$B$4)+IF(R24="",0,Configuración!$B$5)+IF(AA24="",0,Configuración!$B$6)+IF(AD24="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG24" s="20" t="str">
+        <v>4.2</v>
+      </c>
+      <c r="AG24" s="15" t="str">
         <f>IF(AF24="","",IF(AE24&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF24&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="25" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="21">
+      <c r="A25" s="16">
         <v>22</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="D25" s="15">
-        <v>4</v>
-      </c>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="17" t="str">
+      <c r="D25" s="10">
+        <v>9</v>
+      </c>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="17" t="str">
+      <c r="P25" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S25" s="16"/>
-      <c r="T25" s="16"/>
-      <c r="U25" s="16"/>
-      <c r="V25" s="16"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
-      <c r="Y25" s="16"/>
-      <c r="Z25" s="16"/>
-      <c r="AA25" s="17" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="S25" s="11"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="11"/>
+      <c r="V25" s="11"/>
+      <c r="W25" s="11"/>
+      <c r="X25" s="11"/>
+      <c r="Y25" s="11"/>
+      <c r="Z25" s="11"/>
+      <c r="AA25" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB25" s="16"/>
-      <c r="AC25" s="16"/>
-      <c r="AD25" s="17" t="str">
+      <c r="AB25" s="11"/>
+      <c r="AC25" s="11"/>
+      <c r="AD25" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE25" s="18">
+      <c r="AE25" s="13">
         <v>1</v>
       </c>
-      <c r="AF25" s="19" t="str">
+      <c r="AF25" s="14">
         <f>IFERROR((IF(O25="",0,O25*Configuración!$B$4)+IF(R25="",0,R25*Configuración!$B$5)+IF(AA25="",0,AA25*Configuración!$B$6)+IF(AD25="",0,AD25*Configuración!$B$7))/(IF(O25="",0,Configuración!$B$4)+IF(R25="",0,Configuración!$B$5)+IF(AA25="",0,Configuración!$B$6)+IF(AD25="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG25" s="20" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="AG25" s="15" t="str">
         <f>IF(AF25="","",IF(AE25&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF25&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="26" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="13">
+      <c r="A26" s="8">
         <v>23</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="17" t="str">
+      <c r="D26" s="10"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="17" t="str">
+      <c r="P26" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S26" s="16"/>
-      <c r="T26" s="16"/>
-      <c r="U26" s="16"/>
-      <c r="V26" s="16"/>
-      <c r="W26" s="16"/>
-      <c r="X26" s="16"/>
-      <c r="Y26" s="16"/>
-      <c r="Z26" s="16"/>
-      <c r="AA26" s="17" t="str">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="S26" s="11"/>
+      <c r="T26" s="11"/>
+      <c r="U26" s="11"/>
+      <c r="V26" s="11"/>
+      <c r="W26" s="11"/>
+      <c r="X26" s="11"/>
+      <c r="Y26" s="11"/>
+      <c r="Z26" s="11"/>
+      <c r="AA26" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB26" s="16"/>
-      <c r="AC26" s="16"/>
-      <c r="AD26" s="17" t="str">
+      <c r="AB26" s="11"/>
+      <c r="AC26" s="11"/>
+      <c r="AD26" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE26" s="18">
+      <c r="AE26" s="13">
         <v>1</v>
       </c>
-      <c r="AF26" s="19" t="str">
+      <c r="AF26" s="14">
         <f>IFERROR((IF(O26="",0,O26*Configuración!$B$4)+IF(R26="",0,R26*Configuración!$B$5)+IF(AA26="",0,AA26*Configuración!$B$6)+IF(AD26="",0,AD26*Configuración!$B$7))/(IF(O26="",0,Configuración!$B$4)+IF(R26="",0,Configuración!$B$5)+IF(AA26="",0,Configuración!$B$6)+IF(AD26="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG26" s="20" t="str">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AG26" s="15" t="str">
         <f>IF(AF26="","",IF(AE26&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF26&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="27" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="21">
+      <c r="A27" s="16">
         <v>24</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="D27" s="15">
-        <v>4</v>
-      </c>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="17" t="str">
+      <c r="D27" s="10">
+        <v>9</v>
+      </c>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="17" t="str">
+      <c r="P27" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S27" s="16"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="16"/>
-      <c r="V27" s="16"/>
-      <c r="W27" s="16"/>
-      <c r="X27" s="16"/>
-      <c r="Y27" s="16"/>
-      <c r="Z27" s="16"/>
-      <c r="AA27" s="17" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="S27" s="11"/>
+      <c r="T27" s="11"/>
+      <c r="U27" s="11"/>
+      <c r="V27" s="11"/>
+      <c r="W27" s="11"/>
+      <c r="X27" s="11"/>
+      <c r="Y27" s="11"/>
+      <c r="Z27" s="11"/>
+      <c r="AA27" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB27" s="16"/>
-      <c r="AC27" s="16"/>
-      <c r="AD27" s="17" t="str">
+      <c r="AB27" s="11"/>
+      <c r="AC27" s="11"/>
+      <c r="AD27" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE27" s="18">
+      <c r="AE27" s="13">
         <v>1</v>
       </c>
-      <c r="AF27" s="19" t="str">
+      <c r="AF27" s="14">
         <f>IFERROR((IF(O27="",0,O27*Configuración!$B$4)+IF(R27="",0,R27*Configuración!$B$5)+IF(AA27="",0,AA27*Configuración!$B$6)+IF(AD27="",0,AD27*Configuración!$B$7))/(IF(O27="",0,Configuración!$B$4)+IF(R27="",0,Configuración!$B$5)+IF(AA27="",0,Configuración!$B$6)+IF(AD27="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG27" s="20" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="AG27" s="15" t="str">
         <f>IF(AF27="","",IF(AE27&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF27&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="28" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="13">
+      <c r="A28" s="8">
         <v>25</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="10">
         <v>1</v>
       </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="17" t="str">
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="17" t="str">
+      <c r="P28" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="Q28" s="11"/>
+      <c r="R28" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
-      <c r="Y28" s="16"/>
-      <c r="Z28" s="16"/>
-      <c r="AA28" s="17" t="str">
+        <v>4.2</v>
+      </c>
+      <c r="S28" s="11"/>
+      <c r="T28" s="11"/>
+      <c r="U28" s="11"/>
+      <c r="V28" s="11"/>
+      <c r="W28" s="11"/>
+      <c r="X28" s="11"/>
+      <c r="Y28" s="11"/>
+      <c r="Z28" s="11"/>
+      <c r="AA28" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB28" s="16"/>
-      <c r="AC28" s="16"/>
-      <c r="AD28" s="17" t="str">
+      <c r="AB28" s="11"/>
+      <c r="AC28" s="11"/>
+      <c r="AD28" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE28" s="18">
+      <c r="AE28" s="13">
         <v>1</v>
       </c>
-      <c r="AF28" s="19" t="str">
+      <c r="AF28" s="14">
         <f>IFERROR((IF(O28="",0,O28*Configuración!$B$4)+IF(R28="",0,R28*Configuración!$B$5)+IF(AA28="",0,AA28*Configuración!$B$6)+IF(AD28="",0,AD28*Configuración!$B$7))/(IF(O28="",0,Configuración!$B$4)+IF(R28="",0,Configuración!$B$5)+IF(AA28="",0,Configuración!$B$6)+IF(AD28="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG28" s="20" t="str">
+        <v>4.2</v>
+      </c>
+      <c r="AG28" s="15" t="str">
         <f>IF(AF28="","",IF(AE28&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF28&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="29" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="21">
+      <c r="A29" s="16">
         <v>26</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="10">
         <v>2</v>
       </c>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="17" t="str">
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P29" s="16"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="17" t="str">
+      <c r="P29" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S29" s="16"/>
-      <c r="T29" s="16"/>
-      <c r="U29" s="16"/>
-      <c r="V29" s="16"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
-      <c r="Y29" s="16"/>
-      <c r="Z29" s="16"/>
-      <c r="AA29" s="17" t="str">
+        <v>4.7</v>
+      </c>
+      <c r="S29" s="11"/>
+      <c r="T29" s="11"/>
+      <c r="U29" s="11"/>
+      <c r="V29" s="11"/>
+      <c r="W29" s="11"/>
+      <c r="X29" s="11"/>
+      <c r="Y29" s="11"/>
+      <c r="Z29" s="11"/>
+      <c r="AA29" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB29" s="16"/>
-      <c r="AC29" s="16"/>
-      <c r="AD29" s="17" t="str">
+      <c r="AB29" s="11"/>
+      <c r="AC29" s="11"/>
+      <c r="AD29" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE29" s="18">
+      <c r="AE29" s="13">
         <v>1</v>
       </c>
-      <c r="AF29" s="19" t="str">
+      <c r="AF29" s="14">
         <f>IFERROR((IF(O29="",0,O29*Configuración!$B$4)+IF(R29="",0,R29*Configuración!$B$5)+IF(AA29="",0,AA29*Configuración!$B$6)+IF(AD29="",0,AD29*Configuración!$B$7))/(IF(O29="",0,Configuración!$B$4)+IF(R29="",0,Configuración!$B$5)+IF(AA29="",0,Configuración!$B$6)+IF(AD29="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG29" s="20" t="str">
+        <v>4.7</v>
+      </c>
+      <c r="AG29" s="15" t="str">
         <f>IF(AF29="","",IF(AE29&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF29&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="30" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="13">
+      <c r="A30" s="8">
         <v>27</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="10">
         <v>5</v>
       </c>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="17" t="str">
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P30" s="16"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="17" t="str">
+      <c r="P30" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S30" s="16"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="16"/>
-      <c r="V30" s="16"/>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
-      <c r="Y30" s="16"/>
-      <c r="Z30" s="16"/>
-      <c r="AA30" s="17" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="S30" s="11"/>
+      <c r="T30" s="11"/>
+      <c r="U30" s="11"/>
+      <c r="V30" s="11"/>
+      <c r="W30" s="11"/>
+      <c r="X30" s="11"/>
+      <c r="Y30" s="11"/>
+      <c r="Z30" s="11"/>
+      <c r="AA30" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB30" s="16"/>
-      <c r="AC30" s="16"/>
-      <c r="AD30" s="17" t="str">
+      <c r="AB30" s="11"/>
+      <c r="AC30" s="11"/>
+      <c r="AD30" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE30" s="18">
+      <c r="AE30" s="13">
         <v>1</v>
       </c>
-      <c r="AF30" s="19" t="str">
+      <c r="AF30" s="14">
         <f>IFERROR((IF(O30="",0,O30*Configuración!$B$4)+IF(R30="",0,R30*Configuración!$B$5)+IF(AA30="",0,AA30*Configuración!$B$6)+IF(AD30="",0,AD30*Configuración!$B$7))/(IF(O30="",0,Configuración!$B$4)+IF(R30="",0,Configuración!$B$5)+IF(AA30="",0,Configuración!$B$6)+IF(AD30="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG30" s="20" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="AG30" s="15" t="str">
         <f>IF(AF30="","",IF(AE30&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF30&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="31" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="21">
+      <c r="A31" s="16">
         <v>28</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="C31" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="10">
         <v>6</v>
       </c>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="17" t="str">
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="17" t="str">
+      <c r="P31" s="11">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S31" s="16"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="16"/>
-      <c r="V31" s="16"/>
-      <c r="W31" s="16"/>
-      <c r="X31" s="16"/>
-      <c r="Y31" s="16"/>
-      <c r="Z31" s="16"/>
-      <c r="AA31" s="17" t="str">
+        <v>5</v>
+      </c>
+      <c r="S31" s="11"/>
+      <c r="T31" s="11"/>
+      <c r="U31" s="11"/>
+      <c r="V31" s="11"/>
+      <c r="W31" s="11"/>
+      <c r="X31" s="11"/>
+      <c r="Y31" s="11"/>
+      <c r="Z31" s="11"/>
+      <c r="AA31" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB31" s="16"/>
-      <c r="AC31" s="16"/>
-      <c r="AD31" s="17" t="str">
+      <c r="AB31" s="11"/>
+      <c r="AC31" s="11"/>
+      <c r="AD31" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE31" s="18">
+      <c r="AE31" s="13">
         <v>1</v>
       </c>
-      <c r="AF31" s="19" t="str">
+      <c r="AF31" s="14">
         <f>IFERROR((IF(O31="",0,O31*Configuración!$B$4)+IF(R31="",0,R31*Configuración!$B$5)+IF(AA31="",0,AA31*Configuración!$B$6)+IF(AD31="",0,AD31*Configuración!$B$7))/(IF(O31="",0,Configuración!$B$4)+IF(R31="",0,Configuración!$B$5)+IF(AA31="",0,Configuración!$B$6)+IF(AD31="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG31" s="20" t="str">
+        <v>5</v>
+      </c>
+      <c r="AG31" s="15" t="str">
         <f>IF(AF31="","",IF(AE31&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF31&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="32" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="13">
+      <c r="A32" s="8">
         <v>29</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="10">
         <v>3</v>
       </c>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="17" t="str">
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="16"/>
-      <c r="R32" s="17" t="str">
+      <c r="P32" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S32" s="16"/>
-      <c r="T32" s="16"/>
-      <c r="U32" s="16"/>
-      <c r="V32" s="16"/>
-      <c r="W32" s="16"/>
-      <c r="X32" s="16"/>
-      <c r="Y32" s="16"/>
-      <c r="Z32" s="16"/>
-      <c r="AA32" s="17" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="S32" s="11"/>
+      <c r="T32" s="11"/>
+      <c r="U32" s="11"/>
+      <c r="V32" s="11"/>
+      <c r="W32" s="11"/>
+      <c r="X32" s="11"/>
+      <c r="Y32" s="11"/>
+      <c r="Z32" s="11"/>
+      <c r="AA32" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB32" s="16"/>
-      <c r="AC32" s="16"/>
-      <c r="AD32" s="17" t="str">
+      <c r="AB32" s="11"/>
+      <c r="AC32" s="11"/>
+      <c r="AD32" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE32" s="18">
+      <c r="AE32" s="13">
         <v>1</v>
       </c>
-      <c r="AF32" s="19" t="str">
+      <c r="AF32" s="14">
         <f>IFERROR((IF(O32="",0,O32*Configuración!$B$4)+IF(R32="",0,R32*Configuración!$B$5)+IF(AA32="",0,AA32*Configuración!$B$6)+IF(AD32="",0,AD32*Configuración!$B$7))/(IF(O32="",0,Configuración!$B$4)+IF(R32="",0,Configuración!$B$5)+IF(AA32="",0,Configuración!$B$6)+IF(AD32="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG32" s="20" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="AG32" s="15" t="str">
         <f>IF(AF32="","",IF(AE32&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF32&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="33" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21">
+      <c r="A33" s="16">
         <v>30</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="10">
         <v>1</v>
       </c>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="16"/>
-      <c r="O33" s="17" t="str">
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="16"/>
-      <c r="R33" s="17" t="str">
+      <c r="P33" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="Q33" s="11"/>
+      <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S33" s="16"/>
-      <c r="T33" s="16"/>
-      <c r="U33" s="16"/>
-      <c r="V33" s="16"/>
-      <c r="W33" s="16"/>
-      <c r="X33" s="16"/>
-      <c r="Y33" s="16"/>
-      <c r="Z33" s="16"/>
-      <c r="AA33" s="17" t="str">
+        <v>4.7</v>
+      </c>
+      <c r="S33" s="11"/>
+      <c r="T33" s="11"/>
+      <c r="U33" s="11"/>
+      <c r="V33" s="11"/>
+      <c r="W33" s="11"/>
+      <c r="X33" s="11"/>
+      <c r="Y33" s="11"/>
+      <c r="Z33" s="11"/>
+      <c r="AA33" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AB33" s="16"/>
-      <c r="AC33" s="16"/>
-      <c r="AD33" s="17" t="str">
+      <c r="AB33" s="11"/>
+      <c r="AC33" s="11"/>
+      <c r="AD33" s="12" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE33" s="18">
+      <c r="AE33" s="13">
         <v>1</v>
       </c>
-      <c r="AF33" s="19" t="str">
+      <c r="AF33" s="14">
         <f>IFERROR((IF(O33="",0,O33*Configuración!$B$4)+IF(R33="",0,R33*Configuración!$B$5)+IF(AA33="",0,AA33*Configuración!$B$6)+IF(AD33="",0,AD33*Configuración!$B$7))/(IF(O33="",0,Configuración!$B$4)+IF(R33="",0,Configuración!$B$5)+IF(AA33="",0,Configuración!$B$6)+IF(AD33="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG33" s="20" t="str">
+        <v>4.7</v>
+      </c>
+      <c r="AG33" s="15" t="str">
         <f>IF(AF33="","",IF(AE33&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF33&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A34" s="21">
+      <c r="A34" s="16">
         <v>31</v>
       </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="16"/>
-      <c r="O34" s="17" t="str">
-        <f t="shared" ref="O34" si="4">IFERROR(AVERAGE(E34:N34),"")</f>
-        <v/>
-      </c>
-      <c r="P34" s="16"/>
-      <c r="Q34" s="16"/>
-      <c r="R34" s="17" t="str">
-        <f t="shared" ref="R34" si="5">IFERROR(AVERAGE(P34:Q34),"")</f>
-        <v/>
-      </c>
-      <c r="S34" s="16"/>
-      <c r="T34" s="16"/>
-      <c r="U34" s="16"/>
-      <c r="V34" s="16"/>
-      <c r="W34" s="16"/>
-      <c r="X34" s="16"/>
-      <c r="Y34" s="16"/>
-      <c r="Z34" s="16"/>
-      <c r="AA34" s="17" t="str">
-        <f t="shared" ref="AA34" si="6">IFERROR(AVERAGE(S34:Z34),"")</f>
-        <v/>
-      </c>
-      <c r="AB34" s="16"/>
-      <c r="AC34" s="16"/>
-      <c r="AD34" s="17" t="str">
-        <f t="shared" ref="AD34" si="7">IFERROR(AVERAGE(AB34:AC34),"")</f>
-        <v/>
-      </c>
-      <c r="AE34" s="18">
+      <c r="B34" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="C34" s="17"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="12"/>
+      <c r="P34" s="48">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="12">
+        <f>IFERROR(AVERAGE(P34:Q34),"")</f>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S34" s="11"/>
+      <c r="T34" s="11"/>
+      <c r="U34" s="11"/>
+      <c r="V34" s="11"/>
+      <c r="W34" s="11"/>
+      <c r="X34" s="11"/>
+      <c r="Y34" s="11"/>
+      <c r="Z34" s="11"/>
+      <c r="AA34" s="12" t="str">
+        <f t="shared" ref="AA34" si="4">IFERROR(AVERAGE(S34:Z34),"")</f>
+        <v/>
+      </c>
+      <c r="AB34" s="11"/>
+      <c r="AC34" s="11"/>
+      <c r="AD34" s="12" t="str">
+        <f t="shared" ref="AD34" si="5">IFERROR(AVERAGE(AB34:AC34),"")</f>
+        <v/>
+      </c>
+      <c r="AE34" s="13">
         <v>1</v>
       </c>
-      <c r="AF34" s="19" t="str">
+      <c r="AF34" s="14">
         <f>IFERROR((IF(O34="",0,O34*Configuración!$B$4)+IF(R34="",0,R34*Configuración!$B$5)+IF(AA34="",0,AA34*Configuración!$B$6)+IF(AD34="",0,AD34*Configuración!$B$7))/(IF(O34="",0,Configuración!$B$4)+IF(R34="",0,Configuración!$B$5)+IF(AA34="",0,Configuración!$B$6)+IF(AD34="",0,Configuración!$B$7)),"")</f>
-        <v/>
-      </c>
-      <c r="AG34" s="20" t="str">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AG34" s="15" t="str">
         <f>IF(AF34="","",IF(AE34&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF34&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A35" s="23"/>
-      <c r="B35" s="24" t="s">
+      <c r="A35" s="18"/>
+      <c r="B35" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="25" t="str">
-        <f t="shared" ref="E35:AF35" si="8">IFERROR(AVERAGE(E4:E33),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="G35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="H35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="I35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="L35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="M35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="N35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="P35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="R35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="S35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="T35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="U35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="V35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="W35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Y35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Z35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AA35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AB35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AC35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AD35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AE35" s="26">
-        <f t="shared" si="8"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="20" t="str">
+        <f t="shared" ref="E35:AF35" si="6">IFERROR(AVERAGE(E4:E33),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="G35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="H35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="J35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="L35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="N35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="O35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="P35" s="20">
+        <f>IFERROR(AVERAGE(P4:P34),"")</f>
+        <v>4.7032258064516119</v>
+      </c>
+      <c r="Q35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="R35" s="20">
+        <f t="shared" si="6"/>
+        <v>4.7066666666666661</v>
+      </c>
+      <c r="S35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="U35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="V35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="W35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="X35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="Y35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="Z35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AA35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AB35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AC35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AD35" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AE35" s="21">
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="AF35" s="25" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AG35" s="23" t="str">
+      <c r="AF35" s="20">
+        <f t="shared" si="6"/>
+        <v>4.7066666666666661</v>
+      </c>
+      <c r="AG35" s="18" t="str">
         <f>COUNTIF(AG4:AG33,"APROBADO")&amp;" aprob."</f>
-        <v>0 aprob.</v>
+        <v>30 aprob.</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="F36" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AG33" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A3:AG36" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:AG1"/>
     <mergeCell ref="A2:AG2"/>
@@ -4321,336 +4411,336 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="44"/>
+      <c r="D3" s="44" t="s">
         <v>144</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="23">
         <f>COUNTA(Notas!$B$4:$B$33)</f>
         <v>30</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="24" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="23">
         <f>COUNT(Notas!$AF$4:$AF$33)</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="30">
+        <v>30</v>
+      </c>
+      <c r="D5" s="25">
         <v>1</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="26">
         <f>COUNTIF(Notas!$D$4:$D$33,$D5)</f>
         <v>4</v>
       </c>
-      <c r="F5" s="32" t="str">
+      <c r="F5" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D5,Notas!$AF$4:$AF$33),"")</f>
-        <v/>
+        <v>4.625</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="B6" s="33" t="str">
+      <c r="B6" s="28">
         <f>IFERROR(AVERAGE(Notas!$AF$4:$AF$33),"")</f>
-        <v/>
-      </c>
-      <c r="D6" s="30">
+        <v>4.7066666666666661</v>
+      </c>
+      <c r="D6" s="25">
         <v>2</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="26">
         <f>COUNTIF(Notas!$D$4:$D$33,$D6)</f>
         <v>3</v>
       </c>
-      <c r="F6" s="32" t="str">
+      <c r="F6" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D6,Notas!$AF$4:$AF$33),"")</f>
-        <v/>
+        <v>4.6333333333333329</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="28">
         <f>IFERROR(MAX(Notas!$AF$4:$AF$33),"")</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="30">
+        <v>5</v>
+      </c>
+      <c r="D7" s="25">
         <v>3</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="26">
         <f>COUNTIF(Notas!$D$4:$D$33,$D7)</f>
         <v>3</v>
       </c>
-      <c r="F7" s="32" t="str">
+      <c r="F7" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D7,Notas!$AF$4:$AF$33),"")</f>
-        <v/>
+        <v>4.8</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="28">
         <f>IFERROR(MIN(Notas!$AF$4:$AF$33),"")</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="30">
+        <v>4.2</v>
+      </c>
+      <c r="D8" s="25">
         <v>4</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="26">
         <f>COUNTIF(Notas!$D$4:$D$33,$D8)</f>
-        <v>7</v>
-      </c>
-      <c r="F8" s="32" t="str">
+        <v>4</v>
+      </c>
+      <c r="F8" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D8,Notas!$AF$4:$AF$33),"")</f>
-        <v/>
+        <v>4.6999999999999993</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="B9" s="33" t="str">
+      <c r="B9" s="28">
         <f>IFERROR(STDEV(Notas!$AF$4:$AF$33),"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="30">
+        <v>0.24202213254923227</v>
+      </c>
+      <c r="D9" s="25">
         <v>5</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="26">
         <f>COUNTIF(Notas!$D$4:$D$33,$D9)</f>
         <v>3</v>
       </c>
-      <c r="F9" s="32" t="str">
+      <c r="F9" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D9,Notas!$AF$4:$AF$33),"")</f>
-        <v/>
+        <v>4.7</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="23">
         <f>COUNTIF(Notas!$AG$4:$AG$33,"APROBADO")</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="30">
+        <v>30</v>
+      </c>
+      <c r="D10" s="25">
         <v>6</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="26">
         <f>COUNTIF(Notas!$D$4:$D$33,$D10)</f>
         <v>3</v>
       </c>
-      <c r="F10" s="32" t="str">
+      <c r="F10" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D10,Notas!$AF$4:$AF$33),"")</f>
-        <v/>
+        <v>4.4666666666666668</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="23">
         <f>COUNTIF(Notas!$AG$4:$AG$33,"REPROBADO")</f>
         <v>0</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="25">
         <v>7</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="26">
         <f>COUNTIF(Notas!$D$4:$D$33,$D11)</f>
         <v>4</v>
       </c>
-      <c r="F11" s="32" t="str">
+      <c r="F11" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D11,Notas!$AF$4:$AF$33),"")</f>
-        <v/>
+        <v>4.8250000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="23">
         <f>COUNTIF(Notas!$AG$4:$AG$33,"FALLA ASIST.")</f>
         <v>0</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="25">
         <v>8</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="26">
         <f>COUNTIF(Notas!$D$4:$D$33,$D12)</f>
         <v>2</v>
       </c>
-      <c r="F12" s="32" t="str">
+      <c r="F12" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D12,Notas!$AF$4:$AF$33),"")</f>
-        <v/>
+        <v>4.75</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="B13" s="34" t="str">
+      <c r="B13" s="29">
         <f>IFERROR(COUNTIF(Notas!$AG$4:$AG$33,"APROBADO")/COUNT(Notas!$AF$4:$AF$33),"")</f>
-        <v/>
-      </c>
-      <c r="D13" s="30">
+        <v>1</v>
+      </c>
+      <c r="D13" s="25">
         <v>9</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="26">
         <f>COUNTIF(Notas!$D$4:$D$33,$D13)</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="32" t="str">
+        <v>3</v>
+      </c>
+      <c r="F13" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D13,Notas!$AF$4:$AF$33),"")</f>
-        <v/>
+        <v>4.8</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D14" s="30">
+      <c r="D14" s="25">
         <v>10</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="26">
         <f>COUNTIF(Notas!$D$4:$D$33,$D14)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="32" t="str">
+      <c r="F14" s="27" t="str">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D14,Notas!$AF$4:$AF$33),"")</f>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="44" t="s">
         <v>157</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="D16" s="4" t="s">
+      <c r="B16" s="44"/>
+      <c r="D16" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="B17" s="33" t="str">
+      <c r="B17" s="28" t="str">
         <f>IFERROR(AVERAGE(Notas!$O$4:$O$33),"")</f>
         <v/>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="D17" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="E17" s="29" t="s">
+      <c r="E17" s="24" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="B18" s="33" t="str">
+      <c r="B18" s="28">
         <f>IFERROR(AVERAGE(Notas!$R$4:$R$33),"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="35" t="s">
+        <v>4.7066666666666661</v>
+      </c>
+      <c r="D18" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="23">
         <f>COUNTIFS(Notas!$AF$4:$AF$33,"&gt;="&amp;0,Notas!$AF$4:$AF$33,"&lt;"&amp;2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="B19" s="33" t="str">
+      <c r="B19" s="28" t="str">
         <f>IFERROR(AVERAGE(Notas!$AA$4:$AA$33),"")</f>
         <v/>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="23">
         <f>COUNTIFS(Notas!$AF$4:$AF$33,"&gt;="&amp;2,Notas!$AF$4:$AF$33,"&lt;"&amp;3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="B20" s="33" t="str">
+      <c r="B20" s="28" t="str">
         <f>IFERROR(AVERAGE(Notas!$AD$4:$AD$33),"")</f>
         <v/>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="23">
         <f>COUNTIFS(Notas!$AF$4:$AF$33,"&gt;="&amp;3,Notas!$AF$4:$AF$33,"&lt;"&amp;3.5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="23">
         <f>COUNTIFS(Notas!$AF$4:$AF$33,"&gt;="&amp;3.5,Notas!$AF$4:$AF$33,"&lt;"&amp;4)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D22" s="35" t="s">
+      <c r="D22" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="23">
         <f>COUNTIFS(Notas!$AF$4:$AF$33,"&gt;="&amp;4,Notas!$AF$4:$AF$33,"&lt;"&amp;4.5)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D23" s="35" t="s">
+      <c r="D23" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="23">
         <f>COUNTIFS(Notas!$AF$4:$AF$33,"&gt;="&amp;4.5,Notas!$AF$4:$AF$33,"&lt;"&amp;5.01)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -4677,164 +4767,164 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="31" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="B4" s="37">
+      <c r="B4" s="32">
         <v>0.1</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="33" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="37">
+      <c r="B5" s="32">
         <v>0.1</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="33" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="32">
         <v>0.5</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="33" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="B7" s="37">
+      <c r="B7" s="32">
         <v>0.3</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="33" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="B8" s="40">
+      <c r="B8" s="35">
         <f>SUM(B4:B7)</f>
         <v>1</v>
       </c>
-      <c r="C8" s="41" t="str">
+      <c r="C8" s="36" t="str">
         <f>IF(B8=1,"Correcto","¡Los pesos no suman 100 %!")</f>
         <v>Correcto</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="B11" s="42">
+      <c r="B11" s="37">
         <v>3</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="33" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="32">
         <v>0.8</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="33" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="B15" s="43">
+      <c r="B15" s="38">
         <v>5</v>
       </c>
-      <c r="C15" s="44" t="s">
+      <c r="C15" s="39" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="B16" s="43">
+      <c r="B16" s="38">
         <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="B17" s="43">
+      <c r="B17" s="38">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="B18" s="43">
+      <c r="B18" s="38">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="B19" s="43">
+      <c r="B19" s="38">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="B20" s="43">
+      <c r="B20" s="38">
         <v>0</v>
       </c>
     </row>

--- a/Laboratorio_de_mecanica_y_ondas_para_biociencias_2026-2/Notas/Notas_Laboratorio_Biociencias_G4_2026-2.xlsx
+++ b/Laboratorio_de_mecanica_y_ondas_para_biociencias_2026-2/Notas/Notas_Laboratorio_Biociencias_G4_2026-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\miguel_perdomo\Auxiliar_docente_UNAL\Laboratorio_de_mecanica_y_ondas_para_biociencias_2026-2\Notas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FA444A-6378-4554-99F2-29B4B463AC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628BC378-8348-437F-B898-9ADA69FF62FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4245" yWindow="4245" windowWidth="21600" windowHeight="12645" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -1370,22 +1370,22 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1718,267 +1718,287 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
     </row>
     <row r="5" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
     </row>
     <row r="10" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
     </row>
     <row r="11" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
     </row>
     <row r="12" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
     </row>
     <row r="13" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
     </row>
     <row r="14" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
     </row>
     <row r="15" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="44" t="s">
+      <c r="A17" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
     </row>
     <row r="18" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
     </row>
     <row r="19" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
     </row>
     <row r="20" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
     </row>
     <row r="21" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
     </row>
     <row r="22" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
     </row>
     <row r="23" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="45" t="s">
+      <c r="B23" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
     </row>
     <row r="24" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="45" t="s">
+      <c r="B24" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="44" t="s">
+      <c r="A26" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="44"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
     </row>
     <row r="27" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
     </row>
     <row r="28" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="45" t="s">
+      <c r="B28" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
     </row>
     <row r="29" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="45" t="s">
+      <c r="B29" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
     </row>
     <row r="30" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="45" t="s">
+      <c r="B30" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
     </row>
     <row r="31" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="45" t="s">
+      <c r="B31" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B24:D24"/>
@@ -1986,26 +2006,6 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2035,78 +2035,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="46"/>
-      <c r="AB1" s="46"/>
-      <c r="AC1" s="46"/>
-      <c r="AD1" s="46"/>
-      <c r="AE1" s="46"/>
-      <c r="AF1" s="46"/>
-      <c r="AG1" s="46"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="47"/>
+      <c r="AC1" s="47"/>
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="47"/>
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="47"/>
     </row>
     <row r="2" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
-      <c r="W2" s="47"/>
-      <c r="X2" s="47"/>
-      <c r="Y2" s="47"/>
-      <c r="Z2" s="47"/>
-      <c r="AA2" s="47"/>
-      <c r="AB2" s="47"/>
-      <c r="AC2" s="47"/>
-      <c r="AD2" s="47"/>
-      <c r="AE2" s="47"/>
-      <c r="AF2" s="47"/>
-      <c r="AG2" s="47"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="48"/>
+      <c r="AB2" s="48"/>
+      <c r="AC2" s="48"/>
+      <c r="AD2" s="48"/>
+      <c r="AE2" s="48"/>
+      <c r="AF2" s="48"/>
+      <c r="AG2" s="48"/>
     </row>
     <row r="3" spans="1:33" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="40" t="s">
@@ -2239,10 +2239,12 @@
       <c r="P4" s="11">
         <v>4.9000000000000004</v>
       </c>
-      <c r="Q4" s="11"/>
+      <c r="Q4" s="11">
+        <v>5</v>
+      </c>
       <c r="R4" s="12">
         <f t="shared" ref="R4:R33" si="1">IFERROR(AVERAGE(P4:Q4),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.95</v>
       </c>
       <c r="S4" s="11"/>
       <c r="T4" s="11"/>
@@ -2267,7 +2269,7 @@
       </c>
       <c r="AF4" s="14">
         <f>IFERROR((IF(O4="",0,O4*Configuración!$B$4)+IF(R4="",0,R4*Configuración!$B$5)+IF(AA4="",0,AA4*Configuración!$B$6)+IF(AD4="",0,AD4*Configuración!$B$7))/(IF(O4="",0,Configuración!$B$4)+IF(R4="",0,Configuración!$B$5)+IF(AA4="",0,Configuración!$B$6)+IF(AD4="",0,Configuración!$B$7)),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.95</v>
       </c>
       <c r="AG4" s="15" t="str">
         <f>IF(AF4="","",IF(AE4&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF4&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2304,10 +2306,12 @@
       <c r="P5" s="11">
         <v>5</v>
       </c>
-      <c r="Q5" s="11"/>
+      <c r="Q5" s="11">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="R5" s="12">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="S5" s="11"/>
       <c r="T5" s="11"/>
@@ -2332,7 +2336,7 @@
       </c>
       <c r="AF5" s="14">
         <f>IFERROR((IF(O5="",0,O5*Configuración!$B$4)+IF(R5="",0,R5*Configuración!$B$5)+IF(AA5="",0,AA5*Configuración!$B$6)+IF(AD5="",0,AD5*Configuración!$B$7))/(IF(O5="",0,Configuración!$B$4)+IF(R5="",0,Configuración!$B$5)+IF(AA5="",0,Configuración!$B$6)+IF(AD5="",0,Configuración!$B$7)),"")</f>
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AG5" s="15" t="str">
         <f>IF(AF5="","",IF(AE5&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF5&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2369,10 +2373,12 @@
       <c r="P6" s="11">
         <v>4.8</v>
       </c>
-      <c r="Q6" s="11"/>
+      <c r="Q6" s="11">
+        <v>5</v>
+      </c>
       <c r="R6" s="12">
         <f t="shared" si="1"/>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="S6" s="11"/>
       <c r="T6" s="11"/>
@@ -2397,7 +2403,7 @@
       </c>
       <c r="AF6" s="14">
         <f>IFERROR((IF(O6="",0,O6*Configuración!$B$4)+IF(R6="",0,R6*Configuración!$B$5)+IF(AA6="",0,AA6*Configuración!$B$6)+IF(AD6="",0,AD6*Configuración!$B$7))/(IF(O6="",0,Configuración!$B$4)+IF(R6="",0,Configuración!$B$5)+IF(AA6="",0,Configuración!$B$6)+IF(AD6="",0,Configuración!$B$7)),"")</f>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AG6" s="15" t="str">
         <f>IF(AF6="","",IF(AE6&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF6&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2434,10 +2440,12 @@
       <c r="P7" s="11">
         <v>4.8</v>
       </c>
-      <c r="Q7" s="11"/>
+      <c r="Q7" s="11">
+        <v>5</v>
+      </c>
       <c r="R7" s="12">
         <f t="shared" si="1"/>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="S7" s="11"/>
       <c r="T7" s="11"/>
@@ -2462,7 +2470,7 @@
       </c>
       <c r="AF7" s="14">
         <f>IFERROR((IF(O7="",0,O7*Configuración!$B$4)+IF(R7="",0,R7*Configuración!$B$5)+IF(AA7="",0,AA7*Configuración!$B$6)+IF(AD7="",0,AD7*Configuración!$B$7))/(IF(O7="",0,Configuración!$B$4)+IF(R7="",0,Configuración!$B$5)+IF(AA7="",0,Configuración!$B$6)+IF(AD7="",0,Configuración!$B$7)),"")</f>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AG7" s="15" t="str">
         <f>IF(AF7="","",IF(AE7&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF7&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2499,10 +2507,12 @@
       <c r="P8" s="11">
         <v>4.8</v>
       </c>
-      <c r="Q8" s="11"/>
+      <c r="Q8" s="11">
+        <v>5</v>
+      </c>
       <c r="R8" s="12">
         <f t="shared" si="1"/>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="S8" s="11"/>
       <c r="T8" s="11"/>
@@ -2527,7 +2537,7 @@
       </c>
       <c r="AF8" s="14">
         <f>IFERROR((IF(O8="",0,O8*Configuración!$B$4)+IF(R8="",0,R8*Configuración!$B$5)+IF(AA8="",0,AA8*Configuración!$B$6)+IF(AD8="",0,AD8*Configuración!$B$7))/(IF(O8="",0,Configuración!$B$4)+IF(R8="",0,Configuración!$B$5)+IF(AA8="",0,Configuración!$B$6)+IF(AD8="",0,Configuración!$B$7)),"")</f>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AG8" s="15" t="str">
         <f>IF(AF8="","",IF(AE8&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF8&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2564,10 +2574,12 @@
       <c r="P9" s="11">
         <v>5</v>
       </c>
-      <c r="Q9" s="11"/>
+      <c r="Q9" s="11">
+        <v>4.7</v>
+      </c>
       <c r="R9" s="12">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="S9" s="11"/>
       <c r="T9" s="11"/>
@@ -2592,7 +2604,7 @@
       </c>
       <c r="AF9" s="14">
         <f>IFERROR((IF(O9="",0,O9*Configuración!$B$4)+IF(R9="",0,R9*Configuración!$B$5)+IF(AA9="",0,AA9*Configuración!$B$6)+IF(AD9="",0,AD9*Configuración!$B$7))/(IF(O9="",0,Configuración!$B$4)+IF(R9="",0,Configuración!$B$5)+IF(AA9="",0,Configuración!$B$6)+IF(AD9="",0,Configuración!$B$7)),"")</f>
-        <v>5</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="AG9" s="15" t="str">
         <f>IF(AF9="","",IF(AE9&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF9&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2629,10 +2641,12 @@
       <c r="P10" s="11">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Q10" s="11"/>
+      <c r="Q10" s="11">
+        <v>5</v>
+      </c>
       <c r="R10" s="12">
         <f t="shared" si="1"/>
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="S10" s="11"/>
       <c r="T10" s="11"/>
@@ -2657,7 +2671,7 @@
       </c>
       <c r="AF10" s="14">
         <f>IFERROR((IF(O10="",0,O10*Configuración!$B$4)+IF(R10="",0,R10*Configuración!$B$5)+IF(AA10="",0,AA10*Configuración!$B$6)+IF(AD10="",0,AD10*Configuración!$B$7))/(IF(O10="",0,Configuración!$B$4)+IF(R10="",0,Configuración!$B$5)+IF(AA10="",0,Configuración!$B$6)+IF(AD10="",0,Configuración!$B$7)),"")</f>
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="AG10" s="15" t="str">
         <f>IF(AF10="","",IF(AE10&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF10&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2692,12 +2706,14 @@
         <v/>
       </c>
       <c r="P11" s="11">
-        <v>4.2</v>
-      </c>
-      <c r="Q11" s="11"/>
+        <v>4.5</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>5</v>
+      </c>
       <c r="R11" s="12">
         <f t="shared" si="1"/>
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="S11" s="11"/>
       <c r="T11" s="11"/>
@@ -2722,7 +2738,7 @@
       </c>
       <c r="AF11" s="14">
         <f>IFERROR((IF(O11="",0,O11*Configuración!$B$4)+IF(R11="",0,R11*Configuración!$B$5)+IF(AA11="",0,AA11*Configuración!$B$6)+IF(AD11="",0,AD11*Configuración!$B$7))/(IF(O11="",0,Configuración!$B$4)+IF(R11="",0,Configuración!$B$5)+IF(AA11="",0,Configuración!$B$6)+IF(AD11="",0,Configuración!$B$7)),"")</f>
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AG11" s="15" t="str">
         <f>IF(AF11="","",IF(AE11&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF11&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2759,10 +2775,12 @@
       <c r="P12" s="11">
         <v>4.8</v>
       </c>
-      <c r="Q12" s="11"/>
+      <c r="Q12" s="11">
+        <v>5</v>
+      </c>
       <c r="R12" s="12">
         <f t="shared" si="1"/>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="S12" s="11"/>
       <c r="T12" s="11"/>
@@ -2787,7 +2805,7 @@
       </c>
       <c r="AF12" s="14">
         <f>IFERROR((IF(O12="",0,O12*Configuración!$B$4)+IF(R12="",0,R12*Configuración!$B$5)+IF(AA12="",0,AA12*Configuración!$B$6)+IF(AD12="",0,AD12*Configuración!$B$7))/(IF(O12="",0,Configuración!$B$4)+IF(R12="",0,Configuración!$B$5)+IF(AA12="",0,Configuración!$B$6)+IF(AD12="",0,Configuración!$B$7)),"")</f>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AG12" s="15" t="str">
         <f>IF(AF12="","",IF(AE12&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF12&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2824,10 +2842,12 @@
       <c r="P13" s="11">
         <v>4.3</v>
       </c>
-      <c r="Q13" s="11"/>
+      <c r="Q13" s="11">
+        <v>4.8</v>
+      </c>
       <c r="R13" s="12">
         <f t="shared" si="1"/>
-        <v>4.3</v>
+        <v>4.55</v>
       </c>
       <c r="S13" s="11"/>
       <c r="T13" s="11"/>
@@ -2852,7 +2872,7 @@
       </c>
       <c r="AF13" s="14">
         <f>IFERROR((IF(O13="",0,O13*Configuración!$B$4)+IF(R13="",0,R13*Configuración!$B$5)+IF(AA13="",0,AA13*Configuración!$B$6)+IF(AD13="",0,AD13*Configuración!$B$7))/(IF(O13="",0,Configuración!$B$4)+IF(R13="",0,Configuración!$B$5)+IF(AA13="",0,Configuración!$B$6)+IF(AD13="",0,Configuración!$B$7)),"")</f>
-        <v>4.3</v>
+        <v>4.55</v>
       </c>
       <c r="AG13" s="15" t="str">
         <f>IF(AF13="","",IF(AE13&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF13&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2889,10 +2909,12 @@
       <c r="P14" s="11">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Q14" s="11"/>
+      <c r="Q14" s="11">
+        <v>5</v>
+      </c>
       <c r="R14" s="12">
         <f t="shared" si="1"/>
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="S14" s="11"/>
       <c r="T14" s="11"/>
@@ -2917,7 +2939,7 @@
       </c>
       <c r="AF14" s="14">
         <f>IFERROR((IF(O14="",0,O14*Configuración!$B$4)+IF(R14="",0,R14*Configuración!$B$5)+IF(AA14="",0,AA14*Configuración!$B$6)+IF(AD14="",0,AD14*Configuración!$B$7))/(IF(O14="",0,Configuración!$B$4)+IF(R14="",0,Configuración!$B$5)+IF(AA14="",0,Configuración!$B$6)+IF(AD14="",0,Configuración!$B$7)),"")</f>
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="AG14" s="15" t="str">
         <f>IF(AF14="","",IF(AE14&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF14&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2954,10 +2976,12 @@
       <c r="P15" s="11">
         <v>4.7</v>
       </c>
-      <c r="Q15" s="11"/>
+      <c r="Q15" s="11">
+        <v>5</v>
+      </c>
       <c r="R15" s="12">
         <f t="shared" si="1"/>
-        <v>4.7</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="S15" s="11"/>
       <c r="T15" s="11"/>
@@ -2982,7 +3006,7 @@
       </c>
       <c r="AF15" s="14">
         <f>IFERROR((IF(O15="",0,O15*Configuración!$B$4)+IF(R15="",0,R15*Configuración!$B$5)+IF(AA15="",0,AA15*Configuración!$B$6)+IF(AD15="",0,AD15*Configuración!$B$7))/(IF(O15="",0,Configuración!$B$4)+IF(R15="",0,Configuración!$B$5)+IF(AA15="",0,Configuración!$B$6)+IF(AD15="",0,Configuración!$B$7)),"")</f>
-        <v>4.7</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="AG15" s="15" t="str">
         <f>IF(AF15="","",IF(AE15&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF15&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3019,10 +3043,12 @@
       <c r="P16" s="11">
         <v>4.8</v>
       </c>
-      <c r="Q16" s="11"/>
+      <c r="Q16" s="11">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="R16" s="12">
         <f t="shared" si="1"/>
-        <v>4.8</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="S16" s="11"/>
       <c r="T16" s="11"/>
@@ -3047,7 +3073,7 @@
       </c>
       <c r="AF16" s="14">
         <f>IFERROR((IF(O16="",0,O16*Configuración!$B$4)+IF(R16="",0,R16*Configuración!$B$5)+IF(AA16="",0,AA16*Configuración!$B$6)+IF(AD16="",0,AD16*Configuración!$B$7))/(IF(O16="",0,Configuración!$B$4)+IF(R16="",0,Configuración!$B$5)+IF(AA16="",0,Configuración!$B$6)+IF(AD16="",0,Configuración!$B$7)),"")</f>
-        <v>4.8</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="AG16" s="15" t="str">
         <f>IF(AF16="","",IF(AE16&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF16&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3084,10 +3110,12 @@
       <c r="P17" s="11">
         <v>4.9000000000000004</v>
       </c>
-      <c r="Q17" s="11"/>
+      <c r="Q17" s="11">
+        <v>5</v>
+      </c>
       <c r="R17" s="12">
         <f t="shared" si="1"/>
-        <v>4.9000000000000004</v>
+        <v>4.95</v>
       </c>
       <c r="S17" s="11"/>
       <c r="T17" s="11"/>
@@ -3112,7 +3140,7 @@
       </c>
       <c r="AF17" s="14">
         <f>IFERROR((IF(O17="",0,O17*Configuración!$B$4)+IF(R17="",0,R17*Configuración!$B$5)+IF(AA17="",0,AA17*Configuración!$B$6)+IF(AD17="",0,AD17*Configuración!$B$7))/(IF(O17="",0,Configuración!$B$4)+IF(R17="",0,Configuración!$B$5)+IF(AA17="",0,Configuración!$B$6)+IF(AD17="",0,Configuración!$B$7)),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.95</v>
       </c>
       <c r="AG17" s="15" t="str">
         <f>IF(AF17="","",IF(AE17&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF17&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3149,10 +3177,12 @@
       <c r="P18" s="11">
         <v>4.7</v>
       </c>
-      <c r="Q18" s="11"/>
+      <c r="Q18" s="11">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="R18" s="12">
         <f t="shared" si="1"/>
-        <v>4.7</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="S18" s="11"/>
       <c r="T18" s="11"/>
@@ -3177,7 +3207,7 @@
       </c>
       <c r="AF18" s="14">
         <f>IFERROR((IF(O18="",0,O18*Configuración!$B$4)+IF(R18="",0,R18*Configuración!$B$5)+IF(AA18="",0,AA18*Configuración!$B$6)+IF(AD18="",0,AD18*Configuración!$B$7))/(IF(O18="",0,Configuración!$B$4)+IF(R18="",0,Configuración!$B$5)+IF(AA18="",0,Configuración!$B$6)+IF(AD18="",0,Configuración!$B$7)),"")</f>
-        <v>4.7</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="AG18" s="15" t="str">
         <f>IF(AF18="","",IF(AE18&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF18&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3214,10 +3244,12 @@
       <c r="P19" s="11">
         <v>4.8</v>
       </c>
-      <c r="Q19" s="11"/>
+      <c r="Q19" s="11">
+        <v>5</v>
+      </c>
       <c r="R19" s="12">
         <f t="shared" si="1"/>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="S19" s="11"/>
       <c r="T19" s="11"/>
@@ -3242,7 +3274,7 @@
       </c>
       <c r="AF19" s="14">
         <f>IFERROR((IF(O19="",0,O19*Configuración!$B$4)+IF(R19="",0,R19*Configuración!$B$5)+IF(AA19="",0,AA19*Configuración!$B$6)+IF(AD19="",0,AD19*Configuración!$B$7))/(IF(O19="",0,Configuración!$B$4)+IF(R19="",0,Configuración!$B$5)+IF(AA19="",0,Configuración!$B$6)+IF(AD19="",0,Configuración!$B$7)),"")</f>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AG19" s="15" t="str">
         <f>IF(AF19="","",IF(AE19&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF19&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3279,10 +3311,12 @@
       <c r="P20" s="11">
         <v>4.8</v>
       </c>
-      <c r="Q20" s="11"/>
+      <c r="Q20" s="11">
+        <v>5</v>
+      </c>
       <c r="R20" s="12">
         <f t="shared" si="1"/>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="S20" s="11"/>
       <c r="T20" s="11"/>
@@ -3307,7 +3341,7 @@
       </c>
       <c r="AF20" s="14">
         <f>IFERROR((IF(O20="",0,O20*Configuración!$B$4)+IF(R20="",0,R20*Configuración!$B$5)+IF(AA20="",0,AA20*Configuración!$B$6)+IF(AD20="",0,AD20*Configuración!$B$7))/(IF(O20="",0,Configuración!$B$4)+IF(R20="",0,Configuración!$B$5)+IF(AA20="",0,Configuración!$B$6)+IF(AD20="",0,Configuración!$B$7)),"")</f>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AG20" s="15" t="str">
         <f>IF(AF20="","",IF(AE20&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF20&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3344,10 +3378,12 @@
       <c r="P21" s="11">
         <v>4.8</v>
       </c>
-      <c r="Q21" s="11"/>
+      <c r="Q21" s="11">
+        <v>5</v>
+      </c>
       <c r="R21" s="12">
         <f t="shared" si="1"/>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="S21" s="11"/>
       <c r="T21" s="11"/>
@@ -3372,7 +3408,7 @@
       </c>
       <c r="AF21" s="14">
         <f>IFERROR((IF(O21="",0,O21*Configuración!$B$4)+IF(R21="",0,R21*Configuración!$B$5)+IF(AA21="",0,AA21*Configuración!$B$6)+IF(AD21="",0,AD21*Configuración!$B$7))/(IF(O21="",0,Configuración!$B$4)+IF(R21="",0,Configuración!$B$5)+IF(AA21="",0,Configuración!$B$6)+IF(AD21="",0,Configuración!$B$7)),"")</f>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AG21" s="15" t="str">
         <f>IF(AF21="","",IF(AE21&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF21&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3407,12 +3443,14 @@
         <v/>
       </c>
       <c r="P22" s="11">
-        <v>4.2</v>
-      </c>
-      <c r="Q22" s="11"/>
+        <v>4.5</v>
+      </c>
+      <c r="Q22" s="11">
+        <v>5</v>
+      </c>
       <c r="R22" s="12">
         <f t="shared" si="1"/>
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="S22" s="11"/>
       <c r="T22" s="11"/>
@@ -3437,7 +3475,7 @@
       </c>
       <c r="AF22" s="14">
         <f>IFERROR((IF(O22="",0,O22*Configuración!$B$4)+IF(R22="",0,R22*Configuración!$B$5)+IF(AA22="",0,AA22*Configuración!$B$6)+IF(AD22="",0,AD22*Configuración!$B$7))/(IF(O22="",0,Configuración!$B$4)+IF(R22="",0,Configuración!$B$5)+IF(AA22="",0,Configuración!$B$6)+IF(AD22="",0,Configuración!$B$7)),"")</f>
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AG22" s="15" t="str">
         <f>IF(AF22="","",IF(AE22&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF22&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3474,10 +3512,12 @@
       <c r="P23" s="11">
         <v>4.8</v>
       </c>
-      <c r="Q23" s="11"/>
+      <c r="Q23" s="11">
+        <v>5</v>
+      </c>
       <c r="R23" s="12">
         <f t="shared" si="1"/>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="S23" s="11"/>
       <c r="T23" s="11"/>
@@ -3502,7 +3542,7 @@
       </c>
       <c r="AF23" s="14">
         <f>IFERROR((IF(O23="",0,O23*Configuración!$B$4)+IF(R23="",0,R23*Configuración!$B$5)+IF(AA23="",0,AA23*Configuración!$B$6)+IF(AD23="",0,AD23*Configuración!$B$7))/(IF(O23="",0,Configuración!$B$4)+IF(R23="",0,Configuración!$B$5)+IF(AA23="",0,Configuración!$B$6)+IF(AD23="",0,Configuración!$B$7)),"")</f>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AG23" s="15" t="str">
         <f>IF(AF23="","",IF(AE23&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF23&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3537,12 +3577,14 @@
         <v/>
       </c>
       <c r="P24" s="11">
-        <v>4.2</v>
-      </c>
-      <c r="Q24" s="11"/>
+        <v>4.5</v>
+      </c>
+      <c r="Q24" s="11">
+        <v>5</v>
+      </c>
       <c r="R24" s="12">
         <f t="shared" si="1"/>
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="S24" s="11"/>
       <c r="T24" s="11"/>
@@ -3567,7 +3609,7 @@
       </c>
       <c r="AF24" s="14">
         <f>IFERROR((IF(O24="",0,O24*Configuración!$B$4)+IF(R24="",0,R24*Configuración!$B$5)+IF(AA24="",0,AA24*Configuración!$B$6)+IF(AD24="",0,AD24*Configuración!$B$7))/(IF(O24="",0,Configuración!$B$4)+IF(R24="",0,Configuración!$B$5)+IF(AA24="",0,Configuración!$B$6)+IF(AD24="",0,Configuración!$B$7)),"")</f>
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AG24" s="15" t="str">
         <f>IF(AF24="","",IF(AE24&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF24&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3604,10 +3646,12 @@
       <c r="P25" s="11">
         <v>4.8</v>
       </c>
-      <c r="Q25" s="11"/>
+      <c r="Q25" s="41">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="R25" s="12">
         <f t="shared" si="1"/>
-        <v>4.8</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="S25" s="11"/>
       <c r="T25" s="11"/>
@@ -3632,7 +3676,7 @@
       </c>
       <c r="AF25" s="14">
         <f>IFERROR((IF(O25="",0,O25*Configuración!$B$4)+IF(R25="",0,R25*Configuración!$B$5)+IF(AA25="",0,AA25*Configuración!$B$6)+IF(AD25="",0,AD25*Configuración!$B$7))/(IF(O25="",0,Configuración!$B$4)+IF(R25="",0,Configuración!$B$5)+IF(AA25="",0,Configuración!$B$6)+IF(AD25="",0,Configuración!$B$7)),"")</f>
-        <v>4.8</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="AG25" s="15" t="str">
         <f>IF(AF25="","",IF(AE25&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF25&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3667,10 +3711,12 @@
       <c r="P26" s="11">
         <v>4.9000000000000004</v>
       </c>
-      <c r="Q26" s="11"/>
+      <c r="Q26" s="11">
+        <v>4</v>
+      </c>
       <c r="R26" s="12">
         <f t="shared" si="1"/>
-        <v>4.9000000000000004</v>
+        <v>4.45</v>
       </c>
       <c r="S26" s="11"/>
       <c r="T26" s="11"/>
@@ -3695,7 +3741,7 @@
       </c>
       <c r="AF26" s="14">
         <f>IFERROR((IF(O26="",0,O26*Configuración!$B$4)+IF(R26="",0,R26*Configuración!$B$5)+IF(AA26="",0,AA26*Configuración!$B$6)+IF(AD26="",0,AD26*Configuración!$B$7))/(IF(O26="",0,Configuración!$B$4)+IF(R26="",0,Configuración!$B$5)+IF(AA26="",0,Configuración!$B$6)+IF(AD26="",0,Configuración!$B$7)),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.45</v>
       </c>
       <c r="AG26" s="15" t="str">
         <f>IF(AF26="","",IF(AE26&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF26&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3726,16 +3772,18 @@
       <c r="M27" s="11"/>
       <c r="N27" s="11"/>
       <c r="O27" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f>IFERROR(AVERAGE(E27:N27),"")</f>
         <v/>
       </c>
       <c r="P27" s="11">
         <v>4.8</v>
       </c>
-      <c r="Q27" s="11"/>
+      <c r="Q27" s="11">
+        <v>5</v>
+      </c>
       <c r="R27" s="12">
         <f t="shared" si="1"/>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="S27" s="11"/>
       <c r="T27" s="11"/>
@@ -3760,7 +3808,7 @@
       </c>
       <c r="AF27" s="14">
         <f>IFERROR((IF(O27="",0,O27*Configuración!$B$4)+IF(R27="",0,R27*Configuración!$B$5)+IF(AA27="",0,AA27*Configuración!$B$6)+IF(AD27="",0,AD27*Configuración!$B$7))/(IF(O27="",0,Configuración!$B$4)+IF(R27="",0,Configuración!$B$5)+IF(AA27="",0,Configuración!$B$6)+IF(AD27="",0,Configuración!$B$7)),"")</f>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AG27" s="15" t="str">
         <f>IF(AF27="","",IF(AE27&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF27&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3795,12 +3843,14 @@
         <v/>
       </c>
       <c r="P28" s="11">
-        <v>4.2</v>
-      </c>
-      <c r="Q28" s="11"/>
+        <v>4.5</v>
+      </c>
+      <c r="Q28" s="11">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="R28" s="12">
         <f t="shared" si="1"/>
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="S28" s="11"/>
       <c r="T28" s="11"/>
@@ -3825,7 +3875,7 @@
       </c>
       <c r="AF28" s="14">
         <f>IFERROR((IF(O28="",0,O28*Configuración!$B$4)+IF(R28="",0,R28*Configuración!$B$5)+IF(AA28="",0,AA28*Configuración!$B$6)+IF(AD28="",0,AD28*Configuración!$B$7))/(IF(O28="",0,Configuración!$B$4)+IF(R28="",0,Configuración!$B$5)+IF(AA28="",0,Configuración!$B$6)+IF(AD28="",0,Configuración!$B$7)),"")</f>
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AG28" s="15" t="str">
         <f>IF(AF28="","",IF(AE28&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF28&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3862,10 +3912,12 @@
       <c r="P29" s="11">
         <v>4.7</v>
       </c>
-      <c r="Q29" s="11"/>
+      <c r="Q29" s="11">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="R29" s="12">
         <f t="shared" si="1"/>
-        <v>4.7</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="S29" s="11"/>
       <c r="T29" s="11"/>
@@ -3890,7 +3942,7 @@
       </c>
       <c r="AF29" s="14">
         <f>IFERROR((IF(O29="",0,O29*Configuración!$B$4)+IF(R29="",0,R29*Configuración!$B$5)+IF(AA29="",0,AA29*Configuración!$B$6)+IF(AD29="",0,AD29*Configuración!$B$7))/(IF(O29="",0,Configuración!$B$4)+IF(R29="",0,Configuración!$B$5)+IF(AA29="",0,Configuración!$B$6)+IF(AD29="",0,Configuración!$B$7)),"")</f>
-        <v>4.7</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="AG29" s="15" t="str">
         <f>IF(AF29="","",IF(AE29&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF29&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3927,10 +3979,12 @@
       <c r="P30" s="11">
         <v>4.8</v>
       </c>
-      <c r="Q30" s="11"/>
+      <c r="Q30" s="11">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="R30" s="12">
         <f t="shared" si="1"/>
-        <v>4.8</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="S30" s="11"/>
       <c r="T30" s="11"/>
@@ -3955,7 +4009,7 @@
       </c>
       <c r="AF30" s="14">
         <f>IFERROR((IF(O30="",0,O30*Configuración!$B$4)+IF(R30="",0,R30*Configuración!$B$5)+IF(AA30="",0,AA30*Configuración!$B$6)+IF(AD30="",0,AD30*Configuración!$B$7))/(IF(O30="",0,Configuración!$B$4)+IF(R30="",0,Configuración!$B$5)+IF(AA30="",0,Configuración!$B$6)+IF(AD30="",0,Configuración!$B$7)),"")</f>
-        <v>4.8</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="AG30" s="15" t="str">
         <f>IF(AF30="","",IF(AE30&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF30&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3992,10 +4046,12 @@
       <c r="P31" s="11">
         <v>5</v>
       </c>
-      <c r="Q31" s="11"/>
+      <c r="Q31" s="11">
+        <v>4.5</v>
+      </c>
       <c r="R31" s="12">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="S31" s="11"/>
       <c r="T31" s="11"/>
@@ -4020,7 +4076,7 @@
       </c>
       <c r="AF31" s="14">
         <f>IFERROR((IF(O31="",0,O31*Configuración!$B$4)+IF(R31="",0,R31*Configuración!$B$5)+IF(AA31="",0,AA31*Configuración!$B$6)+IF(AD31="",0,AD31*Configuración!$B$7))/(IF(O31="",0,Configuración!$B$4)+IF(R31="",0,Configuración!$B$5)+IF(AA31="",0,Configuración!$B$6)+IF(AD31="",0,Configuración!$B$7)),"")</f>
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AG31" s="15" t="str">
         <f>IF(AF31="","",IF(AE31&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF31&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -4057,10 +4113,12 @@
       <c r="P32" s="11">
         <v>4.8</v>
       </c>
-      <c r="Q32" s="11"/>
+      <c r="Q32" s="11">
+        <v>5</v>
+      </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="S32" s="11"/>
       <c r="T32" s="11"/>
@@ -4085,7 +4143,7 @@
       </c>
       <c r="AF32" s="14">
         <f>IFERROR((IF(O32="",0,O32*Configuración!$B$4)+IF(R32="",0,R32*Configuración!$B$5)+IF(AA32="",0,AA32*Configuración!$B$6)+IF(AD32="",0,AD32*Configuración!$B$7))/(IF(O32="",0,Configuración!$B$4)+IF(R32="",0,Configuración!$B$5)+IF(AA32="",0,Configuración!$B$6)+IF(AD32="",0,Configuración!$B$7)),"")</f>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AG32" s="15" t="str">
         <f>IF(AF32="","",IF(AE32&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF32&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -4122,10 +4180,12 @@
       <c r="P33" s="11">
         <v>4.7</v>
       </c>
-      <c r="Q33" s="11"/>
+      <c r="Q33" s="11">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>4.7</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="S33" s="11"/>
       <c r="T33" s="11"/>
@@ -4150,7 +4210,7 @@
       </c>
       <c r="AF33" s="14">
         <f>IFERROR((IF(O33="",0,O33*Configuración!$B$4)+IF(R33="",0,R33*Configuración!$B$5)+IF(AA33="",0,AA33*Configuración!$B$6)+IF(AD33="",0,AD33*Configuración!$B$7))/(IF(O33="",0,Configuración!$B$4)+IF(R33="",0,Configuración!$B$5)+IF(AA33="",0,Configuración!$B$6)+IF(AD33="",0,Configuración!$B$7)),"")</f>
-        <v>4.7</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="AG33" s="15" t="str">
         <f>IF(AF33="","",IF(AE33&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF33&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -4177,13 +4237,15 @@
       <c r="M34" s="11"/>
       <c r="N34" s="11"/>
       <c r="O34" s="12"/>
-      <c r="P34" s="48">
+      <c r="P34" s="43">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Q34" s="11"/>
+      <c r="Q34" s="11">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="R34" s="12">
         <f>IFERROR(AVERAGE(P34:Q34),"")</f>
-        <v>4.5999999999999996</v>
+        <v>4.75</v>
       </c>
       <c r="S34" s="11"/>
       <c r="T34" s="11"/>
@@ -4208,7 +4270,7 @@
       </c>
       <c r="AF34" s="14">
         <f>IFERROR((IF(O34="",0,O34*Configuración!$B$4)+IF(R34="",0,R34*Configuración!$B$5)+IF(AA34="",0,AA34*Configuración!$B$6)+IF(AD34="",0,AD34*Configuración!$B$7))/(IF(O34="",0,Configuración!$B$4)+IF(R34="",0,Configuración!$B$5)+IF(AA34="",0,Configuración!$B$6)+IF(AD34="",0,Configuración!$B$7)),"")</f>
-        <v>4.5999999999999996</v>
+        <v>4.75</v>
       </c>
       <c r="AG34" s="15" t="str">
         <f>IF(AF34="","",IF(AE34&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF34&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -4268,15 +4330,15 @@
       </c>
       <c r="P35" s="20">
         <f>IFERROR(AVERAGE(P4:P34),"")</f>
-        <v>4.7032258064516119</v>
-      </c>
-      <c r="Q35" s="20" t="str">
+        <v>4.7419354838709671</v>
+      </c>
+      <c r="Q35" s="20">
         <f t="shared" si="6"/>
-        <v/>
+        <v>4.9066666666666672</v>
       </c>
       <c r="R35" s="20">
         <f t="shared" si="6"/>
-        <v>4.7066666666666661</v>
+        <v>4.826666666666668</v>
       </c>
       <c r="S35" s="20" t="str">
         <f t="shared" si="6"/>
@@ -4332,7 +4394,7 @@
       </c>
       <c r="AF35" s="20">
         <f t="shared" si="6"/>
-        <v>4.7066666666666661</v>
+        <v>4.826666666666668</v>
       </c>
       <c r="AG35" s="18" t="str">
         <f>COUNTIF(AG4:AG33,"APROBADO")&amp;" aprob."</f>
@@ -4411,25 +4473,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="D3" s="44" t="s">
+      <c r="B3" s="45"/>
+      <c r="D3" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
@@ -4466,7 +4528,7 @@
       </c>
       <c r="F5" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D5,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.625</v>
+        <v>4.8250000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4475,7 +4537,7 @@
       </c>
       <c r="B6" s="28">
         <f>IFERROR(AVERAGE(Notas!$AF$4:$AF$33),"")</f>
-        <v>4.7066666666666661</v>
+        <v>4.826666666666668</v>
       </c>
       <c r="D6" s="25">
         <v>2</v>
@@ -4486,7 +4548,7 @@
       </c>
       <c r="F6" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D6,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.6333333333333329</v>
+        <v>4.833333333333333</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4495,7 +4557,7 @@
       </c>
       <c r="B7" s="28">
         <f>IFERROR(MAX(Notas!$AF$4:$AF$33),"")</f>
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="D7" s="25">
         <v>3</v>
@@ -4506,7 +4568,7 @@
       </c>
       <c r="F7" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D7,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4515,7 +4577,7 @@
       </c>
       <c r="B8" s="28">
         <f>IFERROR(MIN(Notas!$AF$4:$AF$33),"")</f>
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="D8" s="25">
         <v>4</v>
@@ -4526,7 +4588,7 @@
       </c>
       <c r="F8" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D8,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.6999999999999993</v>
+        <v>4.8500000000000005</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4535,7 +4597,7 @@
       </c>
       <c r="B9" s="28">
         <f>IFERROR(STDEV(Notas!$AF$4:$AF$33),"")</f>
-        <v>0.24202213254923227</v>
+        <v>0.11198316786489605</v>
       </c>
       <c r="D9" s="25">
         <v>5</v>
@@ -4546,7 +4608,7 @@
       </c>
       <c r="F9" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D9,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.7</v>
+        <v>4.7499999999999991</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4566,7 +4628,7 @@
       </c>
       <c r="F10" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D10,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.4666666666666668</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4586,7 +4648,7 @@
       </c>
       <c r="F11" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D11,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.8250000000000002</v>
+        <v>4.9125000000000005</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4606,7 +4668,7 @@
       </c>
       <c r="F12" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D12,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.75</v>
+        <v>4.8500000000000005</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4626,7 +4688,7 @@
       </c>
       <c r="F13" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D13,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.8</v>
+        <v>4.8666666666666663</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4643,15 +4705,15 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="D16" s="44" t="s">
+      <c r="B16" s="45"/>
+      <c r="D16" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
@@ -4674,7 +4736,7 @@
       </c>
       <c r="B18" s="28">
         <f>IFERROR(AVERAGE(Notas!$R$4:$R$33),"")</f>
-        <v>4.7066666666666661</v>
+        <v>4.826666666666668</v>
       </c>
       <c r="D18" s="30" t="s">
         <v>163</v>
@@ -4731,7 +4793,7 @@
       </c>
       <c r="E22" s="23">
         <f>COUNTIFS(Notas!$AF$4:$AF$33,"&gt;="&amp;4,Notas!$AF$4:$AF$33,"&lt;"&amp;4.5)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -4740,7 +4802,7 @@
       </c>
       <c r="E23" s="23">
         <f>COUNTIFS(Notas!$AF$4:$AF$33,"&gt;="&amp;4.5,Notas!$AF$4:$AF$33,"&lt;"&amp;5.01)</f>
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -4767,11 +4829,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="46" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="31" t="s">
@@ -4842,11 +4904,11 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="45" t="s">
         <v>184</v>
       </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="44"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
@@ -4871,11 +4933,11 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">

--- a/Laboratorio_de_mecanica_y_ondas_para_biociencias_2026-2/Notas/Notas_Laboratorio_Biociencias_G4_2026-2.xlsx
+++ b/Laboratorio_de_mecanica_y_ondas_para_biociencias_2026-2/Notas/Notas_Laboratorio_Biociencias_G4_2026-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\miguel_perdomo\Auxiliar_docente_UNAL\Laboratorio_de_mecanica_y_ondas_para_biociencias_2026-2\Notas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628BC378-8348-437F-B898-9ADA69FF62FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0F3E19-BE55-46CF-B199-DA09EF657588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4245" yWindow="4245" windowWidth="21600" windowHeight="12645" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="52680" yWindow="-1965" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -2222,7 +2222,9 @@
       <c r="D4" s="10">
         <v>7</v>
       </c>
-      <c r="E4" s="11"/>
+      <c r="E4" s="11">
+        <v>4</v>
+      </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
@@ -2232,9 +2234,9 @@
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
-      <c r="O4" s="12" t="str">
-        <f t="shared" ref="O4:O33" si="0">IFERROR(AVERAGE(E4:N4),"")</f>
-        <v/>
+      <c r="O4" s="12">
+        <f t="shared" ref="O4:O32" si="0">IFERROR(AVERAGE(E4:N4),"")</f>
+        <v>4</v>
       </c>
       <c r="P4" s="11">
         <v>4.9000000000000004</v>
@@ -2269,7 +2271,7 @@
       </c>
       <c r="AF4" s="14">
         <f>IFERROR((IF(O4="",0,O4*Configuración!$B$4)+IF(R4="",0,R4*Configuración!$B$5)+IF(AA4="",0,AA4*Configuración!$B$6)+IF(AD4="",0,AD4*Configuración!$B$7))/(IF(O4="",0,Configuración!$B$4)+IF(R4="",0,Configuración!$B$5)+IF(AA4="",0,Configuración!$B$6)+IF(AD4="",0,Configuración!$B$7)),"")</f>
-        <v>4.95</v>
+        <v>4.4749999999999996</v>
       </c>
       <c r="AG4" s="15" t="str">
         <f>IF(AF4="","",IF(AE4&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF4&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2289,8 +2291,12 @@
       <c r="D5" s="10">
         <v>2</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
+      <c r="E5" s="11">
+        <v>5</v>
+      </c>
+      <c r="F5" s="11">
+        <v>5</v>
+      </c>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
@@ -2299,9 +2305,9 @@
       <c r="L5" s="11"/>
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
-      <c r="O5" s="12" t="str">
+      <c r="O5" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P5" s="11">
         <v>5</v>
@@ -2336,7 +2342,7 @@
       </c>
       <c r="AF5" s="14">
         <f>IFERROR((IF(O5="",0,O5*Configuración!$B$4)+IF(R5="",0,R5*Configuración!$B$5)+IF(AA5="",0,AA5*Configuración!$B$6)+IF(AD5="",0,AD5*Configuración!$B$7))/(IF(O5="",0,Configuración!$B$4)+IF(R5="",0,Configuración!$B$5)+IF(AA5="",0,Configuración!$B$6)+IF(AD5="",0,Configuración!$B$7)),"")</f>
-        <v>4.95</v>
+        <v>4.9750000000000005</v>
       </c>
       <c r="AG5" s="15" t="str">
         <f>IF(AF5="","",IF(AE5&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF5&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2356,7 +2362,9 @@
       <c r="D6" s="10">
         <v>7</v>
       </c>
-      <c r="E6" s="11"/>
+      <c r="E6" s="11">
+        <v>5</v>
+      </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
@@ -2366,9 +2374,9 @@
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
-      <c r="O6" s="12" t="str">
+      <c r="O6" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P6" s="11">
         <v>4.8</v>
@@ -2403,7 +2411,7 @@
       </c>
       <c r="AF6" s="14">
         <f>IFERROR((IF(O6="",0,O6*Configuración!$B$4)+IF(R6="",0,R6*Configuración!$B$5)+IF(AA6="",0,AA6*Configuración!$B$6)+IF(AD6="",0,AD6*Configuración!$B$7))/(IF(O6="",0,Configuración!$B$4)+IF(R6="",0,Configuración!$B$5)+IF(AA6="",0,Configuración!$B$6)+IF(AD6="",0,Configuración!$B$7)),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="AG6" s="15" t="str">
         <f>IF(AF6="","",IF(AE6&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF6&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2423,7 +2431,9 @@
       <c r="D7" s="10">
         <v>4</v>
       </c>
-      <c r="E7" s="11"/>
+      <c r="E7" s="11">
+        <v>3.8</v>
+      </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
@@ -2433,9 +2443,9 @@
       <c r="L7" s="11"/>
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
-      <c r="O7" s="12" t="str">
+      <c r="O7" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.8</v>
       </c>
       <c r="P7" s="11">
         <v>4.8</v>
@@ -2470,7 +2480,7 @@
       </c>
       <c r="AF7" s="14">
         <f>IFERROR((IF(O7="",0,O7*Configuración!$B$4)+IF(R7="",0,R7*Configuración!$B$5)+IF(AA7="",0,AA7*Configuración!$B$6)+IF(AD7="",0,AD7*Configuración!$B$7))/(IF(O7="",0,Configuración!$B$4)+IF(R7="",0,Configuración!$B$5)+IF(AA7="",0,Configuración!$B$6)+IF(AD7="",0,Configuración!$B$7)),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.3500000000000005</v>
       </c>
       <c r="AG7" s="15" t="str">
         <f>IF(AF7="","",IF(AE7&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF7&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2490,7 +2500,9 @@
       <c r="D8" s="10">
         <v>4</v>
       </c>
-      <c r="E8" s="11"/>
+      <c r="E8" s="11">
+        <v>5</v>
+      </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
@@ -2500,9 +2512,9 @@
       <c r="L8" s="11"/>
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
-      <c r="O8" s="12" t="str">
+      <c r="O8" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P8" s="11">
         <v>4.8</v>
@@ -2537,7 +2549,7 @@
       </c>
       <c r="AF8" s="14">
         <f>IFERROR((IF(O8="",0,O8*Configuración!$B$4)+IF(R8="",0,R8*Configuración!$B$5)+IF(AA8="",0,AA8*Configuración!$B$6)+IF(AD8="",0,AD8*Configuración!$B$7))/(IF(O8="",0,Configuración!$B$4)+IF(R8="",0,Configuración!$B$5)+IF(AA8="",0,Configuración!$B$6)+IF(AD8="",0,Configuración!$B$7)),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="AG8" s="15" t="str">
         <f>IF(AF8="","",IF(AE8&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF8&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2557,8 +2569,12 @@
       <c r="D9" s="10">
         <v>5</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
+      <c r="E9" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="F9" s="11">
+        <v>5</v>
+      </c>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
@@ -2567,9 +2583,9 @@
       <c r="L9" s="11"/>
       <c r="M9" s="11"/>
       <c r="N9" s="11"/>
-      <c r="O9" s="12" t="str">
+      <c r="O9" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4.6500000000000004</v>
       </c>
       <c r="P9" s="11">
         <v>5</v>
@@ -2604,7 +2620,7 @@
       </c>
       <c r="AF9" s="14">
         <f>IFERROR((IF(O9="",0,O9*Configuración!$B$4)+IF(R9="",0,R9*Configuración!$B$5)+IF(AA9="",0,AA9*Configuración!$B$6)+IF(AD9="",0,AD9*Configuración!$B$7))/(IF(O9="",0,Configuración!$B$4)+IF(R9="",0,Configuración!$B$5)+IF(AA9="",0,Configuración!$B$6)+IF(AD9="",0,Configuración!$B$7)),"")</f>
-        <v>4.8499999999999996</v>
+        <v>4.75</v>
       </c>
       <c r="AG9" s="15" t="str">
         <f>IF(AF9="","",IF(AE9&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF9&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2624,7 +2640,9 @@
       <c r="D10" s="10">
         <v>4</v>
       </c>
-      <c r="E10" s="11"/>
+      <c r="E10" s="11">
+        <v>2.8</v>
+      </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
@@ -2634,9 +2652,9 @@
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
       <c r="N10" s="41"/>
-      <c r="O10" s="12" t="str">
+      <c r="O10" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.8</v>
       </c>
       <c r="P10" s="11">
         <v>4.5999999999999996</v>
@@ -2671,7 +2689,7 @@
       </c>
       <c r="AF10" s="14">
         <f>IFERROR((IF(O10="",0,O10*Configuración!$B$4)+IF(R10="",0,R10*Configuración!$B$5)+IF(AA10="",0,AA10*Configuración!$B$6)+IF(AD10="",0,AD10*Configuración!$B$7))/(IF(O10="",0,Configuración!$B$4)+IF(R10="",0,Configuración!$B$5)+IF(AA10="",0,Configuración!$B$6)+IF(AD10="",0,Configuración!$B$7)),"")</f>
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AG10" s="15" t="str">
         <f>IF(AF10="","",IF(AE10&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF10&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2691,7 +2709,9 @@
       <c r="D11" s="10">
         <v>6</v>
       </c>
-      <c r="E11" s="11"/>
+      <c r="E11" s="11">
+        <v>4.5</v>
+      </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
@@ -2701,9 +2721,9 @@
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
       <c r="N11" s="11"/>
-      <c r="O11" s="12" t="str">
+      <c r="O11" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4.5</v>
       </c>
       <c r="P11" s="11">
         <v>4.5</v>
@@ -2738,7 +2758,7 @@
       </c>
       <c r="AF11" s="14">
         <f>IFERROR((IF(O11="",0,O11*Configuración!$B$4)+IF(R11="",0,R11*Configuración!$B$5)+IF(AA11="",0,AA11*Configuración!$B$6)+IF(AD11="",0,AD11*Configuración!$B$7))/(IF(O11="",0,Configuración!$B$4)+IF(R11="",0,Configuración!$B$5)+IF(AA11="",0,Configuración!$B$6)+IF(AD11="",0,Configuración!$B$7)),"")</f>
-        <v>4.75</v>
+        <v>4.625</v>
       </c>
       <c r="AG11" s="15" t="str">
         <f>IF(AF11="","",IF(AE11&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF11&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2758,19 +2778,21 @@
       <c r="D12" s="10">
         <v>7</v>
       </c>
-      <c r="E12" s="11"/>
+      <c r="E12" s="11">
+        <v>4</v>
+      </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
+      <c r="J12" s="43"/>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
       <c r="N12" s="11"/>
-      <c r="O12" s="12" t="str">
+      <c r="O12" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="P12" s="11">
         <v>4.8</v>
@@ -2805,7 +2827,7 @@
       </c>
       <c r="AF12" s="14">
         <f>IFERROR((IF(O12="",0,O12*Configuración!$B$4)+IF(R12="",0,R12*Configuración!$B$5)+IF(AA12="",0,AA12*Configuración!$B$6)+IF(AD12="",0,AD12*Configuración!$B$7))/(IF(O12="",0,Configuración!$B$4)+IF(R12="",0,Configuración!$B$5)+IF(AA12="",0,Configuración!$B$6)+IF(AD12="",0,Configuración!$B$7)),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.45</v>
       </c>
       <c r="AG12" s="15" t="str">
         <f>IF(AF12="","",IF(AE12&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF12&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2825,8 +2847,12 @@
       <c r="D13" s="10">
         <v>5</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
+      <c r="E13" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="F13" s="11">
+        <v>5</v>
+      </c>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
@@ -2835,9 +2861,9 @@
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
       <c r="N13" s="11"/>
-      <c r="O13" s="12" t="str">
+      <c r="O13" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4.6500000000000004</v>
       </c>
       <c r="P13" s="11">
         <v>4.3</v>
@@ -2872,7 +2898,7 @@
       </c>
       <c r="AF13" s="14">
         <f>IFERROR((IF(O13="",0,O13*Configuración!$B$4)+IF(R13="",0,R13*Configuración!$B$5)+IF(AA13="",0,AA13*Configuración!$B$6)+IF(AD13="",0,AD13*Configuración!$B$7))/(IF(O13="",0,Configuración!$B$4)+IF(R13="",0,Configuración!$B$5)+IF(AA13="",0,Configuración!$B$6)+IF(AD13="",0,Configuración!$B$7)),"")</f>
-        <v>4.55</v>
+        <v>4.6000000000000005</v>
       </c>
       <c r="AG13" s="15" t="str">
         <f>IF(AF13="","",IF(AE13&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF13&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2892,7 +2918,9 @@
       <c r="D14" s="10">
         <v>4</v>
       </c>
-      <c r="E14" s="11"/>
+      <c r="E14" s="11">
+        <v>5</v>
+      </c>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
@@ -2902,9 +2930,9 @@
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
-      <c r="O14" s="12" t="str">
+      <c r="O14" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P14" s="11">
         <v>4.5999999999999996</v>
@@ -2939,7 +2967,7 @@
       </c>
       <c r="AF14" s="14">
         <f>IFERROR((IF(O14="",0,O14*Configuración!$B$4)+IF(R14="",0,R14*Configuración!$B$5)+IF(AA14="",0,AA14*Configuración!$B$6)+IF(AD14="",0,AD14*Configuración!$B$7))/(IF(O14="",0,Configuración!$B$4)+IF(R14="",0,Configuración!$B$5)+IF(AA14="",0,Configuración!$B$6)+IF(AD14="",0,Configuración!$B$7)),"")</f>
-        <v>4.8</v>
+        <v>4.8999999999999995</v>
       </c>
       <c r="AG14" s="15" t="str">
         <f>IF(AF14="","",IF(AE14&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF14&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2959,8 +2987,12 @@
       <c r="D15" s="10">
         <v>1</v>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="E15" s="11">
+        <v>4</v>
+      </c>
+      <c r="F15" s="11">
+        <v>4.7</v>
+      </c>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
@@ -2969,9 +3001,9 @@
       <c r="L15" s="11"/>
       <c r="M15" s="11"/>
       <c r="N15" s="11"/>
-      <c r="O15" s="12" t="str">
+      <c r="O15" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4.3499999999999996</v>
       </c>
       <c r="P15" s="11">
         <v>4.7</v>
@@ -3006,7 +3038,7 @@
       </c>
       <c r="AF15" s="14">
         <f>IFERROR((IF(O15="",0,O15*Configuración!$B$4)+IF(R15="",0,R15*Configuración!$B$5)+IF(AA15="",0,AA15*Configuración!$B$6)+IF(AD15="",0,AD15*Configuración!$B$7))/(IF(O15="",0,Configuración!$B$4)+IF(R15="",0,Configuración!$B$5)+IF(AA15="",0,Configuración!$B$6)+IF(AD15="",0,Configuración!$B$7)),"")</f>
-        <v>4.8499999999999996</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AG15" s="15" t="str">
         <f>IF(AF15="","",IF(AE15&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF15&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3026,7 +3058,9 @@
       <c r="D16" s="10">
         <v>9</v>
       </c>
-      <c r="E16" s="11"/>
+      <c r="E16" s="11">
+        <v>5</v>
+      </c>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
@@ -3036,9 +3070,9 @@
       <c r="L16" s="11"/>
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
-      <c r="O16" s="12" t="str">
+      <c r="O16" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P16" s="11">
         <v>4.8</v>
@@ -3073,7 +3107,7 @@
       </c>
       <c r="AF16" s="14">
         <f>IFERROR((IF(O16="",0,O16*Configuración!$B$4)+IF(R16="",0,R16*Configuración!$B$5)+IF(AA16="",0,AA16*Configuración!$B$6)+IF(AD16="",0,AD16*Configuración!$B$7))/(IF(O16="",0,Configuración!$B$4)+IF(R16="",0,Configuración!$B$5)+IF(AA16="",0,Configuración!$B$6)+IF(AD16="",0,Configuración!$B$7)),"")</f>
-        <v>4.8499999999999996</v>
+        <v>4.9249999999999998</v>
       </c>
       <c r="AG16" s="15" t="str">
         <f>IF(AF16="","",IF(AE16&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF16&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3093,8 +3127,12 @@
       <c r="D17" s="10">
         <v>1</v>
       </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+      <c r="E17" s="11">
+        <v>4</v>
+      </c>
+      <c r="F17" s="11">
+        <v>5</v>
+      </c>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -3103,9 +3141,9 @@
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
-      <c r="O17" s="12" t="str">
+      <c r="O17" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4.5</v>
       </c>
       <c r="P17" s="11">
         <v>4.9000000000000004</v>
@@ -3124,7 +3162,7 @@
       <c r="W17" s="11"/>
       <c r="X17" s="11"/>
       <c r="Y17" s="11"/>
-      <c r="Z17" s="11"/>
+      <c r="Z17" s="41"/>
       <c r="AA17" s="12" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -3140,7 +3178,7 @@
       </c>
       <c r="AF17" s="14">
         <f>IFERROR((IF(O17="",0,O17*Configuración!$B$4)+IF(R17="",0,R17*Configuración!$B$5)+IF(AA17="",0,AA17*Configuración!$B$6)+IF(AD17="",0,AD17*Configuración!$B$7))/(IF(O17="",0,Configuración!$B$4)+IF(R17="",0,Configuración!$B$5)+IF(AA17="",0,Configuración!$B$6)+IF(AD17="",0,Configuración!$B$7)),"")</f>
-        <v>4.95</v>
+        <v>4.7249999999999996</v>
       </c>
       <c r="AG17" s="15" t="str">
         <f>IF(AF17="","",IF(AE17&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF17&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3160,7 +3198,9 @@
       <c r="D18" s="10">
         <v>8</v>
       </c>
-      <c r="E18" s="11"/>
+      <c r="E18" s="11">
+        <v>5</v>
+      </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
@@ -3170,9 +3210,9 @@
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
-      <c r="O18" s="12" t="str">
+      <c r="O18" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P18" s="11">
         <v>4.7</v>
@@ -3207,7 +3247,7 @@
       </c>
       <c r="AF18" s="14">
         <f>IFERROR((IF(O18="",0,O18*Configuración!$B$4)+IF(R18="",0,R18*Configuración!$B$5)+IF(AA18="",0,AA18*Configuración!$B$6)+IF(AD18="",0,AD18*Configuración!$B$7))/(IF(O18="",0,Configuración!$B$4)+IF(R18="",0,Configuración!$B$5)+IF(AA18="",0,Configuración!$B$6)+IF(AD18="",0,Configuración!$B$7)),"")</f>
-        <v>4.8000000000000007</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AG18" s="15" t="str">
         <f>IF(AF18="","",IF(AE18&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF18&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3227,7 +3267,9 @@
       <c r="D19" s="10">
         <v>3</v>
       </c>
-      <c r="E19" s="11"/>
+      <c r="E19" s="11">
+        <v>5</v>
+      </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
@@ -3237,9 +3279,9 @@
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
       <c r="N19" s="11"/>
-      <c r="O19" s="12" t="str">
+      <c r="O19" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P19" s="11">
         <v>4.8</v>
@@ -3274,7 +3316,7 @@
       </c>
       <c r="AF19" s="14">
         <f>IFERROR((IF(O19="",0,O19*Configuración!$B$4)+IF(R19="",0,R19*Configuración!$B$5)+IF(AA19="",0,AA19*Configuración!$B$6)+IF(AD19="",0,AD19*Configuración!$B$7))/(IF(O19="",0,Configuración!$B$4)+IF(R19="",0,Configuración!$B$5)+IF(AA19="",0,Configuración!$B$6)+IF(AD19="",0,Configuración!$B$7)),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="AG19" s="15" t="str">
         <f>IF(AF19="","",IF(AE19&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF19&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3294,8 +3336,12 @@
       <c r="D20" s="10">
         <v>3</v>
       </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
+      <c r="E20" s="11">
+        <v>5</v>
+      </c>
+      <c r="F20" s="11">
+        <v>5</v>
+      </c>
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
@@ -3304,9 +3350,9 @@
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
       <c r="N20" s="11"/>
-      <c r="O20" s="12" t="str">
+      <c r="O20" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P20" s="11">
         <v>4.8</v>
@@ -3341,7 +3387,7 @@
       </c>
       <c r="AF20" s="14">
         <f>IFERROR((IF(O20="",0,O20*Configuración!$B$4)+IF(R20="",0,R20*Configuración!$B$5)+IF(AA20="",0,AA20*Configuración!$B$6)+IF(AD20="",0,AD20*Configuración!$B$7))/(IF(O20="",0,Configuración!$B$4)+IF(R20="",0,Configuración!$B$5)+IF(AA20="",0,Configuración!$B$6)+IF(AD20="",0,Configuración!$B$7)),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="AG20" s="15" t="str">
         <f>IF(AF20="","",IF(AE20&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF20&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3361,7 +3407,9 @@
       <c r="D21" s="10">
         <v>8</v>
       </c>
-      <c r="E21" s="11"/>
+      <c r="E21" s="11">
+        <v>5</v>
+      </c>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
       <c r="H21" s="11"/>
@@ -3371,9 +3419,9 @@
       <c r="L21" s="11"/>
       <c r="M21" s="11"/>
       <c r="N21" s="11"/>
-      <c r="O21" s="12" t="str">
+      <c r="O21" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P21" s="11">
         <v>4.8</v>
@@ -3408,7 +3456,7 @@
       </c>
       <c r="AF21" s="14">
         <f>IFERROR((IF(O21="",0,O21*Configuración!$B$4)+IF(R21="",0,R21*Configuración!$B$5)+IF(AA21="",0,AA21*Configuración!$B$6)+IF(AD21="",0,AD21*Configuración!$B$7))/(IF(O21="",0,Configuración!$B$4)+IF(R21="",0,Configuración!$B$5)+IF(AA21="",0,Configuración!$B$6)+IF(AD21="",0,Configuración!$B$7)),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="AG21" s="15" t="str">
         <f>IF(AF21="","",IF(AE21&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF21&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3428,7 +3476,9 @@
       <c r="D22" s="10">
         <v>6</v>
       </c>
-      <c r="E22" s="11"/>
+      <c r="E22" s="11">
+        <v>5</v>
+      </c>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
@@ -3438,9 +3488,9 @@
       <c r="L22" s="11"/>
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
-      <c r="O22" s="12" t="str">
+      <c r="O22" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P22" s="11">
         <v>4.5</v>
@@ -3475,7 +3525,7 @@
       </c>
       <c r="AF22" s="14">
         <f>IFERROR((IF(O22="",0,O22*Configuración!$B$4)+IF(R22="",0,R22*Configuración!$B$5)+IF(AA22="",0,AA22*Configuración!$B$6)+IF(AD22="",0,AD22*Configuración!$B$7))/(IF(O22="",0,Configuración!$B$4)+IF(R22="",0,Configuración!$B$5)+IF(AA22="",0,Configuración!$B$6)+IF(AD22="",0,Configuración!$B$7)),"")</f>
-        <v>4.75</v>
+        <v>4.875</v>
       </c>
       <c r="AG22" s="15" t="str">
         <f>IF(AF22="","",IF(AE22&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF22&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3495,7 +3545,9 @@
       <c r="D23" s="10">
         <v>7</v>
       </c>
-      <c r="E23" s="11"/>
+      <c r="E23" s="11">
+        <v>5</v>
+      </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
@@ -3505,9 +3557,9 @@
       <c r="L23" s="11"/>
       <c r="M23" s="11"/>
       <c r="N23" s="11"/>
-      <c r="O23" s="12" t="str">
+      <c r="O23" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P23" s="11">
         <v>4.8</v>
@@ -3542,7 +3594,7 @@
       </c>
       <c r="AF23" s="14">
         <f>IFERROR((IF(O23="",0,O23*Configuración!$B$4)+IF(R23="",0,R23*Configuración!$B$5)+IF(AA23="",0,AA23*Configuración!$B$6)+IF(AD23="",0,AD23*Configuración!$B$7))/(IF(O23="",0,Configuración!$B$4)+IF(R23="",0,Configuración!$B$5)+IF(AA23="",0,Configuración!$B$6)+IF(AD23="",0,Configuración!$B$7)),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="AG23" s="15" t="str">
         <f>IF(AF23="","",IF(AE23&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF23&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3562,7 +3614,9 @@
       <c r="D24" s="10">
         <v>2</v>
       </c>
-      <c r="E24" s="11"/>
+      <c r="E24" s="11">
+        <v>2.5</v>
+      </c>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
@@ -3572,9 +3626,9 @@
       <c r="L24" s="11"/>
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
-      <c r="O24" s="12" t="str">
+      <c r="O24" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="P24" s="11">
         <v>4.5</v>
@@ -3609,7 +3663,7 @@
       </c>
       <c r="AF24" s="14">
         <f>IFERROR((IF(O24="",0,O24*Configuración!$B$4)+IF(R24="",0,R24*Configuración!$B$5)+IF(AA24="",0,AA24*Configuración!$B$6)+IF(AD24="",0,AD24*Configuración!$B$7))/(IF(O24="",0,Configuración!$B$4)+IF(R24="",0,Configuración!$B$5)+IF(AA24="",0,Configuración!$B$6)+IF(AD24="",0,Configuración!$B$7)),"")</f>
-        <v>4.75</v>
+        <v>3.6250000000000004</v>
       </c>
       <c r="AG24" s="15" t="str">
         <f>IF(AF24="","",IF(AE24&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF24&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3629,7 +3683,9 @@
       <c r="D25" s="10">
         <v>9</v>
       </c>
-      <c r="E25" s="11"/>
+      <c r="E25" s="11">
+        <v>5</v>
+      </c>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
@@ -3639,9 +3695,9 @@
       <c r="L25" s="11"/>
       <c r="M25" s="11"/>
       <c r="N25" s="11"/>
-      <c r="O25" s="12" t="str">
+      <c r="O25" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P25" s="11">
         <v>4.8</v>
@@ -3676,7 +3732,7 @@
       </c>
       <c r="AF25" s="14">
         <f>IFERROR((IF(O25="",0,O25*Configuración!$B$4)+IF(R25="",0,R25*Configuración!$B$5)+IF(AA25="",0,AA25*Configuración!$B$6)+IF(AD25="",0,AD25*Configuración!$B$7))/(IF(O25="",0,Configuración!$B$4)+IF(R25="",0,Configuración!$B$5)+IF(AA25="",0,Configuración!$B$6)+IF(AD25="",0,Configuración!$B$7)),"")</f>
-        <v>4.8499999999999996</v>
+        <v>4.9249999999999998</v>
       </c>
       <c r="AG25" s="15" t="str">
         <f>IF(AF25="","",IF(AE25&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF25&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3693,8 +3749,12 @@
       <c r="C26" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="D26" s="10"/>
-      <c r="E26" s="11"/>
+      <c r="D26" s="10">
+        <v>3</v>
+      </c>
+      <c r="E26" s="11">
+        <v>1</v>
+      </c>
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
@@ -3704,9 +3764,9 @@
       <c r="L26" s="11"/>
       <c r="M26" s="11"/>
       <c r="N26" s="11"/>
-      <c r="O26" s="12" t="str">
+      <c r="O26" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="P26" s="11">
         <v>4.9000000000000004</v>
@@ -3741,11 +3801,11 @@
       </c>
       <c r="AF26" s="14">
         <f>IFERROR((IF(O26="",0,O26*Configuración!$B$4)+IF(R26="",0,R26*Configuración!$B$5)+IF(AA26="",0,AA26*Configuración!$B$6)+IF(AD26="",0,AD26*Configuración!$B$7))/(IF(O26="",0,Configuración!$B$4)+IF(R26="",0,Configuración!$B$5)+IF(AA26="",0,Configuración!$B$6)+IF(AD26="",0,Configuración!$B$7)),"")</f>
-        <v>4.45</v>
+        <v>2.7250000000000001</v>
       </c>
       <c r="AG26" s="15" t="str">
         <f>IF(AF26="","",IF(AE26&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF26&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v>APROBADO</v>
+        <v>REPROBADO</v>
       </c>
     </row>
     <row r="27" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3761,7 +3821,9 @@
       <c r="D27" s="10">
         <v>9</v>
       </c>
-      <c r="E27" s="11"/>
+      <c r="E27" s="11">
+        <v>5</v>
+      </c>
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
@@ -3771,9 +3833,9 @@
       <c r="L27" s="11"/>
       <c r="M27" s="11"/>
       <c r="N27" s="11"/>
-      <c r="O27" s="12" t="str">
+      <c r="O27" s="12">
         <f>IFERROR(AVERAGE(E27:N27),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P27" s="11">
         <v>4.8</v>
@@ -3808,7 +3870,7 @@
       </c>
       <c r="AF27" s="14">
         <f>IFERROR((IF(O27="",0,O27*Configuración!$B$4)+IF(R27="",0,R27*Configuración!$B$5)+IF(AA27="",0,AA27*Configuración!$B$6)+IF(AD27="",0,AD27*Configuración!$B$7))/(IF(O27="",0,Configuración!$B$4)+IF(R27="",0,Configuración!$B$5)+IF(AA27="",0,Configuración!$B$6)+IF(AD27="",0,Configuración!$B$7)),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.9499999999999993</v>
       </c>
       <c r="AG27" s="15" t="str">
         <f>IF(AF27="","",IF(AE27&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF27&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3828,8 +3890,12 @@
       <c r="D28" s="10">
         <v>1</v>
       </c>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
+      <c r="E28" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="F28" s="11">
+        <v>5</v>
+      </c>
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
@@ -3838,9 +3904,9 @@
       <c r="L28" s="11"/>
       <c r="M28" s="11"/>
       <c r="N28" s="11"/>
-      <c r="O28" s="12" t="str">
+      <c r="O28" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4.1500000000000004</v>
       </c>
       <c r="P28" s="11">
         <v>4.5</v>
@@ -3875,7 +3941,7 @@
       </c>
       <c r="AF28" s="14">
         <f>IFERROR((IF(O28="",0,O28*Configuración!$B$4)+IF(R28="",0,R28*Configuración!$B$5)+IF(AA28="",0,AA28*Configuración!$B$6)+IF(AD28="",0,AD28*Configuración!$B$7))/(IF(O28="",0,Configuración!$B$4)+IF(R28="",0,Configuración!$B$5)+IF(AA28="",0,Configuración!$B$6)+IF(AD28="",0,Configuración!$B$7)),"")</f>
-        <v>4.7</v>
+        <v>4.4249999999999998</v>
       </c>
       <c r="AG28" s="15" t="str">
         <f>IF(AF28="","",IF(AE28&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF28&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3895,8 +3961,12 @@
       <c r="D29" s="10">
         <v>2</v>
       </c>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
+      <c r="E29" s="11">
+        <v>5</v>
+      </c>
+      <c r="F29" s="11">
+        <v>5</v>
+      </c>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
@@ -3905,9 +3975,9 @@
       <c r="L29" s="11"/>
       <c r="M29" s="11"/>
       <c r="N29" s="11"/>
-      <c r="O29" s="12" t="str">
+      <c r="O29" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="P29" s="11">
         <v>4.7</v>
@@ -3942,7 +4012,7 @@
       </c>
       <c r="AF29" s="14">
         <f>IFERROR((IF(O29="",0,O29*Configuración!$B$4)+IF(R29="",0,R29*Configuración!$B$5)+IF(AA29="",0,AA29*Configuración!$B$6)+IF(AD29="",0,AD29*Configuración!$B$7))/(IF(O29="",0,Configuración!$B$4)+IF(R29="",0,Configuración!$B$5)+IF(AA29="",0,Configuración!$B$6)+IF(AD29="",0,Configuración!$B$7)),"")</f>
-        <v>4.8000000000000007</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AG29" s="15" t="str">
         <f>IF(AF29="","",IF(AE29&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF29&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3962,8 +4032,12 @@
       <c r="D30" s="10">
         <v>5</v>
       </c>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
+      <c r="E30" s="11">
+        <v>4</v>
+      </c>
+      <c r="F30" s="11">
+        <v>5</v>
+      </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
@@ -3972,9 +4046,9 @@
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
       <c r="N30" s="11"/>
-      <c r="O30" s="12" t="str">
+      <c r="O30" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4.5</v>
       </c>
       <c r="P30" s="11">
         <v>4.8</v>
@@ -4009,7 +4083,7 @@
       </c>
       <c r="AF30" s="14">
         <f>IFERROR((IF(O30="",0,O30*Configuración!$B$4)+IF(R30="",0,R30*Configuración!$B$5)+IF(AA30="",0,AA30*Configuración!$B$6)+IF(AD30="",0,AD30*Configuración!$B$7))/(IF(O30="",0,Configuración!$B$4)+IF(R30="",0,Configuración!$B$5)+IF(AA30="",0,Configuración!$B$6)+IF(AD30="",0,Configuración!$B$7)),"")</f>
-        <v>4.8499999999999996</v>
+        <v>4.6749999999999998</v>
       </c>
       <c r="AG30" s="15" t="str">
         <f>IF(AF30="","",IF(AE30&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF30&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -4029,8 +4103,12 @@
       <c r="D31" s="10">
         <v>6</v>
       </c>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
+      <c r="E31" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="F31" s="11">
+        <v>5</v>
+      </c>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -4039,9 +4117,9 @@
       <c r="L31" s="11"/>
       <c r="M31" s="11"/>
       <c r="N31" s="11"/>
-      <c r="O31" s="12" t="str">
+      <c r="O31" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4.25</v>
       </c>
       <c r="P31" s="11">
         <v>5</v>
@@ -4076,7 +4154,7 @@
       </c>
       <c r="AF31" s="14">
         <f>IFERROR((IF(O31="",0,O31*Configuración!$B$4)+IF(R31="",0,R31*Configuración!$B$5)+IF(AA31="",0,AA31*Configuración!$B$6)+IF(AD31="",0,AD31*Configuración!$B$7))/(IF(O31="",0,Configuración!$B$4)+IF(R31="",0,Configuración!$B$5)+IF(AA31="",0,Configuración!$B$6)+IF(AD31="",0,Configuración!$B$7)),"")</f>
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AG31" s="15" t="str">
         <f>IF(AF31="","",IF(AE31&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF31&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -4096,8 +4174,12 @@
       <c r="D32" s="10">
         <v>3</v>
       </c>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
+      <c r="E32" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="F32" s="11">
+        <v>5</v>
+      </c>
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
@@ -4106,9 +4188,9 @@
       <c r="L32" s="11"/>
       <c r="M32" s="11"/>
       <c r="N32" s="11"/>
-      <c r="O32" s="12" t="str">
+      <c r="O32" s="12">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3.25</v>
       </c>
       <c r="P32" s="11">
         <v>4.8</v>
@@ -4143,7 +4225,7 @@
       </c>
       <c r="AF32" s="14">
         <f>IFERROR((IF(O32="",0,O32*Configuración!$B$4)+IF(R32="",0,R32*Configuración!$B$5)+IF(AA32="",0,AA32*Configuración!$B$6)+IF(AD32="",0,AD32*Configuración!$B$7))/(IF(O32="",0,Configuración!$B$4)+IF(R32="",0,Configuración!$B$5)+IF(AA32="",0,Configuración!$B$6)+IF(AD32="",0,Configuración!$B$7)),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.0750000000000002</v>
       </c>
       <c r="AG32" s="15" t="str">
         <f>IF(AF32="","",IF(AE32&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF32&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -4163,7 +4245,9 @@
       <c r="D33" s="10">
         <v>1</v>
       </c>
-      <c r="E33" s="11"/>
+      <c r="E33" s="11">
+        <v>5</v>
+      </c>
       <c r="F33" s="11"/>
       <c r="G33" s="11"/>
       <c r="H33" s="11"/>
@@ -4173,9 +4257,9 @@
       <c r="L33" s="11"/>
       <c r="M33" s="11"/>
       <c r="N33" s="11"/>
-      <c r="O33" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="O33" s="12">
+        <f>IFERROR(AVERAGE(E33:N33),"")</f>
+        <v>5</v>
       </c>
       <c r="P33" s="11">
         <v>4.7</v>
@@ -4210,7 +4294,7 @@
       </c>
       <c r="AF33" s="14">
         <f>IFERROR((IF(O33="",0,O33*Configuración!$B$4)+IF(R33="",0,R33*Configuración!$B$5)+IF(AA33="",0,AA33*Configuración!$B$6)+IF(AD33="",0,AD33*Configuración!$B$7))/(IF(O33="",0,Configuración!$B$4)+IF(R33="",0,Configuración!$B$5)+IF(AA33="",0,Configuración!$B$6)+IF(AD33="",0,Configuración!$B$7)),"")</f>
-        <v>4.8000000000000007</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AG33" s="15" t="str">
         <f>IF(AF33="","",IF(AE33&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF33&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -4226,7 +4310,9 @@
       </c>
       <c r="C34" s="17"/>
       <c r="D34" s="10"/>
-      <c r="E34" s="11"/>
+      <c r="E34" s="11">
+        <v>4.3</v>
+      </c>
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
       <c r="H34" s="11"/>
@@ -4236,7 +4322,10 @@
       <c r="L34" s="11"/>
       <c r="M34" s="11"/>
       <c r="N34" s="11"/>
-      <c r="O34" s="12"/>
+      <c r="O34" s="12">
+        <f>IFERROR(AVERAGE(E34:N34),"")</f>
+        <v>4.3</v>
+      </c>
       <c r="P34" s="43">
         <v>4.5999999999999996</v>
       </c>
@@ -4270,7 +4359,7 @@
       </c>
       <c r="AF34" s="14">
         <f>IFERROR((IF(O34="",0,O34*Configuración!$B$4)+IF(R34="",0,R34*Configuración!$B$5)+IF(AA34="",0,AA34*Configuración!$B$6)+IF(AD34="",0,AD34*Configuración!$B$7))/(IF(O34="",0,Configuración!$B$4)+IF(R34="",0,Configuración!$B$5)+IF(AA34="",0,Configuración!$B$6)+IF(AD34="",0,Configuración!$B$7)),"")</f>
-        <v>4.75</v>
+        <v>4.5249999999999995</v>
       </c>
       <c r="AG34" s="15" t="str">
         <f>IF(AF34="","",IF(AE34&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF34&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -4284,13 +4373,13 @@
       </c>
       <c r="C35" s="18"/>
       <c r="D35" s="18"/>
-      <c r="E35" s="20" t="str">
-        <f t="shared" ref="E35:AF35" si="6">IFERROR(AVERAGE(E4:E33),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="20" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+      <c r="E35" s="20">
+        <f>IFERROR(AVERAGE(E4:E34),"")</f>
+        <v>4.2193548387096778</v>
+      </c>
+      <c r="F35" s="20">
+        <f t="shared" ref="F35:AF35" si="6">IFERROR(AVERAGE(F4:F33),"")</f>
+        <v>4.9727272727272727</v>
       </c>
       <c r="G35" s="20" t="str">
         <f t="shared" si="6"/>
@@ -4324,9 +4413,9 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O35" s="20" t="str">
+      <c r="O35" s="20">
         <f t="shared" si="6"/>
-        <v/>
+        <v>4.3966666666666665</v>
       </c>
       <c r="P35" s="20">
         <f>IFERROR(AVERAGE(P4:P34),"")</f>
@@ -4394,11 +4483,11 @@
       </c>
       <c r="AF35" s="20">
         <f t="shared" si="6"/>
-        <v>4.826666666666668</v>
+        <v>4.6116666666666664</v>
       </c>
       <c r="AG35" s="18" t="str">
         <f>COUNTIF(AG4:AG33,"APROBADO")&amp;" aprob."</f>
-        <v>30 aprob.</v>
+        <v>29 aprob.</v>
       </c>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
@@ -4528,7 +4617,7 @@
       </c>
       <c r="F5" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D5,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.8250000000000002</v>
+        <v>4.6624999999999996</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4537,7 +4626,7 @@
       </c>
       <c r="B6" s="28">
         <f>IFERROR(AVERAGE(Notas!$AF$4:$AF$33),"")</f>
-        <v>4.826666666666668</v>
+        <v>4.6116666666666664</v>
       </c>
       <c r="D6" s="25">
         <v>2</v>
@@ -4548,7 +4637,7 @@
       </c>
       <c r="F6" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D6,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.833333333333333</v>
+        <v>4.5000000000000009</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4557,18 +4646,18 @@
       </c>
       <c r="B7" s="28">
         <f>IFERROR(MAX(Notas!$AF$4:$AF$33),"")</f>
-        <v>4.95</v>
+        <v>4.9750000000000005</v>
       </c>
       <c r="D7" s="25">
         <v>3</v>
       </c>
       <c r="E7" s="26">
         <f>COUNTIF(Notas!$D$4:$D$33,$D7)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D7,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.1749999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4577,7 +4666,7 @@
       </c>
       <c r="B8" s="28">
         <f>IFERROR(MIN(Notas!$AF$4:$AF$33),"")</f>
-        <v>4.45</v>
+        <v>2.7250000000000001</v>
       </c>
       <c r="D8" s="25">
         <v>4</v>
@@ -4588,7 +4677,7 @@
       </c>
       <c r="F8" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D8,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.8500000000000005</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4597,7 +4686,7 @@
       </c>
       <c r="B9" s="28">
         <f>IFERROR(STDEV(Notas!$AF$4:$AF$33),"")</f>
-        <v>0.11198316786489605</v>
+        <v>0.49856402994402321</v>
       </c>
       <c r="D9" s="25">
         <v>5</v>
@@ -4608,7 +4697,7 @@
       </c>
       <c r="F9" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D9,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.7499999999999991</v>
+        <v>4.6750000000000007</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4617,7 +4706,7 @@
       </c>
       <c r="B10" s="23">
         <f>COUNTIF(Notas!$AG$4:$AG$33,"APROBADO")</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="25">
         <v>6</v>
@@ -4628,7 +4717,7 @@
       </c>
       <c r="F10" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D10,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.75</v>
+        <v>4.666666666666667</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4637,7 +4726,7 @@
       </c>
       <c r="B11" s="23">
         <f>COUNTIF(Notas!$AG$4:$AG$33,"REPROBADO")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="25">
         <v>7</v>
@@ -4648,7 +4737,7 @@
       </c>
       <c r="F11" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D11,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.9125000000000005</v>
+        <v>4.7062499999999998</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4668,7 +4757,7 @@
       </c>
       <c r="F12" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D12,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.8500000000000005</v>
+        <v>4.9249999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4677,7 +4766,7 @@
       </c>
       <c r="B13" s="29">
         <f>IFERROR(COUNTIF(Notas!$AG$4:$AG$33,"APROBADO")/COUNT(Notas!$AF$4:$AF$33),"")</f>
-        <v>1</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="D13" s="25">
         <v>9</v>
@@ -4688,7 +4777,7 @@
       </c>
       <c r="F13" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D13,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.8666666666666663</v>
+        <v>4.9333333333333327</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4719,9 +4808,9 @@
       <c r="A17" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="B17" s="28" t="str">
+      <c r="B17" s="28">
         <f>IFERROR(AVERAGE(Notas!$O$4:$O$33),"")</f>
-        <v/>
+        <v>4.3966666666666665</v>
       </c>
       <c r="D17" s="24" t="s">
         <v>160</v>
@@ -4759,7 +4848,7 @@
       </c>
       <c r="E19" s="23">
         <f>COUNTIFS(Notas!$AF$4:$AF$33,"&gt;="&amp;2,Notas!$AF$4:$AF$33,"&lt;"&amp;3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -4784,7 +4873,7 @@
       </c>
       <c r="E21" s="23">
         <f>COUNTIFS(Notas!$AF$4:$AF$33,"&gt;="&amp;3.5,Notas!$AF$4:$AF$33,"&lt;"&amp;4)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -4793,7 +4882,7 @@
       </c>
       <c r="E22" s="23">
         <f>COUNTIFS(Notas!$AF$4:$AF$33,"&gt;="&amp;4,Notas!$AF$4:$AF$33,"&lt;"&amp;4.5)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -4802,7 +4891,7 @@
       </c>
       <c r="E23" s="23">
         <f>COUNTIFS(Notas!$AF$4:$AF$33,"&gt;="&amp;4.5,Notas!$AF$4:$AF$33,"&lt;"&amp;5.01)</f>
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Laboratorio_de_mecanica_y_ondas_para_biociencias_2026-2/Notas/Notas_Laboratorio_Biociencias_G4_2026-2.xlsx
+++ b/Laboratorio_de_mecanica_y_ondas_para_biociencias_2026-2/Notas/Notas_Laboratorio_Biociencias_G4_2026-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\miguel_perdomo\Auxiliar_docente_UNAL\Laboratorio_de_mecanica_y_ondas_para_biociencias_2026-2\Notas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0F3E19-BE55-46CF-B199-DA09EF657588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310993B6-5590-4BC6-9E2F-E618D867F3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="52680" yWindow="-1965" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,9 +34,6 @@
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1154,7 +1151,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1209,8 +1206,20 @@
         <bgColor rgb="FFF0FAF3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor rgb="FFF0FAF3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1248,11 +1257,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1373,14 +1393,26 @@
     <xf numFmtId="164" fontId="17" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1718,287 +1750,267 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
     </row>
     <row r="4" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
     </row>
     <row r="5" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="44" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
+      <c r="B5" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
     </row>
     <row r="10" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
     </row>
     <row r="11" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
     </row>
     <row r="12" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
     </row>
     <row r="13" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
     </row>
     <row r="14" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
     </row>
     <row r="15" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="45" t="s">
+      <c r="A17" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="45"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
     </row>
     <row r="18" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="44" t="s">
+      <c r="B18" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
     </row>
     <row r="19" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
     </row>
     <row r="20" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="44" t="s">
+      <c r="B20" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="50"/>
     </row>
     <row r="21" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="44" t="s">
+      <c r="B21" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
     </row>
     <row r="22" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="44" t="s">
+      <c r="B22" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="50"/>
     </row>
     <row r="23" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="44" t="s">
+      <c r="B23" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
     </row>
     <row r="24" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="44" t="s">
+      <c r="B24" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
     </row>
     <row r="27" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="44" t="s">
+      <c r="B27" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
     </row>
     <row r="28" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="44" t="s">
+      <c r="B28" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="50"/>
     </row>
     <row r="29" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="44" t="s">
+      <c r="B29" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
     </row>
     <row r="30" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="44" t="s">
+      <c r="B30" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
     </row>
     <row r="31" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="44" t="s">
+      <c r="B31" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="44"/>
-      <c r="D31" s="44"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B24:D24"/>
@@ -2006,6 +2018,26 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2014,7 +2046,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AG36"/>
+  <dimension ref="A1:AG37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.42578125" customWidth="1"/>
@@ -2035,78 +2067,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
-      <c r="X1" s="47"/>
-      <c r="Y1" s="47"/>
-      <c r="Z1" s="47"/>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="47"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="51"/>
+      <c r="W1" s="51"/>
+      <c r="X1" s="51"/>
+      <c r="Y1" s="51"/>
+      <c r="Z1" s="51"/>
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="51"/>
+      <c r="AC1" s="51"/>
+      <c r="AD1" s="51"/>
+      <c r="AE1" s="51"/>
+      <c r="AF1" s="51"/>
+      <c r="AG1" s="51"/>
     </row>
     <row r="2" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="52" t="s">
         <v>197</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
-      <c r="W2" s="48"/>
-      <c r="X2" s="48"/>
-      <c r="Y2" s="48"/>
-      <c r="Z2" s="48"/>
-      <c r="AA2" s="48"/>
-      <c r="AB2" s="48"/>
-      <c r="AC2" s="48"/>
-      <c r="AD2" s="48"/>
-      <c r="AE2" s="48"/>
-      <c r="AF2" s="48"/>
-      <c r="AG2" s="48"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="52"/>
+      <c r="Z2" s="52"/>
+      <c r="AA2" s="52"/>
+      <c r="AB2" s="52"/>
+      <c r="AC2" s="52"/>
+      <c r="AD2" s="52"/>
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="52"/>
+      <c r="AG2" s="52"/>
     </row>
     <row r="3" spans="1:33" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="40" t="s">
@@ -2213,7 +2245,7 @@
       <c r="A4" s="8">
         <v>1</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="46" t="s">
         <v>81</v>
       </c>
       <c r="C4" s="9" t="s">
@@ -2225,8 +2257,12 @@
       <c r="E4" s="11">
         <v>4</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+      <c r="F4" s="11">
+        <v>5</v>
+      </c>
+      <c r="G4" s="11">
+        <v>5</v>
+      </c>
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
       <c r="J4" s="11"/>
@@ -2236,7 +2272,7 @@
       <c r="N4" s="11"/>
       <c r="O4" s="12">
         <f t="shared" ref="O4:O32" si="0">IFERROR(AVERAGE(E4:N4),"")</f>
-        <v>4</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="P4" s="11">
         <v>4.9000000000000004</v>
@@ -2248,17 +2284,23 @@
         <f t="shared" ref="R4:R33" si="1">IFERROR(AVERAGE(P4:Q4),"")</f>
         <v>4.95</v>
       </c>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
+      <c r="S4" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="T4" s="11">
+        <v>5</v>
+      </c>
+      <c r="U4" s="11">
+        <v>5</v>
+      </c>
       <c r="V4" s="11"/>
       <c r="W4" s="11"/>
       <c r="X4" s="11"/>
       <c r="Y4" s="11"/>
       <c r="Z4" s="11"/>
-      <c r="AA4" s="12" t="str">
+      <c r="AA4" s="12">
         <f t="shared" ref="AA4:AA33" si="2">IFERROR(AVERAGE(S4:Z4),"")</f>
-        <v/>
+        <v>4.9333333333333336</v>
       </c>
       <c r="AB4" s="11"/>
       <c r="AC4" s="11"/>
@@ -2271,7 +2313,7 @@
       </c>
       <c r="AF4" s="14">
         <f>IFERROR((IF(O4="",0,O4*Configuración!$B$4)+IF(R4="",0,R4*Configuración!$B$5)+IF(AA4="",0,AA4*Configuración!$B$6)+IF(AD4="",0,AD4*Configuración!$B$7))/(IF(O4="",0,Configuración!$B$4)+IF(R4="",0,Configuración!$B$5)+IF(AA4="",0,Configuración!$B$6)+IF(AD4="",0,Configuración!$B$7)),"")</f>
-        <v>4.4749999999999996</v>
+        <v>4.897619047619048</v>
       </c>
       <c r="AG4" s="15" t="str">
         <f>IF(AF4="","",IF(AE4&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF4&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2282,7 +2324,7 @@
       <c r="A5" s="16">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="45" t="s">
         <v>83</v>
       </c>
       <c r="C5" s="17" t="s">
@@ -2297,7 +2339,9 @@
       <c r="F5" s="11">
         <v>5</v>
       </c>
-      <c r="G5" s="11"/>
+      <c r="G5" s="11">
+        <v>5</v>
+      </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
       <c r="J5" s="11"/>
@@ -2319,17 +2363,23 @@
         <f t="shared" si="1"/>
         <v>4.95</v>
       </c>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
+      <c r="S5" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="T5" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U5" s="11">
+        <v>5</v>
+      </c>
       <c r="V5" s="11"/>
       <c r="W5" s="11"/>
       <c r="X5" s="11"/>
       <c r="Y5" s="11"/>
       <c r="Z5" s="11"/>
-      <c r="AA5" s="12" t="str">
+      <c r="AA5" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.7666666666666666</v>
       </c>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11"/>
@@ -2342,7 +2392,7 @@
       </c>
       <c r="AF5" s="14">
         <f>IFERROR((IF(O5="",0,O5*Configuración!$B$4)+IF(R5="",0,R5*Configuración!$B$5)+IF(AA5="",0,AA5*Configuración!$B$6)+IF(AD5="",0,AD5*Configuración!$B$7))/(IF(O5="",0,Configuración!$B$4)+IF(R5="",0,Configuración!$B$5)+IF(AA5="",0,Configuración!$B$6)+IF(AD5="",0,Configuración!$B$7)),"")</f>
-        <v>4.9750000000000005</v>
+        <v>4.8261904761904768</v>
       </c>
       <c r="AG5" s="15" t="str">
         <f>IF(AF5="","",IF(AE5&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF5&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2353,7 +2403,7 @@
       <c r="A6" s="8">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="46" t="s">
         <v>85</v>
       </c>
       <c r="C6" s="9" t="s">
@@ -2365,8 +2415,12 @@
       <c r="E6" s="11">
         <v>5</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
+      <c r="F6" s="44">
+        <v>5</v>
+      </c>
+      <c r="G6" s="11">
+        <v>5</v>
+      </c>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
@@ -2388,17 +2442,23 @@
         <f t="shared" si="1"/>
         <v>4.9000000000000004</v>
       </c>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
+      <c r="S6" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="T6" s="11">
+        <v>5</v>
+      </c>
+      <c r="U6" s="11">
+        <v>5</v>
+      </c>
       <c r="V6" s="11"/>
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
       <c r="Y6" s="11"/>
       <c r="Z6" s="11"/>
-      <c r="AA6" s="12" t="str">
+      <c r="AA6" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.9333333333333336</v>
       </c>
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
@@ -2411,7 +2471,7 @@
       </c>
       <c r="AF6" s="14">
         <f>IFERROR((IF(O6="",0,O6*Configuración!$B$4)+IF(R6="",0,R6*Configuración!$B$5)+IF(AA6="",0,AA6*Configuración!$B$6)+IF(AD6="",0,AD6*Configuración!$B$7))/(IF(O6="",0,Configuración!$B$4)+IF(R6="",0,Configuración!$B$5)+IF(AA6="",0,Configuración!$B$6)+IF(AD6="",0,Configuración!$B$7)),"")</f>
-        <v>4.9499999999999993</v>
+        <v>4.9380952380952392</v>
       </c>
       <c r="AG6" s="15" t="str">
         <f>IF(AF6="","",IF(AE6&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF6&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2434,8 +2494,12 @@
       <c r="E7" s="11">
         <v>3.8</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
+      <c r="F7" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="G7" s="11">
+        <v>5</v>
+      </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
       <c r="J7" s="11"/>
@@ -2445,7 +2509,7 @@
       <c r="N7" s="11"/>
       <c r="O7" s="12">
         <f t="shared" si="0"/>
-        <v>3.8</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="P7" s="11">
         <v>4.8</v>
@@ -2457,17 +2521,23 @@
         <f t="shared" si="1"/>
         <v>4.9000000000000004</v>
       </c>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
+      <c r="S7" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="T7" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U7" s="11">
+        <v>4.8</v>
+      </c>
       <c r="V7" s="11"/>
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
       <c r="Y7" s="11"/>
       <c r="Z7" s="11"/>
-      <c r="AA7" s="12" t="str">
+      <c r="AA7" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.6333333333333329</v>
       </c>
       <c r="AB7" s="11"/>
       <c r="AC7" s="11"/>
@@ -2480,7 +2550,7 @@
       </c>
       <c r="AF7" s="14">
         <f>IFERROR((IF(O7="",0,O7*Configuración!$B$4)+IF(R7="",0,R7*Configuración!$B$5)+IF(AA7="",0,AA7*Configuración!$B$6)+IF(AD7="",0,AD7*Configuración!$B$7))/(IF(O7="",0,Configuración!$B$4)+IF(R7="",0,Configuración!$B$5)+IF(AA7="",0,Configuración!$B$6)+IF(AD7="",0,Configuración!$B$7)),"")</f>
-        <v>4.3500000000000005</v>
+        <v>4.6285714285714281</v>
       </c>
       <c r="AG7" s="15" t="str">
         <f>IF(AF7="","",IF(AE7&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF7&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2503,8 +2573,12 @@
       <c r="E8" s="11">
         <v>5</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
+      <c r="F8" s="11">
+        <v>5</v>
+      </c>
+      <c r="G8" s="11">
+        <v>5</v>
+      </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
@@ -2526,17 +2600,23 @@
         <f t="shared" si="1"/>
         <v>4.9000000000000004</v>
       </c>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="S8" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="T8" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U8" s="11">
+        <v>4.8</v>
+      </c>
       <c r="V8" s="11"/>
       <c r="W8" s="11"/>
       <c r="X8" s="11"/>
       <c r="Y8" s="11"/>
       <c r="Z8" s="11"/>
-      <c r="AA8" s="12" t="str">
+      <c r="AA8" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.6333333333333329</v>
       </c>
       <c r="AB8" s="11"/>
       <c r="AC8" s="11"/>
@@ -2549,7 +2629,7 @@
       </c>
       <c r="AF8" s="14">
         <f>IFERROR((IF(O8="",0,O8*Configuración!$B$4)+IF(R8="",0,R8*Configuración!$B$5)+IF(AA8="",0,AA8*Configuración!$B$6)+IF(AD8="",0,AD8*Configuración!$B$7))/(IF(O8="",0,Configuración!$B$4)+IF(R8="",0,Configuración!$B$5)+IF(AA8="",0,Configuración!$B$6)+IF(AD8="",0,Configuración!$B$7)),"")</f>
-        <v>4.9499999999999993</v>
+        <v>4.7238095238095239</v>
       </c>
       <c r="AG8" s="15" t="str">
         <f>IF(AF8="","",IF(AE8&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF8&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2575,7 +2655,9 @@
       <c r="F9" s="11">
         <v>5</v>
       </c>
-      <c r="G9" s="11"/>
+      <c r="G9" s="11">
+        <v>5</v>
+      </c>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11"/>
@@ -2585,7 +2667,7 @@
       <c r="N9" s="11"/>
       <c r="O9" s="12">
         <f t="shared" si="0"/>
-        <v>4.6500000000000004</v>
+        <v>4.7666666666666666</v>
       </c>
       <c r="P9" s="11">
         <v>5</v>
@@ -2597,17 +2679,23 @@
         <f t="shared" si="1"/>
         <v>4.8499999999999996</v>
       </c>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="S9" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="T9" s="11">
+        <v>5</v>
+      </c>
+      <c r="U9" s="11">
+        <v>4.8</v>
+      </c>
       <c r="V9" s="11"/>
       <c r="W9" s="11"/>
       <c r="X9" s="11"/>
       <c r="Y9" s="11"/>
       <c r="Z9" s="11"/>
-      <c r="AA9" s="12" t="str">
+      <c r="AA9" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.7</v>
       </c>
       <c r="AB9" s="11"/>
       <c r="AC9" s="11"/>
@@ -2620,7 +2708,7 @@
       </c>
       <c r="AF9" s="14">
         <f>IFERROR((IF(O9="",0,O9*Configuración!$B$4)+IF(R9="",0,R9*Configuración!$B$5)+IF(AA9="",0,AA9*Configuración!$B$6)+IF(AD9="",0,AD9*Configuración!$B$7))/(IF(O9="",0,Configuración!$B$4)+IF(R9="",0,Configuración!$B$5)+IF(AA9="",0,Configuración!$B$6)+IF(AD9="",0,Configuración!$B$7)),"")</f>
-        <v>4.75</v>
+        <v>4.730952380952381</v>
       </c>
       <c r="AG9" s="15" t="str">
         <f>IF(AF9="","",IF(AE9&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF9&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2643,8 +2731,12 @@
       <c r="E10" s="11">
         <v>2.8</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
+      <c r="F10" s="11">
+        <v>5</v>
+      </c>
+      <c r="G10" s="11">
+        <v>5</v>
+      </c>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
@@ -2654,7 +2746,7 @@
       <c r="N10" s="41"/>
       <c r="O10" s="12">
         <f t="shared" si="0"/>
-        <v>2.8</v>
+        <v>4.2666666666666666</v>
       </c>
       <c r="P10" s="11">
         <v>4.5999999999999996</v>
@@ -2666,17 +2758,23 @@
         <f t="shared" si="1"/>
         <v>4.8</v>
       </c>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="S10" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="T10" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U10" s="11">
+        <v>4.8</v>
+      </c>
       <c r="V10" s="11"/>
       <c r="W10" s="11"/>
       <c r="X10" s="11"/>
       <c r="Y10" s="11"/>
       <c r="Z10" s="11"/>
-      <c r="AA10" s="12" t="str">
+      <c r="AA10" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.6333333333333329</v>
       </c>
       <c r="AB10" s="11"/>
       <c r="AC10" s="11"/>
@@ -2689,7 +2787,7 @@
       </c>
       <c r="AF10" s="14">
         <f>IFERROR((IF(O10="",0,O10*Configuración!$B$4)+IF(R10="",0,R10*Configuración!$B$5)+IF(AA10="",0,AA10*Configuración!$B$6)+IF(AD10="",0,AD10*Configuración!$B$7))/(IF(O10="",0,Configuración!$B$4)+IF(R10="",0,Configuración!$B$5)+IF(AA10="",0,Configuración!$B$6)+IF(AD10="",0,Configuración!$B$7)),"")</f>
-        <v>3.8</v>
+        <v>4.6047619047619044</v>
       </c>
       <c r="AG10" s="15" t="str">
         <f>IF(AF10="","",IF(AE10&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF10&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2712,8 +2810,12 @@
       <c r="E11" s="11">
         <v>4.5</v>
       </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
+      <c r="F11" s="11">
+        <v>5</v>
+      </c>
+      <c r="G11" s="11">
+        <v>5</v>
+      </c>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
@@ -2723,7 +2825,7 @@
       <c r="N11" s="11"/>
       <c r="O11" s="12">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="P11" s="11">
         <v>4.5</v>
@@ -2735,17 +2837,23 @@
         <f t="shared" si="1"/>
         <v>4.75</v>
       </c>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="S11" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="T11" s="11">
+        <v>5</v>
+      </c>
+      <c r="U11" s="11">
+        <v>5</v>
+      </c>
       <c r="V11" s="11"/>
       <c r="W11" s="11"/>
       <c r="X11" s="11"/>
       <c r="Y11" s="11"/>
       <c r="Z11" s="11"/>
-      <c r="AA11" s="12" t="str">
+      <c r="AA11" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.7666666666666666</v>
       </c>
       <c r="AB11" s="11"/>
       <c r="AC11" s="11"/>
@@ -2758,7 +2866,7 @@
       </c>
       <c r="AF11" s="14">
         <f>IFERROR((IF(O11="",0,O11*Configuración!$B$4)+IF(R11="",0,R11*Configuración!$B$5)+IF(AA11="",0,AA11*Configuración!$B$6)+IF(AD11="",0,AD11*Configuración!$B$7))/(IF(O11="",0,Configuración!$B$4)+IF(R11="",0,Configuración!$B$5)+IF(AA11="",0,Configuración!$B$6)+IF(AD11="",0,Configuración!$B$7)),"")</f>
-        <v>4.625</v>
+        <v>4.7738095238095246</v>
       </c>
       <c r="AG11" s="15" t="str">
         <f>IF(AF11="","",IF(AE11&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF11&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2781,8 +2889,12 @@
       <c r="E12" s="11">
         <v>4</v>
       </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="F12" s="11">
+        <v>5</v>
+      </c>
+      <c r="G12" s="11">
+        <v>5</v>
+      </c>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
       <c r="J12" s="43"/>
@@ -2792,7 +2904,7 @@
       <c r="N12" s="11"/>
       <c r="O12" s="12">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="P12" s="11">
         <v>4.8</v>
@@ -2804,17 +2916,23 @@
         <f t="shared" si="1"/>
         <v>4.9000000000000004</v>
       </c>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="S12" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="T12" s="11">
+        <v>5</v>
+      </c>
+      <c r="U12" s="11">
+        <v>5</v>
+      </c>
       <c r="V12" s="11"/>
       <c r="W12" s="11"/>
       <c r="X12" s="11"/>
       <c r="Y12" s="11"/>
       <c r="Z12" s="11"/>
-      <c r="AA12" s="12" t="str">
+      <c r="AA12" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.9333333333333336</v>
       </c>
       <c r="AB12" s="11"/>
       <c r="AC12" s="11"/>
@@ -2827,7 +2945,7 @@
       </c>
       <c r="AF12" s="14">
         <f>IFERROR((IF(O12="",0,O12*Configuración!$B$4)+IF(R12="",0,R12*Configuración!$B$5)+IF(AA12="",0,AA12*Configuración!$B$6)+IF(AD12="",0,AD12*Configuración!$B$7))/(IF(O12="",0,Configuración!$B$4)+IF(R12="",0,Configuración!$B$5)+IF(AA12="",0,Configuración!$B$6)+IF(AD12="",0,Configuración!$B$7)),"")</f>
-        <v>4.45</v>
+        <v>4.8904761904761918</v>
       </c>
       <c r="AG12" s="15" t="str">
         <f>IF(AF12="","",IF(AE12&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF12&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2853,7 +2971,9 @@
       <c r="F13" s="11">
         <v>5</v>
       </c>
-      <c r="G13" s="11"/>
+      <c r="G13" s="11">
+        <v>5</v>
+      </c>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
@@ -2863,7 +2983,7 @@
       <c r="N13" s="11"/>
       <c r="O13" s="12">
         <f t="shared" si="0"/>
-        <v>4.6500000000000004</v>
+        <v>4.7666666666666666</v>
       </c>
       <c r="P13" s="11">
         <v>4.3</v>
@@ -2875,17 +2995,23 @@
         <f t="shared" si="1"/>
         <v>4.55</v>
       </c>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="S13" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="T13" s="11">
+        <v>5</v>
+      </c>
+      <c r="U13" s="11">
+        <v>4.8</v>
+      </c>
       <c r="V13" s="11"/>
       <c r="W13" s="11"/>
       <c r="X13" s="11"/>
       <c r="Y13" s="11"/>
       <c r="Z13" s="11"/>
-      <c r="AA13" s="12" t="str">
+      <c r="AA13" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.7</v>
       </c>
       <c r="AB13" s="11"/>
       <c r="AC13" s="11"/>
@@ -2898,7 +3024,7 @@
       </c>
       <c r="AF13" s="14">
         <f>IFERROR((IF(O13="",0,O13*Configuración!$B$4)+IF(R13="",0,R13*Configuración!$B$5)+IF(AA13="",0,AA13*Configuración!$B$6)+IF(AD13="",0,AD13*Configuración!$B$7))/(IF(O13="",0,Configuración!$B$4)+IF(R13="",0,Configuración!$B$5)+IF(AA13="",0,Configuración!$B$6)+IF(AD13="",0,Configuración!$B$7)),"")</f>
-        <v>4.6000000000000005</v>
+        <v>4.6880952380952383</v>
       </c>
       <c r="AG13" s="15" t="str">
         <f>IF(AF13="","",IF(AE13&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF13&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2921,8 +3047,12 @@
       <c r="E14" s="11">
         <v>5</v>
       </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
+      <c r="F14" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="G14" s="11">
+        <v>5</v>
+      </c>
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
@@ -2932,7 +3062,7 @@
       <c r="N14" s="11"/>
       <c r="O14" s="12">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4.7666666666666666</v>
       </c>
       <c r="P14" s="11">
         <v>4.5999999999999996</v>
@@ -2944,17 +3074,23 @@
         <f t="shared" si="1"/>
         <v>4.8</v>
       </c>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="S14" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="T14" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U14" s="11">
+        <v>4.8</v>
+      </c>
       <c r="V14" s="11"/>
       <c r="W14" s="11"/>
       <c r="X14" s="11"/>
       <c r="Y14" s="11"/>
       <c r="Z14" s="11"/>
-      <c r="AA14" s="12" t="str">
+      <c r="AA14" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.6333333333333329</v>
       </c>
       <c r="AB14" s="11"/>
       <c r="AC14" s="11"/>
@@ -2967,7 +3103,7 @@
       </c>
       <c r="AF14" s="14">
         <f>IFERROR((IF(O14="",0,O14*Configuración!$B$4)+IF(R14="",0,R14*Configuración!$B$5)+IF(AA14="",0,AA14*Configuración!$B$6)+IF(AD14="",0,AD14*Configuración!$B$7))/(IF(O14="",0,Configuración!$B$4)+IF(R14="",0,Configuración!$B$5)+IF(AA14="",0,Configuración!$B$6)+IF(AD14="",0,Configuración!$B$7)),"")</f>
-        <v>4.8999999999999995</v>
+        <v>4.6761904761904756</v>
       </c>
       <c r="AG14" s="15" t="str">
         <f>IF(AF14="","",IF(AE14&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF14&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -2993,7 +3129,9 @@
       <c r="F15" s="11">
         <v>4.7</v>
       </c>
-      <c r="G15" s="11"/>
+      <c r="G15" s="11">
+        <v>5</v>
+      </c>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
@@ -3003,7 +3141,7 @@
       <c r="N15" s="11"/>
       <c r="O15" s="12">
         <f t="shared" si="0"/>
-        <v>4.3499999999999996</v>
+        <v>4.5666666666666664</v>
       </c>
       <c r="P15" s="11">
         <v>4.7</v>
@@ -3015,17 +3153,23 @@
         <f t="shared" si="1"/>
         <v>4.8499999999999996</v>
       </c>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
+      <c r="S15" s="11">
+        <v>5</v>
+      </c>
+      <c r="T15" s="11">
+        <v>5</v>
+      </c>
+      <c r="U15" s="11">
+        <v>5</v>
+      </c>
       <c r="V15" s="11"/>
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
       <c r="Y15" s="11"/>
       <c r="Z15" s="11"/>
-      <c r="AA15" s="12" t="str">
+      <c r="AA15" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AB15" s="11"/>
       <c r="AC15" s="11"/>
@@ -3038,7 +3182,7 @@
       </c>
       <c r="AF15" s="14">
         <f>IFERROR((IF(O15="",0,O15*Configuración!$B$4)+IF(R15="",0,R15*Configuración!$B$5)+IF(AA15="",0,AA15*Configuración!$B$6)+IF(AD15="",0,AD15*Configuración!$B$7))/(IF(O15="",0,Configuración!$B$4)+IF(R15="",0,Configuración!$B$5)+IF(AA15="",0,Configuración!$B$6)+IF(AD15="",0,Configuración!$B$7)),"")</f>
-        <v>4.5999999999999996</v>
+        <v>4.916666666666667</v>
       </c>
       <c r="AG15" s="15" t="str">
         <f>IF(AF15="","",IF(AE15&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF15&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3061,8 +3205,10 @@
       <c r="E16" s="11">
         <v>5</v>
       </c>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
+      <c r="F16" s="44">
+        <v>5</v>
+      </c>
+      <c r="G16" s="44"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
@@ -3084,17 +3230,23 @@
         <f t="shared" si="1"/>
         <v>4.8499999999999996</v>
       </c>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
+      <c r="S16" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="T16" s="11">
+        <v>5</v>
+      </c>
+      <c r="U16" s="11">
+        <v>5</v>
+      </c>
       <c r="V16" s="11"/>
       <c r="W16" s="11"/>
       <c r="X16" s="11"/>
       <c r="Y16" s="11"/>
       <c r="Z16" s="11"/>
-      <c r="AA16" s="12" t="str">
+      <c r="AA16" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.8666666666666663</v>
       </c>
       <c r="AB16" s="11"/>
       <c r="AC16" s="11"/>
@@ -3107,7 +3259,7 @@
       </c>
       <c r="AF16" s="14">
         <f>IFERROR((IF(O16="",0,O16*Configuración!$B$4)+IF(R16="",0,R16*Configuración!$B$5)+IF(AA16="",0,AA16*Configuración!$B$6)+IF(AD16="",0,AD16*Configuración!$B$7))/(IF(O16="",0,Configuración!$B$4)+IF(R16="",0,Configuración!$B$5)+IF(AA16="",0,Configuración!$B$6)+IF(AD16="",0,Configuración!$B$7)),"")</f>
-        <v>4.9249999999999998</v>
+        <v>4.8833333333333329</v>
       </c>
       <c r="AG16" s="15" t="str">
         <f>IF(AF16="","",IF(AE16&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF16&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3118,7 +3270,7 @@
       <c r="A17" s="16">
         <v>14</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="45" t="s">
         <v>107</v>
       </c>
       <c r="C17" s="17" t="s">
@@ -3133,7 +3285,9 @@
       <c r="F17" s="11">
         <v>5</v>
       </c>
-      <c r="G17" s="11"/>
+      <c r="G17" s="11">
+        <v>5</v>
+      </c>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
@@ -3143,7 +3297,7 @@
       <c r="N17" s="11"/>
       <c r="O17" s="12">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="P17" s="11">
         <v>4.9000000000000004</v>
@@ -3155,17 +3309,23 @@
         <f t="shared" si="1"/>
         <v>4.95</v>
       </c>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
+      <c r="S17" s="11">
+        <v>5</v>
+      </c>
+      <c r="T17" s="11">
+        <v>5</v>
+      </c>
+      <c r="U17" s="11">
+        <v>5</v>
+      </c>
       <c r="V17" s="11"/>
       <c r="W17" s="11"/>
       <c r="X17" s="11"/>
       <c r="Y17" s="11"/>
       <c r="Z17" s="41"/>
-      <c r="AA17" s="12" t="str">
+      <c r="AA17" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AB17" s="11"/>
       <c r="AC17" s="11"/>
@@ -3178,7 +3338,7 @@
       </c>
       <c r="AF17" s="14">
         <f>IFERROR((IF(O17="",0,O17*Configuración!$B$4)+IF(R17="",0,R17*Configuración!$B$5)+IF(AA17="",0,AA17*Configuración!$B$6)+IF(AD17="",0,AD17*Configuración!$B$7))/(IF(O17="",0,Configuración!$B$4)+IF(R17="",0,Configuración!$B$5)+IF(AA17="",0,Configuración!$B$6)+IF(AD17="",0,Configuración!$B$7)),"")</f>
-        <v>4.7249999999999996</v>
+        <v>4.9452380952380954</v>
       </c>
       <c r="AG17" s="15" t="str">
         <f>IF(AF17="","",IF(AE17&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF17&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3201,8 +3361,12 @@
       <c r="E18" s="11">
         <v>5</v>
       </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
+      <c r="F18" s="11">
+        <v>5</v>
+      </c>
+      <c r="G18" s="11">
+        <v>5</v>
+      </c>
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
@@ -3224,17 +3388,23 @@
         <f t="shared" si="1"/>
         <v>4.8000000000000007</v>
       </c>
-      <c r="S18" s="11"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
+      <c r="S18" s="11">
+        <v>5</v>
+      </c>
+      <c r="T18" s="11">
+        <v>5</v>
+      </c>
+      <c r="U18" s="11">
+        <v>5</v>
+      </c>
       <c r="V18" s="11"/>
       <c r="W18" s="11"/>
       <c r="X18" s="11"/>
       <c r="Y18" s="11"/>
       <c r="Z18" s="11"/>
-      <c r="AA18" s="12" t="str">
+      <c r="AA18" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AB18" s="11"/>
       <c r="AC18" s="11"/>
@@ -3247,7 +3417,7 @@
       </c>
       <c r="AF18" s="14">
         <f>IFERROR((IF(O18="",0,O18*Configuración!$B$4)+IF(R18="",0,R18*Configuración!$B$5)+IF(AA18="",0,AA18*Configuración!$B$6)+IF(AD18="",0,AD18*Configuración!$B$7))/(IF(O18="",0,Configuración!$B$4)+IF(R18="",0,Configuración!$B$5)+IF(AA18="",0,Configuración!$B$6)+IF(AD18="",0,Configuración!$B$7)),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.9714285714285715</v>
       </c>
       <c r="AG18" s="15" t="str">
         <f>IF(AF18="","",IF(AE18&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF18&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3270,8 +3440,12 @@
       <c r="E19" s="11">
         <v>5</v>
       </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
+      <c r="F19" s="11">
+        <v>5</v>
+      </c>
+      <c r="G19" s="11">
+        <v>5</v>
+      </c>
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
       <c r="J19" s="11"/>
@@ -3293,17 +3467,23 @@
         <f t="shared" si="1"/>
         <v>4.9000000000000004</v>
       </c>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
+      <c r="S19" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="T19" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="U19" s="11">
+        <v>4.8</v>
+      </c>
       <c r="V19" s="11"/>
       <c r="W19" s="11"/>
       <c r="X19" s="11"/>
       <c r="Y19" s="11"/>
       <c r="Z19" s="11"/>
-      <c r="AA19" s="12" t="str">
+      <c r="AA19" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.6000000000000005</v>
       </c>
       <c r="AB19" s="11"/>
       <c r="AC19" s="11"/>
@@ -3316,7 +3496,7 @@
       </c>
       <c r="AF19" s="14">
         <f>IFERROR((IF(O19="",0,O19*Configuración!$B$4)+IF(R19="",0,R19*Configuración!$B$5)+IF(AA19="",0,AA19*Configuración!$B$6)+IF(AD19="",0,AD19*Configuración!$B$7))/(IF(O19="",0,Configuración!$B$4)+IF(R19="",0,Configuración!$B$5)+IF(AA19="",0,Configuración!$B$6)+IF(AD19="",0,Configuración!$B$7)),"")</f>
-        <v>4.9499999999999993</v>
+        <v>4.7</v>
       </c>
       <c r="AG19" s="15" t="str">
         <f>IF(AF19="","",IF(AE19&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF19&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3342,7 +3522,9 @@
       <c r="F20" s="11">
         <v>5</v>
       </c>
-      <c r="G20" s="11"/>
+      <c r="G20" s="11">
+        <v>5</v>
+      </c>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
@@ -3364,17 +3546,23 @@
         <f t="shared" si="1"/>
         <v>4.9000000000000004</v>
       </c>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
+      <c r="S20" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="T20" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="U20" s="11">
+        <v>4.8</v>
+      </c>
       <c r="V20" s="11"/>
       <c r="W20" s="11"/>
       <c r="X20" s="11"/>
       <c r="Y20" s="11"/>
       <c r="Z20" s="11"/>
-      <c r="AA20" s="12" t="str">
+      <c r="AA20" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.6000000000000005</v>
       </c>
       <c r="AB20" s="11"/>
       <c r="AC20" s="11"/>
@@ -3387,7 +3575,7 @@
       </c>
       <c r="AF20" s="14">
         <f>IFERROR((IF(O20="",0,O20*Configuración!$B$4)+IF(R20="",0,R20*Configuración!$B$5)+IF(AA20="",0,AA20*Configuración!$B$6)+IF(AD20="",0,AD20*Configuración!$B$7))/(IF(O20="",0,Configuración!$B$4)+IF(R20="",0,Configuración!$B$5)+IF(AA20="",0,Configuración!$B$6)+IF(AD20="",0,Configuración!$B$7)),"")</f>
-        <v>4.9499999999999993</v>
+        <v>4.7</v>
       </c>
       <c r="AG20" s="15" t="str">
         <f>IF(AF20="","",IF(AE20&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF20&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3410,8 +3598,12 @@
       <c r="E21" s="11">
         <v>5</v>
       </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
+      <c r="F21" s="11">
+        <v>5</v>
+      </c>
+      <c r="G21" s="11">
+        <v>5</v>
+      </c>
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
@@ -3433,17 +3625,23 @@
         <f t="shared" si="1"/>
         <v>4.9000000000000004</v>
       </c>
-      <c r="S21" s="11"/>
-      <c r="T21" s="11"/>
-      <c r="U21" s="11"/>
+      <c r="S21" s="11">
+        <v>5</v>
+      </c>
+      <c r="T21" s="11">
+        <v>5</v>
+      </c>
+      <c r="U21" s="11">
+        <v>5</v>
+      </c>
       <c r="V21" s="11"/>
       <c r="W21" s="11"/>
       <c r="X21" s="11"/>
       <c r="Y21" s="11"/>
       <c r="Z21" s="11"/>
-      <c r="AA21" s="12" t="str">
+      <c r="AA21" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AB21" s="11"/>
       <c r="AC21" s="11"/>
@@ -3456,7 +3654,7 @@
       </c>
       <c r="AF21" s="14">
         <f>IFERROR((IF(O21="",0,O21*Configuración!$B$4)+IF(R21="",0,R21*Configuración!$B$5)+IF(AA21="",0,AA21*Configuración!$B$6)+IF(AD21="",0,AD21*Configuración!$B$7))/(IF(O21="",0,Configuración!$B$4)+IF(R21="",0,Configuración!$B$5)+IF(AA21="",0,Configuración!$B$6)+IF(AD21="",0,Configuración!$B$7)),"")</f>
-        <v>4.9499999999999993</v>
+        <v>4.9857142857142867</v>
       </c>
       <c r="AG21" s="15" t="str">
         <f>IF(AF21="","",IF(AE21&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF21&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3479,8 +3677,12 @@
       <c r="E22" s="11">
         <v>5</v>
       </c>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
+      <c r="F22" s="11">
+        <v>5</v>
+      </c>
+      <c r="G22" s="11">
+        <v>4.5</v>
+      </c>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
@@ -3490,7 +3692,7 @@
       <c r="N22" s="11"/>
       <c r="O22" s="12">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="P22" s="11">
         <v>4.5</v>
@@ -3502,17 +3704,23 @@
         <f t="shared" si="1"/>
         <v>4.75</v>
       </c>
-      <c r="S22" s="11"/>
-      <c r="T22" s="11"/>
-      <c r="U22" s="11"/>
+      <c r="S22" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="T22" s="11">
+        <v>5</v>
+      </c>
+      <c r="U22" s="11">
+        <v>5</v>
+      </c>
       <c r="V22" s="11"/>
       <c r="W22" s="11"/>
       <c r="X22" s="11"/>
       <c r="Y22" s="11"/>
       <c r="Z22" s="11"/>
-      <c r="AA22" s="12" t="str">
+      <c r="AA22" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.7666666666666666</v>
       </c>
       <c r="AB22" s="11"/>
       <c r="AC22" s="11"/>
@@ -3525,7 +3733,7 @@
       </c>
       <c r="AF22" s="14">
         <f>IFERROR((IF(O22="",0,O22*Configuración!$B$4)+IF(R22="",0,R22*Configuración!$B$5)+IF(AA22="",0,AA22*Configuración!$B$6)+IF(AD22="",0,AD22*Configuración!$B$7))/(IF(O22="",0,Configuración!$B$4)+IF(R22="",0,Configuración!$B$5)+IF(AA22="",0,Configuración!$B$6)+IF(AD22="",0,Configuración!$B$7)),"")</f>
-        <v>4.875</v>
+        <v>4.7738095238095246</v>
       </c>
       <c r="AG22" s="15" t="str">
         <f>IF(AF22="","",IF(AE22&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF22&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3536,7 +3744,7 @@
       <c r="A23" s="16">
         <v>20</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="45" t="s">
         <v>119</v>
       </c>
       <c r="C23" s="17" t="s">
@@ -3548,8 +3756,12 @@
       <c r="E23" s="11">
         <v>5</v>
       </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
+      <c r="F23" s="11">
+        <v>5</v>
+      </c>
+      <c r="G23" s="11">
+        <v>5</v>
+      </c>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
@@ -3571,17 +3783,23 @@
         <f t="shared" si="1"/>
         <v>4.9000000000000004</v>
       </c>
-      <c r="S23" s="11"/>
-      <c r="T23" s="11"/>
-      <c r="U23" s="11"/>
+      <c r="S23" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="T23" s="11">
+        <v>5</v>
+      </c>
+      <c r="U23" s="11">
+        <v>5</v>
+      </c>
       <c r="V23" s="11"/>
       <c r="W23" s="11"/>
       <c r="X23" s="11"/>
       <c r="Y23" s="11"/>
       <c r="Z23" s="11"/>
-      <c r="AA23" s="12" t="str">
+      <c r="AA23" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.9333333333333336</v>
       </c>
       <c r="AB23" s="11"/>
       <c r="AC23" s="11"/>
@@ -3594,7 +3812,7 @@
       </c>
       <c r="AF23" s="14">
         <f>IFERROR((IF(O23="",0,O23*Configuración!$B$4)+IF(R23="",0,R23*Configuración!$B$5)+IF(AA23="",0,AA23*Configuración!$B$6)+IF(AD23="",0,AD23*Configuración!$B$7))/(IF(O23="",0,Configuración!$B$4)+IF(R23="",0,Configuración!$B$5)+IF(AA23="",0,Configuración!$B$6)+IF(AD23="",0,Configuración!$B$7)),"")</f>
-        <v>4.9499999999999993</v>
+        <v>4.9380952380952392</v>
       </c>
       <c r="AG23" s="15" t="str">
         <f>IF(AF23="","",IF(AE23&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF23&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3617,8 +3835,12 @@
       <c r="E24" s="11">
         <v>2.5</v>
       </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
+      <c r="F24" s="44">
+        <v>5</v>
+      </c>
+      <c r="G24" s="11">
+        <v>5</v>
+      </c>
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
       <c r="J24" s="11"/>
@@ -3628,7 +3850,7 @@
       <c r="N24" s="11"/>
       <c r="O24" s="12">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="P24" s="11">
         <v>4.5</v>
@@ -3640,17 +3862,23 @@
         <f t="shared" si="1"/>
         <v>4.75</v>
       </c>
-      <c r="S24" s="11"/>
-      <c r="T24" s="11"/>
-      <c r="U24" s="11"/>
+      <c r="S24" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="T24" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U24" s="11">
+        <v>5</v>
+      </c>
       <c r="V24" s="11"/>
       <c r="W24" s="11"/>
       <c r="X24" s="11"/>
       <c r="Y24" s="11"/>
       <c r="Z24" s="11"/>
-      <c r="AA24" s="12" t="str">
+      <c r="AA24" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.7666666666666666</v>
       </c>
       <c r="AB24" s="11"/>
       <c r="AC24" s="11"/>
@@ -3663,7 +3891,7 @@
       </c>
       <c r="AF24" s="14">
         <f>IFERROR((IF(O24="",0,O24*Configuración!$B$4)+IF(R24="",0,R24*Configuración!$B$5)+IF(AA24="",0,AA24*Configuración!$B$6)+IF(AD24="",0,AD24*Configuración!$B$7))/(IF(O24="",0,Configuración!$B$4)+IF(R24="",0,Configuración!$B$5)+IF(AA24="",0,Configuración!$B$6)+IF(AD24="",0,Configuración!$B$7)),"")</f>
-        <v>3.6250000000000004</v>
+        <v>4.6785714285714297</v>
       </c>
       <c r="AG24" s="15" t="str">
         <f>IF(AF24="","",IF(AE24&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF24&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3686,8 +3914,12 @@
       <c r="E25" s="11">
         <v>5</v>
       </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
+      <c r="F25" s="11">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G25" s="11">
+        <v>5</v>
+      </c>
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
@@ -3697,7 +3929,7 @@
       <c r="N25" s="11"/>
       <c r="O25" s="12">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="P25" s="11">
         <v>4.8</v>
@@ -3709,17 +3941,23 @@
         <f t="shared" si="1"/>
         <v>4.8499999999999996</v>
       </c>
-      <c r="S25" s="11"/>
-      <c r="T25" s="11"/>
-      <c r="U25" s="11"/>
+      <c r="S25" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="T25" s="11">
+        <v>5</v>
+      </c>
+      <c r="U25" s="11">
+        <v>5</v>
+      </c>
       <c r="V25" s="11"/>
       <c r="W25" s="11"/>
       <c r="X25" s="11"/>
       <c r="Y25" s="11"/>
       <c r="Z25" s="11"/>
-      <c r="AA25" s="12" t="str">
+      <c r="AA25" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.8666666666666663</v>
       </c>
       <c r="AB25" s="11"/>
       <c r="AC25" s="11"/>
@@ -3732,7 +3970,7 @@
       </c>
       <c r="AF25" s="14">
         <f>IFERROR((IF(O25="",0,O25*Configuración!$B$4)+IF(R25="",0,R25*Configuración!$B$5)+IF(AA25="",0,AA25*Configuración!$B$6)+IF(AD25="",0,AD25*Configuración!$B$7))/(IF(O25="",0,Configuración!$B$4)+IF(R25="",0,Configuración!$B$5)+IF(AA25="",0,Configuración!$B$6)+IF(AD25="",0,Configuración!$B$7)),"")</f>
-        <v>4.9249999999999998</v>
+        <v>4.8404761904761902</v>
       </c>
       <c r="AG25" s="15" t="str">
         <f>IF(AF25="","",IF(AE25&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF25&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3755,8 +3993,10 @@
       <c r="E26" s="11">
         <v>1</v>
       </c>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
+      <c r="F26" s="11">
+        <v>1</v>
+      </c>
+      <c r="G26" s="44"/>
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
       <c r="J26" s="11"/>
@@ -3778,17 +4018,23 @@
         <f t="shared" si="1"/>
         <v>4.45</v>
       </c>
-      <c r="S26" s="11"/>
-      <c r="T26" s="11"/>
-      <c r="U26" s="11"/>
+      <c r="S26" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="T26" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="U26" s="11">
+        <v>4.8</v>
+      </c>
       <c r="V26" s="11"/>
       <c r="W26" s="11"/>
       <c r="X26" s="11"/>
       <c r="Y26" s="11"/>
       <c r="Z26" s="11"/>
-      <c r="AA26" s="12" t="str">
+      <c r="AA26" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.6000000000000005</v>
       </c>
       <c r="AB26" s="11"/>
       <c r="AC26" s="11"/>
@@ -3801,11 +4047,11 @@
       </c>
       <c r="AF26" s="14">
         <f>IFERROR((IF(O26="",0,O26*Configuración!$B$4)+IF(R26="",0,R26*Configuración!$B$5)+IF(AA26="",0,AA26*Configuración!$B$6)+IF(AD26="",0,AD26*Configuración!$B$7))/(IF(O26="",0,Configuración!$B$4)+IF(R26="",0,Configuración!$B$5)+IF(AA26="",0,Configuración!$B$6)+IF(AD26="",0,Configuración!$B$7)),"")</f>
-        <v>2.7250000000000001</v>
+        <v>4.0642857142857149</v>
       </c>
       <c r="AG26" s="15" t="str">
         <f>IF(AF26="","",IF(AE26&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF26&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
-        <v>REPROBADO</v>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="27" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3824,8 +4070,12 @@
       <c r="E27" s="11">
         <v>5</v>
       </c>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
+      <c r="F27" s="11">
+        <v>5</v>
+      </c>
+      <c r="G27" s="11">
+        <v>5</v>
+      </c>
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
@@ -3847,17 +4097,23 @@
         <f t="shared" si="1"/>
         <v>4.9000000000000004</v>
       </c>
-      <c r="S27" s="11"/>
-      <c r="T27" s="11"/>
-      <c r="U27" s="11"/>
+      <c r="S27" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="T27" s="11">
+        <v>5</v>
+      </c>
+      <c r="U27" s="11">
+        <v>5</v>
+      </c>
       <c r="V27" s="11"/>
       <c r="W27" s="11"/>
       <c r="X27" s="11"/>
       <c r="Y27" s="11"/>
       <c r="Z27" s="11"/>
-      <c r="AA27" s="12" t="str">
+      <c r="AA27" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.8666666666666663</v>
       </c>
       <c r="AB27" s="11"/>
       <c r="AC27" s="11"/>
@@ -3870,7 +4126,7 @@
       </c>
       <c r="AF27" s="14">
         <f>IFERROR((IF(O27="",0,O27*Configuración!$B$4)+IF(R27="",0,R27*Configuración!$B$5)+IF(AA27="",0,AA27*Configuración!$B$6)+IF(AD27="",0,AD27*Configuración!$B$7))/(IF(O27="",0,Configuración!$B$4)+IF(R27="",0,Configuración!$B$5)+IF(AA27="",0,Configuración!$B$6)+IF(AD27="",0,Configuración!$B$7)),"")</f>
-        <v>4.9499999999999993</v>
+        <v>4.89047619047619</v>
       </c>
       <c r="AG27" s="15" t="str">
         <f>IF(AF27="","",IF(AE27&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF27&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3896,7 +4152,9 @@
       <c r="F28" s="11">
         <v>5</v>
       </c>
-      <c r="G28" s="11"/>
+      <c r="G28" s="11">
+        <v>5</v>
+      </c>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
       <c r="J28" s="11"/>
@@ -3906,7 +4164,7 @@
       <c r="N28" s="11"/>
       <c r="O28" s="12">
         <f t="shared" si="0"/>
-        <v>4.1500000000000004</v>
+        <v>4.4333333333333336</v>
       </c>
       <c r="P28" s="11">
         <v>4.5</v>
@@ -3918,17 +4176,23 @@
         <f t="shared" si="1"/>
         <v>4.7</v>
       </c>
-      <c r="S28" s="11"/>
-      <c r="T28" s="11"/>
-      <c r="U28" s="11"/>
+      <c r="S28" s="11">
+        <v>5</v>
+      </c>
+      <c r="T28" s="11">
+        <v>5</v>
+      </c>
+      <c r="U28" s="11">
+        <v>5</v>
+      </c>
       <c r="V28" s="11"/>
       <c r="W28" s="11"/>
       <c r="X28" s="11"/>
       <c r="Y28" s="11"/>
       <c r="Z28" s="11"/>
-      <c r="AA28" s="12" t="str">
+      <c r="AA28" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AB28" s="11"/>
       <c r="AC28" s="11"/>
@@ -3941,7 +4205,7 @@
       </c>
       <c r="AF28" s="14">
         <f>IFERROR((IF(O28="",0,O28*Configuración!$B$4)+IF(R28="",0,R28*Configuración!$B$5)+IF(AA28="",0,AA28*Configuración!$B$6)+IF(AD28="",0,AD28*Configuración!$B$7))/(IF(O28="",0,Configuración!$B$4)+IF(R28="",0,Configuración!$B$5)+IF(AA28="",0,Configuración!$B$6)+IF(AD28="",0,Configuración!$B$7)),"")</f>
-        <v>4.4249999999999998</v>
+        <v>4.8761904761904757</v>
       </c>
       <c r="AG28" s="15" t="str">
         <f>IF(AF28="","",IF(AE28&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF28&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -3967,7 +4231,9 @@
       <c r="F29" s="11">
         <v>5</v>
       </c>
-      <c r="G29" s="11"/>
+      <c r="G29" s="11">
+        <v>5</v>
+      </c>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
       <c r="J29" s="11"/>
@@ -3989,17 +4255,23 @@
         <f t="shared" si="1"/>
         <v>4.8000000000000007</v>
       </c>
-      <c r="S29" s="11"/>
-      <c r="T29" s="11"/>
-      <c r="U29" s="11"/>
+      <c r="S29" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="T29" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="U29" s="11">
+        <v>5</v>
+      </c>
       <c r="V29" s="11"/>
       <c r="W29" s="11"/>
       <c r="X29" s="11"/>
       <c r="Y29" s="11"/>
       <c r="Z29" s="11"/>
-      <c r="AA29" s="12" t="str">
+      <c r="AA29" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.7666666666666666</v>
       </c>
       <c r="AB29" s="11"/>
       <c r="AC29" s="11"/>
@@ -4012,7 +4284,7 @@
       </c>
       <c r="AF29" s="14">
         <f>IFERROR((IF(O29="",0,O29*Configuración!$B$4)+IF(R29="",0,R29*Configuración!$B$5)+IF(AA29="",0,AA29*Configuración!$B$6)+IF(AD29="",0,AD29*Configuración!$B$7))/(IF(O29="",0,Configuración!$B$4)+IF(R29="",0,Configuración!$B$5)+IF(AA29="",0,Configuración!$B$6)+IF(AD29="",0,Configuración!$B$7)),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.8047619047619046</v>
       </c>
       <c r="AG29" s="15" t="str">
         <f>IF(AF29="","",IF(AE29&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF29&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -4038,7 +4310,9 @@
       <c r="F30" s="11">
         <v>5</v>
       </c>
-      <c r="G30" s="11"/>
+      <c r="G30" s="11">
+        <v>5</v>
+      </c>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
       <c r="J30" s="11"/>
@@ -4048,7 +4322,7 @@
       <c r="N30" s="11"/>
       <c r="O30" s="12">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="P30" s="11">
         <v>4.8</v>
@@ -4060,17 +4334,23 @@
         <f t="shared" si="1"/>
         <v>4.8499999999999996</v>
       </c>
-      <c r="S30" s="11"/>
-      <c r="T30" s="11"/>
-      <c r="U30" s="11"/>
+      <c r="S30" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="T30" s="11">
+        <v>5</v>
+      </c>
+      <c r="U30" s="11">
+        <v>4.8</v>
+      </c>
       <c r="V30" s="11"/>
       <c r="W30" s="11"/>
       <c r="X30" s="11"/>
       <c r="Y30" s="11"/>
       <c r="Z30" s="11"/>
-      <c r="AA30" s="12" t="str">
+      <c r="AA30" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.7</v>
       </c>
       <c r="AB30" s="11"/>
       <c r="AC30" s="11"/>
@@ -4083,7 +4363,7 @@
       </c>
       <c r="AF30" s="14">
         <f>IFERROR((IF(O30="",0,O30*Configuración!$B$4)+IF(R30="",0,R30*Configuración!$B$5)+IF(AA30="",0,AA30*Configuración!$B$6)+IF(AD30="",0,AD30*Configuración!$B$7))/(IF(O30="",0,Configuración!$B$4)+IF(R30="",0,Configuración!$B$5)+IF(AA30="",0,Configuración!$B$6)+IF(AD30="",0,Configuración!$B$7)),"")</f>
-        <v>4.6749999999999998</v>
+        <v>4.7166666666666668</v>
       </c>
       <c r="AG30" s="15" t="str">
         <f>IF(AF30="","",IF(AE30&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF30&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -4109,7 +4389,7 @@
       <c r="F31" s="11">
         <v>5</v>
       </c>
-      <c r="G31" s="11"/>
+      <c r="G31" s="44"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
       <c r="J31" s="11"/>
@@ -4131,17 +4411,23 @@
         <f t="shared" si="1"/>
         <v>4.75</v>
       </c>
-      <c r="S31" s="11"/>
-      <c r="T31" s="11"/>
-      <c r="U31" s="11"/>
+      <c r="S31" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="T31" s="11">
+        <v>5</v>
+      </c>
+      <c r="U31" s="11">
+        <v>5</v>
+      </c>
       <c r="V31" s="11"/>
       <c r="W31" s="11"/>
       <c r="X31" s="11"/>
       <c r="Y31" s="11"/>
       <c r="Z31" s="11"/>
-      <c r="AA31" s="12" t="str">
+      <c r="AA31" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.7666666666666666</v>
       </c>
       <c r="AB31" s="11"/>
       <c r="AC31" s="11"/>
@@ -4154,7 +4440,7 @@
       </c>
       <c r="AF31" s="14">
         <f>IFERROR((IF(O31="",0,O31*Configuración!$B$4)+IF(R31="",0,R31*Configuración!$B$5)+IF(AA31="",0,AA31*Configuración!$B$6)+IF(AD31="",0,AD31*Configuración!$B$7))/(IF(O31="",0,Configuración!$B$4)+IF(R31="",0,Configuración!$B$5)+IF(AA31="",0,Configuración!$B$6)+IF(AD31="",0,Configuración!$B$7)),"")</f>
-        <v>4.5</v>
+        <v>4.6904761904761907</v>
       </c>
       <c r="AG31" s="15" t="str">
         <f>IF(AF31="","",IF(AE31&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF31&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -4180,7 +4466,9 @@
       <c r="F32" s="11">
         <v>5</v>
       </c>
-      <c r="G32" s="11"/>
+      <c r="G32" s="11">
+        <v>5</v>
+      </c>
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
       <c r="J32" s="11"/>
@@ -4190,7 +4478,7 @@
       <c r="N32" s="11"/>
       <c r="O32" s="12">
         <f t="shared" si="0"/>
-        <v>3.25</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="P32" s="11">
         <v>4.8</v>
@@ -4202,17 +4490,23 @@
         <f t="shared" si="1"/>
         <v>4.9000000000000004</v>
       </c>
-      <c r="S32" s="11"/>
-      <c r="T32" s="11"/>
-      <c r="U32" s="11"/>
+      <c r="S32" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="T32" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="U32" s="11">
+        <v>4.8</v>
+      </c>
       <c r="V32" s="11"/>
       <c r="W32" s="11"/>
       <c r="X32" s="11"/>
       <c r="Y32" s="11"/>
       <c r="Z32" s="11"/>
-      <c r="AA32" s="12" t="str">
+      <c r="AA32" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>4.6000000000000005</v>
       </c>
       <c r="AB32" s="11"/>
       <c r="AC32" s="11"/>
@@ -4225,7 +4519,7 @@
       </c>
       <c r="AF32" s="14">
         <f>IFERROR((IF(O32="",0,O32*Configuración!$B$4)+IF(R32="",0,R32*Configuración!$B$5)+IF(AA32="",0,AA32*Configuración!$B$6)+IF(AD32="",0,AD32*Configuración!$B$7))/(IF(O32="",0,Configuración!$B$4)+IF(R32="",0,Configuración!$B$5)+IF(AA32="",0,Configuración!$B$6)+IF(AD32="",0,Configuración!$B$7)),"")</f>
-        <v>4.0750000000000002</v>
+        <v>4.5333333333333341</v>
       </c>
       <c r="AG32" s="15" t="str">
         <f>IF(AF32="","",IF(AE32&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF32&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -4248,8 +4542,12 @@
       <c r="E33" s="11">
         <v>5</v>
       </c>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
+      <c r="F33" s="11">
+        <v>5</v>
+      </c>
+      <c r="G33" s="11">
+        <v>5</v>
+      </c>
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
       <c r="J33" s="11"/>
@@ -4271,17 +4569,23 @@
         <f t="shared" si="1"/>
         <v>4.8000000000000007</v>
       </c>
-      <c r="S33" s="11"/>
-      <c r="T33" s="11"/>
-      <c r="U33" s="11"/>
+      <c r="S33" s="11">
+        <v>5</v>
+      </c>
+      <c r="T33" s="11">
+        <v>5</v>
+      </c>
+      <c r="U33" s="11">
+        <v>5</v>
+      </c>
       <c r="V33" s="11"/>
       <c r="W33" s="11"/>
       <c r="X33" s="11"/>
       <c r="Y33" s="11"/>
       <c r="Z33" s="11"/>
-      <c r="AA33" s="12" t="str">
+      <c r="AA33" s="12">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AB33" s="11"/>
       <c r="AC33" s="11"/>
@@ -4294,7 +4598,7 @@
       </c>
       <c r="AF33" s="14">
         <f>IFERROR((IF(O33="",0,O33*Configuración!$B$4)+IF(R33="",0,R33*Configuración!$B$5)+IF(AA33="",0,AA33*Configuración!$B$6)+IF(AD33="",0,AD33*Configuración!$B$7))/(IF(O33="",0,Configuración!$B$4)+IF(R33="",0,Configuración!$B$5)+IF(AA33="",0,Configuración!$B$6)+IF(AD33="",0,Configuración!$B$7)),"")</f>
-        <v>4.9000000000000004</v>
+        <v>4.9714285714285715</v>
       </c>
       <c r="AG33" s="15" t="str">
         <f>IF(AF33="","",IF(AE33&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF33&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -4309,12 +4613,18 @@
         <v>199</v>
       </c>
       <c r="C34" s="17"/>
-      <c r="D34" s="10"/>
+      <c r="D34" s="10">
+        <v>8</v>
+      </c>
       <c r="E34" s="11">
         <v>4.3</v>
       </c>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
+      <c r="F34" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G34" s="11">
+        <v>5</v>
+      </c>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
       <c r="J34" s="11"/>
@@ -4324,7 +4634,7 @@
       <c r="N34" s="11"/>
       <c r="O34" s="12">
         <f>IFERROR(AVERAGE(E34:N34),"")</f>
-        <v>4.3</v>
+        <v>4.5666666666666664</v>
       </c>
       <c r="P34" s="43">
         <v>4.5999999999999996</v>
@@ -4336,22 +4646,28 @@
         <f>IFERROR(AVERAGE(P34:Q34),"")</f>
         <v>4.75</v>
       </c>
-      <c r="S34" s="11"/>
-      <c r="T34" s="11"/>
-      <c r="U34" s="11"/>
+      <c r="S34" s="11">
+        <v>5</v>
+      </c>
+      <c r="T34" s="11">
+        <v>5</v>
+      </c>
+      <c r="U34" s="11">
+        <v>5</v>
+      </c>
       <c r="V34" s="11"/>
       <c r="W34" s="11"/>
       <c r="X34" s="11"/>
       <c r="Y34" s="11"/>
       <c r="Z34" s="11"/>
-      <c r="AA34" s="12" t="str">
-        <f t="shared" ref="AA34" si="4">IFERROR(AVERAGE(S34:Z34),"")</f>
-        <v/>
+      <c r="AA34" s="12">
+        <f>IFERROR(AVERAGE(S34:Z34),"")</f>
+        <v>5</v>
       </c>
       <c r="AB34" s="11"/>
       <c r="AC34" s="11"/>
       <c r="AD34" s="12" t="str">
-        <f t="shared" ref="AD34" si="5">IFERROR(AVERAGE(AB34:AC34),"")</f>
+        <f>IFERROR(AVERAGE(AB34:AC34),"")</f>
         <v/>
       </c>
       <c r="AE34" s="13">
@@ -4359,7 +4675,7 @@
       </c>
       <c r="AF34" s="14">
         <f>IFERROR((IF(O34="",0,O34*Configuración!$B$4)+IF(R34="",0,R34*Configuración!$B$5)+IF(AA34="",0,AA34*Configuración!$B$6)+IF(AD34="",0,AD34*Configuración!$B$7))/(IF(O34="",0,Configuración!$B$4)+IF(R34="",0,Configuración!$B$5)+IF(AA34="",0,Configuración!$B$6)+IF(AD34="",0,Configuración!$B$7)),"")</f>
-        <v>4.5249999999999995</v>
+        <v>4.9023809523809527</v>
       </c>
       <c r="AG34" s="15" t="str">
         <f>IF(AF34="","",IF(AE34&lt;Configuración!$B$12,"FALLA ASIST.",IF(AF34&gt;=Configuración!$B$11,"APROBADO","REPROBADO")))</f>
@@ -4378,122 +4694,125 @@
         <v>4.2193548387096778</v>
       </c>
       <c r="F35" s="20">
-        <f t="shared" ref="F35:AF35" si="6">IFERROR(AVERAGE(F4:F33),"")</f>
-        <v>4.9727272727272727</v>
-      </c>
-      <c r="G35" s="20" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="F35:AF35" si="4">IFERROR(AVERAGE(F4:F33),"")</f>
+        <v>4.7766666666666673</v>
+      </c>
+      <c r="G35" s="20">
+        <f t="shared" si="4"/>
+        <v>4.9814814814814818</v>
+      </c>
+      <c r="H35" s="20" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="H35" s="20" t="str">
-        <f t="shared" si="6"/>
+      <c r="I35" s="20" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="I35" s="20" t="str">
-        <f t="shared" si="6"/>
+      <c r="J35" s="20" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="J35" s="20" t="str">
-        <f t="shared" si="6"/>
+      <c r="K35" s="20" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K35" s="20" t="str">
-        <f t="shared" si="6"/>
+      <c r="L35" s="20" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="L35" s="20" t="str">
-        <f t="shared" si="6"/>
+      <c r="M35" s="20" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M35" s="20" t="str">
-        <f t="shared" si="6"/>
+      <c r="N35" s="20" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N35" s="20" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
       <c r="O35" s="20">
-        <f t="shared" si="6"/>
-        <v>4.3966666666666665</v>
+        <f t="shared" si="4"/>
+        <v>4.6061111111111126</v>
       </c>
       <c r="P35" s="20">
         <f>IFERROR(AVERAGE(P4:P34),"")</f>
         <v>4.7419354838709671</v>
       </c>
       <c r="Q35" s="20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>4.9066666666666672</v>
       </c>
       <c r="R35" s="20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>4.826666666666668</v>
       </c>
-      <c r="S35" s="20" t="str">
-        <f t="shared" si="6"/>
+      <c r="S35" s="20">
+        <f t="shared" si="4"/>
+        <v>4.5833333333333321</v>
+      </c>
+      <c r="T35" s="20">
+        <f t="shared" si="4"/>
+        <v>4.8866666666666667</v>
+      </c>
+      <c r="U35" s="20">
+        <f t="shared" si="4"/>
+        <v>4.9266666666666667</v>
+      </c>
+      <c r="V35" s="20" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="T35" s="20" t="str">
-        <f t="shared" si="6"/>
+      <c r="W35" s="20" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="U35" s="20" t="str">
-        <f t="shared" si="6"/>
+      <c r="X35" s="20" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="V35" s="20" t="str">
-        <f t="shared" si="6"/>
+      <c r="Y35" s="20" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="W35" s="20" t="str">
-        <f t="shared" si="6"/>
+      <c r="Z35" s="20" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="X35" s="20" t="str">
-        <f t="shared" si="6"/>
+      <c r="AA35" s="20">
+        <f t="shared" si="4"/>
+        <v>4.7988888888888876</v>
+      </c>
+      <c r="AB35" s="20" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y35" s="20" t="str">
-        <f t="shared" si="6"/>
+      <c r="AC35" s="20" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Z35" s="20" t="str">
-        <f t="shared" si="6"/>
+      <c r="AD35" s="20" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AA35" s="20" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AB35" s="20" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AC35" s="20" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AD35" s="20" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
       <c r="AE35" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF35" s="20">
-        <f t="shared" si="6"/>
-        <v>4.6116666666666664</v>
+        <f t="shared" si="4"/>
+        <v>4.7753174603174608</v>
       </c>
       <c r="AG35" s="18" t="str">
         <f>COUNTIF(AG4:AG33,"APROBADO")&amp;" aprob."</f>
-        <v>29 aprob.</v>
+        <v>30 aprob.</v>
       </c>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F36" t="s">
         <v>198</v>
       </c>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="T37" s="47"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AG36" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
@@ -4517,7 +4836,7 @@
       <formula>"FALLA ASIST."</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:AC34">
+  <conditionalFormatting sqref="E4:AC34 T37">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4562,25 +4881,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="49" t="s">
         <v>143</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="D3" s="45" t="s">
+      <c r="B3" s="49"/>
+      <c r="D3" s="49" t="s">
         <v>144</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
@@ -4617,7 +4936,7 @@
       </c>
       <c r="F5" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D5,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.6624999999999996</v>
+        <v>4.9273809523809522</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4626,7 +4945,7 @@
       </c>
       <c r="B6" s="28">
         <f>IFERROR(AVERAGE(Notas!$AF$4:$AF$33),"")</f>
-        <v>4.6116666666666664</v>
+        <v>4.7753174603174608</v>
       </c>
       <c r="D6" s="25">
         <v>2</v>
@@ -4637,7 +4956,7 @@
       </c>
       <c r="F6" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D6,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.5000000000000009</v>
+        <v>4.7698412698412698</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4646,7 +4965,7 @@
       </c>
       <c r="B7" s="28">
         <f>IFERROR(MAX(Notas!$AF$4:$AF$33),"")</f>
-        <v>4.9750000000000005</v>
+        <v>4.9857142857142867</v>
       </c>
       <c r="D7" s="25">
         <v>3</v>
@@ -4657,7 +4976,7 @@
       </c>
       <c r="F7" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D7,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.1749999999999998</v>
+        <v>4.4994047619047626</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4666,7 +4985,7 @@
       </c>
       <c r="B8" s="28">
         <f>IFERROR(MIN(Notas!$AF$4:$AF$33),"")</f>
-        <v>2.7250000000000001</v>
+        <v>4.0642857142857149</v>
       </c>
       <c r="D8" s="25">
         <v>4</v>
@@ -4677,7 +4996,7 @@
       </c>
       <c r="F8" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D8,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.5</v>
+        <v>4.6583333333333332</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4686,7 +5005,7 @@
       </c>
       <c r="B9" s="28">
         <f>IFERROR(STDEV(Notas!$AF$4:$AF$33),"")</f>
-        <v>0.49856402994402321</v>
+        <v>0.18215236389040626</v>
       </c>
       <c r="D9" s="25">
         <v>5</v>
@@ -4697,7 +5016,7 @@
       </c>
       <c r="F9" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D9,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.6750000000000007</v>
+        <v>4.711904761904762</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4706,7 +5025,7 @@
       </c>
       <c r="B10" s="23">
         <f>COUNTIF(Notas!$AG$4:$AG$33,"APROBADO")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="25">
         <v>6</v>
@@ -4717,7 +5036,7 @@
       </c>
       <c r="F10" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D10,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.666666666666667</v>
+        <v>4.7460317460317469</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4726,7 +5045,7 @@
       </c>
       <c r="B11" s="23">
         <f>COUNTIF(Notas!$AG$4:$AG$33,"REPROBADO")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="25">
         <v>7</v>
@@ -4737,7 +5056,7 @@
       </c>
       <c r="F11" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D11,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.7062499999999998</v>
+        <v>4.9160714285714295</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4757,7 +5076,7 @@
       </c>
       <c r="F12" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D12,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.9249999999999998</v>
+        <v>4.9785714285714295</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4766,7 +5085,7 @@
       </c>
       <c r="B13" s="29">
         <f>IFERROR(COUNTIF(Notas!$AG$4:$AG$33,"APROBADO")/COUNT(Notas!$AF$4:$AF$33),"")</f>
-        <v>0.96666666666666667</v>
+        <v>1</v>
       </c>
       <c r="D13" s="25">
         <v>9</v>
@@ -4777,7 +5096,7 @@
       </c>
       <c r="F13" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$33,$D13,Notas!$AF$4:$AF$33),"")</f>
-        <v>4.9333333333333327</v>
+        <v>4.871428571428571</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4794,15 +5113,15 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="49" t="s">
         <v>157</v>
       </c>
-      <c r="B16" s="45"/>
-      <c r="D16" s="45" t="s">
+      <c r="B16" s="49"/>
+      <c r="D16" s="49" t="s">
         <v>158</v>
       </c>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
@@ -4810,7 +5129,7 @@
       </c>
       <c r="B17" s="28">
         <f>IFERROR(AVERAGE(Notas!$O$4:$O$33),"")</f>
-        <v>4.3966666666666665</v>
+        <v>4.6061111111111126</v>
       </c>
       <c r="D17" s="24" t="s">
         <v>160</v>
@@ -4839,16 +5158,16 @@
       <c r="A19" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="B19" s="28" t="str">
+      <c r="B19" s="28">
         <f>IFERROR(AVERAGE(Notas!$AA$4:$AA$33),"")</f>
-        <v/>
+        <v>4.7988888888888876</v>
       </c>
       <c r="D19" s="30" t="s">
         <v>165</v>
       </c>
       <c r="E19" s="23">
         <f>COUNTIFS(Notas!$AF$4:$AF$33,"&gt;="&amp;2,Notas!$AF$4:$AF$33,"&lt;"&amp;3)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -4873,7 +5192,7 @@
       </c>
       <c r="E21" s="23">
         <f>COUNTIFS(Notas!$AF$4:$AF$33,"&gt;="&amp;3.5,Notas!$AF$4:$AF$33,"&lt;"&amp;4)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -4882,7 +5201,7 @@
       </c>
       <c r="E22" s="23">
         <f>COUNTIFS(Notas!$AF$4:$AF$33,"&gt;="&amp;4,Notas!$AF$4:$AF$33,"&lt;"&amp;4.5)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -4891,7 +5210,7 @@
       </c>
       <c r="E23" s="23">
         <f>COUNTIFS(Notas!$AF$4:$AF$33,"&gt;="&amp;4.5,Notas!$AF$4:$AF$33,"&lt;"&amp;5.01)</f>
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -4918,11 +5237,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="31" t="s">
@@ -4993,11 +5312,11 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="49" t="s">
         <v>184</v>
       </c>
-      <c r="B10" s="45"/>
-      <c r="C10" s="45"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
@@ -5022,11 +5341,11 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
